--- a/Datas/LanguageSwitchDataList.xlsx
+++ b/Datas/LanguageSwitchDataList.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="LanguageSwitchData" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="1092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="1798">
   <si>
     <t>string</t>
   </si>
@@ -3490,6 +3491,2127 @@
   <si>
     <t>睡到晚上7点</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我来买东西！</t>
+  </si>
+  <si>
+    <t>你好,你的房子好大呀！</t>
+  </si>
+  <si>
+    <t>我来逛逛你的商店,\n今天有什么好东西呀？</t>
+  </si>
+  <si>
+    <t>你好！有什么事吗？</t>
+  </si>
+  <si>
+    <t>嗯..你,要干嘛？</t>
+  </si>
+  <si>
+    <t>嘿,你今天是来约我一起去冒险吗？</t>
+  </si>
+  <si>
+    <t>噢,你又发现什么了吗？</t>
+  </si>
+  <si>
+    <t>风带来了你的讯息..</t>
+  </si>
+  <si>
+    <t>准备好接受你的命运了吗？</t>
+  </si>
+  <si>
+    <t>你知道吗？当年我一个人在战场上…</t>
+  </si>
+  <si>
+    <t>欢迎光临。</t>
+  </si>
+  <si>
+    <t>嗨,今天天气不错,适合挑选家具哦。</t>
+  </si>
+  <si>
+    <t>对动物一定要温柔啊。</t>
+  </si>
+  <si>
+    <t>客人,你想要点什么？</t>
+  </si>
+  <si>
+    <t>想和我来一次命运的邂逅…</t>
+  </si>
+  <si>
+    <t>嗯,今天一定不要再犯错。</t>
+  </si>
+  <si>
+    <t>良好的工具可以使工作更有效率。</t>
+  </si>
+  <si>
+    <t>你是来参观我的商店的吗？请尽情参观吧。</t>
+  </si>
+  <si>
+    <t>年轻真好啊,如果可以,我想…</t>
+  </si>
+  <si>
+    <t>小家伙们,来挑点东西吧？</t>
+  </si>
+  <si>
+    <t>太好了,终于有人来陪我了。</t>
+  </si>
+  <si>
+    <t>职责、荣耀...抱歉,没看到你。</t>
+  </si>
+  <si>
+    <t>想要料理的话,可以和黛芙妮说。</t>
+  </si>
+  <si>
+    <t>啊！你是在开玩笑吧,不过这个不好笑哦。</t>
+  </si>
+  <si>
+    <t>你,你怎么能这么轻易,说出,这种话…</t>
+  </si>
+  <si>
+    <t>如果你是一个大英雄就好了…</t>
+  </si>
+  <si>
+    <t>抱歉,我只对考古感兴趣…</t>
+  </si>
+  <si>
+    <t>就让这份情绪随风而逝吧…</t>
+  </si>
+  <si>
+    <t>小家伙,你能驾驭我吗?</t>
+  </si>
+  <si>
+    <t>我的激情已经留在战场上了。</t>
+  </si>
+  <si>
+    <t>好高兴哦,不过我还得努力长大才行呢。</t>
+  </si>
+  <si>
+    <t>谢谢,如果可以请在店里买点东西吧。</t>
+  </si>
+  <si>
+    <t>抱歉,人类的心是会说谎的。</t>
+  </si>
+  <si>
+    <t>真的吗,谢谢你给我打气。</t>
+  </si>
+  <si>
+    <t>我对长期的感情没有兴趣。</t>
+  </si>
+  <si>
+    <t>你说的是什么意思,我听不懂哎…</t>
+  </si>
+  <si>
+    <t>我已经对大哥发过誓了,无法接受你的心意。</t>
+  </si>
+  <si>
+    <t>啊,你难道看上我的身家了吗？</t>
+  </si>
+  <si>
+    <t>哎呀,我这可衰老的心可经不起你的挑拨…</t>
+  </si>
+  <si>
+    <t>如果我还年轻的话…</t>
+  </si>
+  <si>
+    <t>对不起,人鱼和人类是不会有结果的…</t>
+  </si>
+  <si>
+    <t>我还是想以我的事业为重…</t>
+  </si>
+  <si>
+    <t>虽然我是想给黛芙妮她们找个父亲,但你就…</t>
+  </si>
+  <si>
+    <t>抱歉,从上次受伤后,我还在修养中,过段时间再来找我吧。</t>
+  </si>
+  <si>
+    <t>我还是想和更熟悉的人一起冒险...</t>
+  </si>
+  <si>
+    <t>OK,那么我们就一起去冒险吧.</t>
+  </si>
+  <si>
+    <t>嗯,你这么请求的话,我只好答应了.</t>
+  </si>
+  <si>
+    <t>我早就等着这一天了.</t>
+  </si>
+  <si>
+    <t>希望这次会发现一些古代遗迹线索.</t>
+  </si>
+  <si>
+    <t>好啦,好啦,清风告诉我应该和你一起出动…</t>
+  </si>
+  <si>
+    <t>你可要机灵点呀,我可不想让你拖后腿。</t>
+  </si>
+  <si>
+    <t>那么就让你见识一下我英勇的身姿吧。</t>
+  </si>
+  <si>
+    <t>那么,请多指教了。</t>
+  </si>
+  <si>
+    <t>好吧,希望会有一个美好的旅程。</t>
+  </si>
+  <si>
+    <t>要紧紧跟着姐姐后面,姐姐会保护你的。</t>
+  </si>
+  <si>
+    <t>嗯,很久没有出去了,出去走走也不错。</t>
+  </si>
+  <si>
+    <t>既然你这么有诚意,就答应你吧。</t>
+  </si>
+  <si>
+    <t>正好我也想练习一下我的技能。</t>
+  </si>
+  <si>
+    <t>也应该活动活动手脚了。</t>
+  </si>
+  <si>
+    <t>你终于认识到我的厉害了啊。</t>
+  </si>
+  <si>
+    <t>如果你不嫌弃我这把老骨头的话…</t>
+  </si>
+  <si>
+    <t>偶尔也该让布莱兹独自看店了。</t>
+  </si>
+  <si>
+    <t>其实我早就想出去看看了。</t>
+  </si>
+  <si>
+    <t>放心吧,战士的职责就是保护平民。</t>
+  </si>
+  <si>
+    <t>我也该出去寻找一下新食材了。</t>
+  </si>
+  <si>
+    <t>噢..你想聊什么..真无聊啊</t>
+  </si>
+  <si>
+    <t>我知道了,你一定是来偷看我姐姐的。</t>
+  </si>
+  <si>
+    <t>你有留意旅途中未知的遗迹吗？不知道那些到底代表着什么？</t>
+  </si>
+  <si>
+    <t>啊,风中传来你的气息,让我将思念寄托于你…</t>
+  </si>
+  <si>
+    <t>现在的人类真是太羸弱了,如果是古代那些强悍的战士,周围就不会有怪物存在了。</t>
+  </si>
+  <si>
+    <t>在那场战争中,本来王国军处于劣势,但是凭着我的活跃表现,才逆转获得胜利。</t>
+  </si>
+  <si>
+    <t>你喜欢吃什么料理呢？奥蒂莉亚喜欢烤海鲜噢。</t>
+  </si>
+  <si>
+    <t>真高兴你能来找我玩,明天你还会来吗？</t>
+  </si>
+  <si>
+    <t>动物是我们的好伙伴,不仅有优良的产出还能跟随我们战斗呢。</t>
+  </si>
+  <si>
+    <t>真的很感谢客人对本店的光顾,能帮上妈妈我也很高兴。</t>
+  </si>
+  <si>
+    <t>在这个宁静的小镇,我找到了久违的安心,我想我还会再住一阵子吧。</t>
+  </si>
+  <si>
+    <t>究竟怎样才能和是否一样优秀呢？这真让我困扰。</t>
+  </si>
+  <si>
+    <t>我一定要把布拉德利培养成一个优秀的男人,这就是我生活的意义。</t>
+  </si>
+  <si>
+    <t>我曾经走过大山和大海,追寻财富的脚步永不停息,你能理解吗？</t>
+  </si>
+  <si>
+    <t>唉,过去这么多年来,玛德琳还不肯原谅我吗…</t>
+  </si>
+  <si>
+    <t>可爱的小家伙们,今天又来问候我啊,真的谢谢你们了。</t>
+  </si>
+  <si>
+    <t>见到你,多莉丝真高兴,真像能和你一样到处去玩。</t>
+  </si>
+  <si>
+    <t>我一定要成为将军那样强大的军人,为此我得坚持锻炼。</t>
+  </si>
+  <si>
+    <t>制作料理一定要有想象力,只有这样才能将美味融入其中。</t>
+  </si>
+  <si>
+    <t>像我这样的天才果然不应该困在这种小店里吧。</t>
+  </si>
+  <si>
+    <t>我其实一直在锻炼,因为我知道有一天命运会安排我成为救世主。</t>
+  </si>
+  <si>
+    <t>经过我的研究,我推断在远古时代有一个伟大的文明,但是不知为何消失了。</t>
+  </si>
+  <si>
+    <t>没必要活得太累,偶尔停下脚步欣赏一下自然也是很好的。</t>
+  </si>
+  <si>
+    <t>魔法=百分之九九的天赋+百分之一的努力,所以你似乎无法成为魔法师了。</t>
+  </si>
+  <si>
+    <t>如果不是那件事,王国的军队的总司令官非我莫属了。</t>
+  </si>
+  <si>
+    <t>不管下雨还是晴天,我觉得每一天的天气都很好,你觉得呢？</t>
+  </si>
+  <si>
+    <t>其实班尼迪克先生不是你看到的那样,他也有温柔的一面。</t>
+  </si>
+  <si>
+    <t>每天都要记得喂养动物啊,不要让他们挨饿。</t>
+  </si>
+  <si>
+    <t>和你说一会话,真的很轻松,可是我还有工作,不能在和你再聊了。</t>
+  </si>
+  <si>
+    <t>漂泊了多年,没想到我还是感到很寂寞,不知道我的归宿在哪里。</t>
+  </si>
+  <si>
+    <t>师父是个大美人吧,不过你可不要打她的主意哦,师父可不是你能驾驭的。</t>
+  </si>
+  <si>
+    <t>如果你学会了制作的话,你就可以自己制作装备了。</t>
+  </si>
+  <si>
+    <t>在这个世界上除了人类还有一些奇怪的种族,可是为什么是人类占据了大陆呢？</t>
+  </si>
+  <si>
+    <t>你听到了什么？可不要到处乱说啊,这都是我们年轻时发生的事。</t>
+  </si>
+  <si>
+    <t>传说我们人鱼族有一位女孩的鱼尾变成了双脚,走上了陆地呢…</t>
+  </si>
+  <si>
+    <t>其实一个人站岗也挺无聊的,如果有人来和我聊聊的话,我会很高兴。</t>
+  </si>
+  <si>
+    <t>如果你发现了奇怪的食材,请一定要告诉我。</t>
+  </si>
+  <si>
+    <t>如果没什么事,可以请你离开吗？</t>
+  </si>
+  <si>
+    <t>今天我还得看店,不能展示我的雄姿给你看,改天再来吧。</t>
+  </si>
+  <si>
+    <t>这个小镇里应该有一个古代遗迹的,但是我怎么也找不到。</t>
+  </si>
+  <si>
+    <t>这里真是一个神奇的地方,你知道吗,在小镇的四周竟然分布着四季。</t>
+  </si>
+  <si>
+    <t>魔法药剂现在还在配置,暂时还无法供应。</t>
+  </si>
+  <si>
+    <t>注意,不要走得太远,外面可是有很多可怕的怪物。</t>
+  </si>
+  <si>
+    <t>好孩子饮食要均衡哦,不论是蔬菜还是肉类都不能挑食。</t>
+  </si>
+  <si>
+    <t>如果有一天你要组成家庭,那么你一定要到这里购买家具啊。</t>
+  </si>
+  <si>
+    <t>如果可以的话,希望你能多来找格吉尔玩。</t>
+  </si>
+  <si>
+    <t>我的妈妈好厉害的,很多料理都是她自己发明的。</t>
+  </si>
+  <si>
+    <t>呵呵,和你说这么多,你也不懂吧,像你这种小孩子还要多多进行人生历练啊。</t>
+  </si>
+  <si>
+    <t>最近师父获得了一些魔法药剂的配方,我们正在收集材料调配。</t>
+  </si>
+  <si>
+    <t>一定不要吝啬装备哦,即使不用的装备也可以售卖获得金币。</t>
+  </si>
+  <si>
+    <t>传说中这个世界曾经被魔族统治,不知道是不是真的。</t>
+  </si>
+  <si>
+    <t>想不到还会有年轻人来找我这个老头子聊天,真令人高兴。</t>
+  </si>
+  <si>
+    <t>虽然我的道具屋里都是些过时的老东西,但是很用哦。</t>
+  </si>
+  <si>
+    <t>其实水里也有很多有意思的地方,如果你能在水里生存的话……</t>
+  </si>
+  <si>
+    <t>如果遇到了危险,一定要向我求助,我可是时刻准备着。</t>
+  </si>
+  <si>
+    <t>我的女儿可是我的心肝宝贝,你可不要想轻易就将他们欺骗到手。</t>
+  </si>
+  <si>
+    <t>今天是你的生日吧,这是我送你的生日礼物。</t>
+  </si>
+  <si>
+    <t>正好这个用不到了,就送你吧。</t>
+  </si>
+  <si>
+    <t>一直都收你的礼物,这个就表达一下我的心意吧。</t>
+  </si>
+  <si>
+    <t>这些东西,希望你能用的上。</t>
+  </si>
+  <si>
+    <t>生日快乐哟,希望你喜欢我的礼物。</t>
+  </si>
+  <si>
+    <t>你是来向我讨礼物的吗？好吧,这个就给你吧。</t>
+  </si>
+  <si>
+    <t>孩子,恭喜你又长大一岁了,给你我的礼物。</t>
+  </si>
+  <si>
+    <t>生日快乐！</t>
+  </si>
+  <si>
+    <t>希望你能喜欢我送你的礼物。</t>
+  </si>
+  <si>
+    <t>我记得今天是你的生日,给你的礼物。</t>
+  </si>
+  <si>
+    <t>希望幸运之神能日日降临于你。</t>
+  </si>
+  <si>
+    <t>咦,今天是你的生日吗？那这个可以作为生日礼物吗？</t>
+  </si>
+  <si>
+    <t>我这里有一些基础材料,送你一些作为生日礼物吧。</t>
+  </si>
+  <si>
+    <t>今天对你是重要的一天,收下我的礼物吧。</t>
+  </si>
+  <si>
+    <t>这是我的一点心意,虽然我没有什么其他东西。</t>
+  </si>
+  <si>
+    <t>我只有这些东西,应该能有点用。</t>
+  </si>
+  <si>
+    <t>马车怎么停下了？</t>
+  </si>
+  <si>
+    <t>看来有怪物逼近了。</t>
+  </si>
+  <si>
+    <t>那可怎么办？</t>
+  </si>
+  <si>
+    <t>不必担心,凭着我们的几个实力,一般怪物都不难对付！</t>
+  </si>
+  <si>
+    <t>怪物来了,准备战斗！</t>
+  </si>
+  <si>
+    <t>刚才真是危险啊！</t>
+  </si>
+  <si>
+    <t>好,趁现在快点赶到镇子吧。</t>
+  </si>
+  <si>
+    <t>我代表小镇欢迎你,小朋友。</t>
+  </si>
+  <si>
+    <t>你的外公已经离开了,就由我来指导你在小镇的生活吧。</t>
+  </si>
+  <si>
+    <t>那么,我该做什么？</t>
+  </si>
+  <si>
+    <t>今天你已经很累了,走吧,我带你回家。</t>
+  </si>
+  <si>
+    <t>以后这就是你的家了，早点休息吧，明天我会来叫醒你的。</t>
+  </si>
+  <si>
+    <t>我先走了，晚安</t>
+  </si>
+  <si>
+    <t>哎呀,你已经起床了啊,那么我们就先到你外公留下的商店去看看吧。</t>
+  </si>
+  <si>
+    <t>按照你外公的嘱托,我们给你开放了商贸、社交许可,其他的许可还需要你自己努力达成。</t>
+  </si>
+  <si>
+    <t>许可清单你可以随时去看看。</t>
+  </si>
+  <si>
+    <t>那么，现在我应该做些什么呢？</t>
+  </si>
+  <si>
+    <t>从最简单的售卖开始吧，看到前面的柜台了么,将东西放到上面就行了。</t>
+  </si>
+  <si>
+    <t>对了，有些商品只能放在特定柜台上，你可以仔细观察一下。</t>
+  </si>
+  <si>
+    <t>很好，现在去把商店的招牌换成营业吧，只有营业状态时才会有客人上门。</t>
+  </si>
+  <si>
+    <t>做的不错，你可以再熟悉一下售卖商品，我在外面等你。</t>
+  </si>
+  <si>
+    <t>看来你已经掌握了售卖物品的方法了,如此一来,你的种植许可也开放了,那么现在去买一些种子回来吧。</t>
+  </si>
+  <si>
+    <t>哪里有种子出售？</t>
+  </si>
+  <si>
+    <t>植物店里拥有各种植物种子,来跟我去熟悉熟悉吧。</t>
+  </si>
+  <si>
+    <t>这就是新来小镇的孩子吧，欢迎你哟，想来点什么？</t>
+  </si>
+  <si>
+    <t>买好了种子了，我们回农场种植吧。</t>
+  </si>
+  <si>
+    <t>等一下，我这里有一些种植工具，送给你。</t>
+  </si>
+  <si>
+    <t>谢谢，我会好好使用的。</t>
+  </si>
+  <si>
+    <t>第一步,先将农具从背包里拿出来。</t>
+  </si>
+  <si>
+    <t>现在走到农田上，使用锄头将田地锄松吧。</t>
+  </si>
+  <si>
+    <t>很好,就是这样,现在选择种子进行播种吧。</t>
+  </si>
+  <si>
+    <t>好了,终于完成种植了。</t>
+  </si>
+  <si>
+    <t>别急,还差最后一步呢,种下的植物需要浇水,现在去河边打水回来。</t>
+  </si>
+  <si>
+    <t>记住每天都得来浇水啊,不然植物会枯死的。</t>
+  </si>
+  <si>
+    <t>植物生长需要几天时间,在此期间,不如去野外探险一下,也许会获得想不到的收获哦。</t>
+  </si>
+  <si>
+    <t>前面就是春之山脉的入口，今天就让我这个老头子陪你闯一下吧。</t>
+  </si>
+  <si>
+    <t>现在前进走到光圈中，开始今天的探索。</t>
+  </si>
+  <si>
+    <t>打起精神来，现在前进吧。</t>
+  </si>
+  <si>
+    <t>我的伤势需要休养几天,接下来的事情就要靠你自己努力了。</t>
+  </si>
+  <si>
+    <t>多么美丽的花儿啊,真的是送给我的吗？</t>
+  </si>
+  <si>
+    <t>想用鲜花俘虏我的心吗？</t>
+  </si>
+  <si>
+    <t>哦,太美了,我一直幻想着有人能送我鲜花呢。</t>
+  </si>
+  <si>
+    <t>你..你是什么意思？,不..不管怎样,谢谢了。</t>
+  </si>
+  <si>
+    <t>好高兴！竟然可以收到鲜花！</t>
+  </si>
+  <si>
+    <t>没想到像我这种老头子也可以收到年轻孩子的鲜花！</t>
+  </si>
+  <si>
+    <t>谢谢,这束鲜花我会铭记在心。</t>
+  </si>
+  <si>
+    <t>你的心意,我已知晓。</t>
+  </si>
+  <si>
+    <t>美丽的鲜花代表着美丽的心灵,你是我值得信赖的人…</t>
+  </si>
+  <si>
+    <t>鲜花是英雄的绝配,你真是我的知己…</t>
+  </si>
+  <si>
+    <t>谢谢你,如果可以,能多来陪陪我吗？</t>
+  </si>
+  <si>
+    <t>鲜花是爱情的魔法,现在我还没办法免疫…</t>
+  </si>
+  <si>
+    <t>收到花儿后,我也感到年轻了呢！</t>
+  </si>
+  <si>
+    <t>生命如花,我的心又变得有活力了。</t>
+  </si>
+  <si>
+    <t>愿这份美丽能长存常在！</t>
+  </si>
+  <si>
+    <t>原来,你对我…</t>
+  </si>
+  <si>
+    <t>嗯,对我来说,你很特别。</t>
+  </si>
+  <si>
+    <t>看来,我也该有自己的生活了。</t>
+  </si>
+  <si>
+    <t>我的少女心被你勾起了呢。</t>
+  </si>
+  <si>
+    <t>令人怀念啊,我的激情岁月。</t>
+  </si>
+  <si>
+    <t>今天的鲜花已经收到,这份美丽请留到明天。</t>
+  </si>
+  <si>
+    <t>好高兴！其实我也喜欢你！</t>
+  </si>
+  <si>
+    <t>你..你说什么？既然,你..坚持的话,我..就勉强答应你吧。</t>
+  </si>
+  <si>
+    <t>那么,今后我们就一起努力吧。</t>
+  </si>
+  <si>
+    <t>嗯,我也该留意一下身边的美丽了,我美丽的女孩。</t>
+  </si>
+  <si>
+    <t>恒久的等待,只为了你的到来,让我们携手向前…</t>
+  </si>
+  <si>
+    <t>虽然并不完美,不过你还是不错的,那就答应你吧。</t>
+  </si>
+  <si>
+    <t>我,真的可以吗？其实我一直都喜欢你！</t>
+  </si>
+  <si>
+    <t>盯…其实我早就知道了,没想到你这么晚才来,你说我该怎么办？亲爱的。</t>
+  </si>
+  <si>
+    <t>你也是我欣赏的人,今后就请多多关照了。</t>
+  </si>
+  <si>
+    <t>哇,好羞人,不过我真的好高兴,今后希望能和你一起走下去。</t>
+  </si>
+  <si>
+    <t>你是认真的吗？呐,就先相信你吧,如果你欺骗我的话…</t>
+  </si>
+  <si>
+    <t>没想到你会选择我,我也会得到幸福呢。</t>
+  </si>
+  <si>
+    <t>跨种族的爱恋是很困难的,你要做好觉悟哦。</t>
+  </si>
+  <si>
+    <t>亲爱的,你来了,刚才我还在想你呢,嘿嘿。</t>
+  </si>
+  <si>
+    <t>亲..亲爱的,你来这里,有什么事吗？</t>
+  </si>
+  <si>
+    <t>甜心,看到你,我的心情就变好了,如果可以,希望你能多陪我一会…</t>
+  </si>
+  <si>
+    <t>这种枯燥的工作,果然还是需要你的陪伴,今天过来是想干什么呢？</t>
+  </si>
+  <si>
+    <t>吾爱,你如风中的精灵,真想为你献上一首赞美诗..</t>
+  </si>
+  <si>
+    <t>噢,你来了呀,是想我了吗？</t>
+  </si>
+  <si>
+    <t>刚刚我还在想你,没想到你竟然马上就来了,我好幸福…</t>
+  </si>
+  <si>
+    <t>是你啊,亲爱的,见到你真高兴,你是来看我的吗？</t>
+  </si>
+  <si>
+    <t>不知道为什么,在见到你之后,心情变得轻松了。</t>
+  </si>
+  <si>
+    <t>呐呐,以后等我们组成家庭,我每天给你做便当吃好吗？</t>
+  </si>
+  <si>
+    <t>亲爱的,我决定了,以后,我的舞姿只会为你而绽放。</t>
+  </si>
+  <si>
+    <t>自从见到了你,我就中了一种叫爱情的魔法。</t>
+  </si>
+  <si>
+    <t>守护这里是我的职责,那么,守护我的就是你了吗？</t>
+  </si>
+  <si>
+    <t>原来像我这种无名小卒也可以拥有爱情啊,我会珍惜你的。</t>
+  </si>
+  <si>
+    <t>我要更加努力,我会与你相配的。</t>
+  </si>
+  <si>
+    <t>没想到…</t>
+  </si>
+  <si>
+    <t>别以为,我会挽留..</t>
+  </si>
+  <si>
+    <t>哼…</t>
+  </si>
+  <si>
+    <t>请你以后不要来打扰我</t>
+  </si>
+  <si>
+    <t>爱情总以悲剧而告终…</t>
+  </si>
+  <si>
+    <t>这还不值得我愤怒…</t>
+  </si>
+  <si>
+    <t>为什么？是我哪里做的不好吗？</t>
+  </si>
+  <si>
+    <t>你这个渣男…</t>
+  </si>
+  <si>
+    <t>人心总是丑陋的…</t>
+  </si>
+  <si>
+    <t>唉,怎么会这样…</t>
+  </si>
+  <si>
+    <t>你胆子很大啊,竟敢这样玩弄我！</t>
+  </si>
+  <si>
+    <t>我再也不会相信你了！</t>
+  </si>
+  <si>
+    <t>果然,种族是无法跨越的…</t>
+  </si>
+  <si>
+    <t>这里的风景真是美丽啊。</t>
+  </si>
+  <si>
+    <t>真想在这里多呆一会。</t>
+  </si>
+  <si>
+    <t>这里风景也不过如此吗？</t>
+  </si>
+  <si>
+    <t>我们就随便看看吧。</t>
+  </si>
+  <si>
+    <t>让我们享受这美好的时光吧。</t>
+  </si>
+  <si>
+    <t>我的心灵受到抚慰了。</t>
+  </si>
+  <si>
+    <t>我真的有这么好吗？</t>
+  </si>
+  <si>
+    <t>只是山风有些冷啊。</t>
+  </si>
+  <si>
+    <t>呐,我们只是来看风景吗？</t>
+  </si>
+  <si>
+    <t>好啊,大家一起</t>
+  </si>
+  <si>
+    <t>唉,你在做什么？</t>
+  </si>
+  <si>
+    <t>唔,下次可以先告诉我吗？</t>
+  </si>
+  <si>
+    <t>好吧,我们也该迎来一段新生活了。</t>
+  </si>
+  <si>
+    <t>花心可是不好的行为。</t>
+  </si>
+  <si>
+    <t>嗯,我也是。</t>
+  </si>
+  <si>
+    <t>好吧,那么我们就出发吧。</t>
+  </si>
+  <si>
+    <t>今天已经约过了,明天在来吧。</t>
+  </si>
+  <si>
+    <t>好舒服,疲劳都消除了！辛苦你了,亲爱的。</t>
+  </si>
+  <si>
+    <t>今天我已经累了,明天我在为你服务！</t>
+  </si>
+  <si>
+    <t>亲爱的,你已经拿不下了,先把背包腾出一个格子来吧。</t>
+  </si>
+  <si>
+    <t>今天已经没有了,明天我会早点准备好的。</t>
+  </si>
+  <si>
+    <t>今天辛苦了,有什么需要我服务的吗？</t>
+  </si>
+  <si>
+    <t>亲爱的,今天,我的身体有点不舒服。</t>
+  </si>
+  <si>
+    <t>怎么了吗？我去找人来给你看看。</t>
+  </si>
+  <si>
+    <t>恭喜你们了,你们要有小宝宝了。</t>
+  </si>
+  <si>
+    <t>这么说,我..</t>
+  </si>
+  <si>
+    <t>太好了,亲爱的,我们要有孩子了。</t>
+  </si>
+  <si>
+    <t>我先走了,过段时间孩子出生时我在来。</t>
+  </si>
+  <si>
+    <t>小宝宝终于出生了,恭喜你们了。</t>
+  </si>
+  <si>
+    <t>这就是我的孩子！亲爱的,谢谢你！</t>
+  </si>
+  <si>
+    <t>好了,我们该给他取一个名字了！</t>
+  </si>
+  <si>
+    <t>真是个好名字,你们可要照顾好这个小家伙呀。</t>
+  </si>
+  <si>
+    <t>这是我们的责任。</t>
+  </si>
+  <si>
+    <t>多谢你的药,我的身体已经痊愈了,随时来找我组队啊！</t>
+  </si>
+  <si>
+    <t>谢谢</t>
+  </si>
+  <si>
+    <t>我很累了,应该先休息一下才行</t>
+  </si>
+  <si>
+    <t>我没有锄头，没办法锄地</t>
+  </si>
+  <si>
+    <t>这块地已经平整过了，\n不需要再锄地了</t>
+  </si>
+  <si>
+    <t>如果不选择种子，\n是没办法种地的</t>
+  </si>
+  <si>
+    <t>这块地无法种植</t>
+  </si>
+  <si>
+    <t>不使用水壶的话,\n我没办法浇水</t>
+  </si>
+  <si>
+    <t>这块地已经不需要浇水了</t>
+  </si>
+  <si>
+    <t>水壶里没有水了</t>
+  </si>
+  <si>
+    <t>水壶已经满了,\n不需要再装水了</t>
+  </si>
+  <si>
+    <t>嗯，还是先留着为好</t>
+  </si>
+  <si>
+    <t>我的背包没有空间了,\n我应该至少在背包中留一个空位置</t>
+  </si>
+  <si>
+    <t>我累了,还是先休息,明天再出去</t>
+  </si>
+  <si>
+    <t>我缺少建造材料，我得先收集一些才行</t>
+  </si>
+  <si>
+    <t>太好了,这下可以饲养动物了！</t>
+  </si>
+  <si>
+    <t>我没有镰刀，没办法收割</t>
+  </si>
+  <si>
+    <t>我需要先装备斧头</t>
+  </si>
+  <si>
+    <t>我没有鱼竿，没法钓鱼！</t>
+  </si>
+  <si>
+    <t>我需要装备鱼饵，否则不能钓鱼！</t>
+  </si>
+  <si>
+    <t>欢迎光临，有什么需要的吗</t>
+  </si>
+  <si>
+    <t>如果每天都能下雨就好了，这样就不需要为植物浇水了。</t>
+  </si>
+  <si>
+    <t>你知道吗,其实蔬菜里也有很多营养哦。</t>
+  </si>
+  <si>
+    <t>种植是很有学问的,一定要在合适的季节种植作物哦,\n否则作物的生长时间会变的很长。</t>
+  </si>
+  <si>
+    <t>我要好好帮助玛德琳奶奶。</t>
+  </si>
+  <si>
+    <t>你好呀，小家伙，需要我的帮助吗？</t>
+  </si>
+  <si>
+    <t>帕特里克那个老固执在干什么呢？..明明过去那么久了…</t>
+  </si>
+  <si>
+    <t>布莱兹是个好孩子，如果他的父母还在的话…</t>
+  </si>
+  <si>
+    <t>年轻真好呀，要好好享受生活哟..</t>
+  </si>
+  <si>
+    <t>有烦心事的话，来和奶奶说，我会帮助你的。</t>
+  </si>
+  <si>
+    <t>做一个好农夫也不容易呢，要加油哦！</t>
+  </si>
+  <si>
+    <t>你好，有什么事吗？</t>
+  </si>
+  <si>
+    <t>格吉尔总是想着去冒险，我还是希望他能在小镇安稳的生活。</t>
+  </si>
+  <si>
+    <t>平静的生活就是最大的幸福，你觉得的呢？</t>
+  </si>
+  <si>
+    <t>我很喜欢和动物们相处，它们既单纯又可爱。</t>
+  </si>
+  <si>
+    <t>准备干些什么？</t>
+  </si>
+  <si>
+    <t>相比温顺的动物，我更喜欢能和我一起战斗的伙伴。</t>
+  </si>
+  <si>
+    <t>你如果要去冒险的话，一定要带上我呀。</t>
+  </si>
+  <si>
+    <t>有的人天生就是主角，你看我像不像，哈哈。</t>
+  </si>
+  <si>
+    <t>风儿带来了你的讯息，你有什么想要倾诉？</t>
+  </si>
+  <si>
+    <t>人的生命如此短暂，你是否已经准备好接受自己的命运…</t>
+  </si>
+  <si>
+    <t>高山之后是大海，大海之边是高山，不知山海相连何处是尽头…</t>
+  </si>
+  <si>
+    <t>人无法跨过两次同一条河流，那么河里的鱼是否相同…</t>
+  </si>
+  <si>
+    <t>美丽的人啊，偎依在河岸，我只敢远远欣赏不敢靠近，害怕，你那美丽的面庞将我的眼睛灼伤…</t>
+  </si>
+  <si>
+    <t>愿主保佑你，想要祈祷什么？</t>
+  </si>
+  <si>
+    <t>一切存在都源自内心，如果希望世界更好，那么就让自己的内心更纯净吧。</t>
+  </si>
+  <si>
+    <t>现在的年轻人都不知道敬畏上帝了，平时都不来礼拜了。</t>
+  </si>
+  <si>
+    <t>愿主的荣光照耀在你身上。</t>
+  </si>
+  <si>
+    <t>希望每一个远行的人都能平安的归来…</t>
+  </si>
+  <si>
+    <t>命运还是要把握在自己手里，想知道什么？</t>
+  </si>
+  <si>
+    <t>我知道很多，但我不能都告诉你。</t>
+  </si>
+  <si>
+    <t>从远方而来的人啊，你的故乡在何处，你可知你的真名，我在此等候你的倾诉..</t>
+  </si>
+  <si>
+    <t>年轻人，探索精神固然可贵，但不要盲目冒险呐。</t>
+  </si>
+  <si>
+    <t>即使知道了命运，依然能够笑着面对的人才是真正的勇士。</t>
+  </si>
+  <si>
+    <t>你好呀，想要点什么吗？</t>
+  </si>
+  <si>
+    <t>尽管每天都很忙，但我们都很快乐。</t>
+  </si>
+  <si>
+    <t>美食和美景都不能错过。</t>
+  </si>
+  <si>
+    <t>你笑起来真好看，多笑笑嘛。</t>
+  </si>
+  <si>
+    <t>平时多出来和我们一起玩吧，不要老呆在家里嘛。</t>
+  </si>
+  <si>
+    <t>你好，今天也很精神呀，需要我做什么吗？</t>
+  </si>
+  <si>
+    <t>班尼迪克先生是个好人。</t>
+  </si>
+  <si>
+    <t>一切安好，也希望你也能开开心心。</t>
+  </si>
+  <si>
+    <t>有什么可以为你服务的吗？</t>
+  </si>
+  <si>
+    <t>今天也是平静而美好的。</t>
+  </si>
+  <si>
+    <t>看着环境变得干净卫生，我会很舒心。</t>
+  </si>
+  <si>
+    <t>是你啊，有事的话，请尽管吩咐。</t>
+  </si>
+  <si>
+    <t>如果能发挥我的特长的话就太好了。</t>
+  </si>
+  <si>
+    <t>这个小镇能如此安宁是很多人付出的结果。</t>
+  </si>
+  <si>
+    <t>守护家人是我的职责。</t>
+  </si>
+  <si>
+    <t>其实回到这个养育我的小镇，我很开心。</t>
+  </si>
+  <si>
+    <t>哟，找我有事？</t>
+  </si>
+  <si>
+    <t>真是无聊，这样的日子何时才能结束。</t>
+  </si>
+  <si>
+    <t>看着别人四处旅行，我却只能在这里，真羡慕啊。</t>
+  </si>
+  <si>
+    <t>如果以后你要出去旅行的话，希望我们可以同行。</t>
+  </si>
+  <si>
+    <t>我已经准备了很久行囊，就是没有机会出发。</t>
+  </si>
+  <si>
+    <t>你是来找我的吗？不知道能为你做些什么？</t>
+  </si>
+  <si>
+    <t>我有一个感觉，这个小镇是我的归宿。</t>
+  </si>
+  <si>
+    <t>繁华终归会褪去，回归平淡才是真正的人生。</t>
+  </si>
+  <si>
+    <t>虽然我的魔力还不够，但我会努力的，你有什么需要我的？</t>
+  </si>
+  <si>
+    <t>究竟怎样才能和师父一样优秀呢？这真让我困扰。</t>
+  </si>
+  <si>
+    <t>我的梦想是成为一个大魔导师。</t>
+  </si>
+  <si>
+    <t>是遇到什么疑难了吗？</t>
+  </si>
+  <si>
+    <t>别看我单身一人，年轻时候的我也是很受欢迎的。</t>
+  </si>
+  <si>
+    <t>看见你，就想让我想到了年轻时候的我，真怀念呐。</t>
+  </si>
+  <si>
+    <t>我不会拒绝对弱者的怜悯，所以你有什么事？</t>
+  </si>
+  <si>
+    <t>这个小镇虽然不是很繁华，但我却很喜欢。</t>
+  </si>
+  <si>
+    <t>你想来找我学习贵族礼仪吗?</t>
+  </si>
+  <si>
+    <t>你愿意来找我，我心里还是有一点高兴的。</t>
+  </si>
+  <si>
+    <t>可不要误会，这只是基本的贵族礼仪。</t>
+  </si>
+  <si>
+    <t>你想要了解魔法的力量吗？</t>
+  </si>
+  <si>
+    <t>魔法的力量远超你的想象，</t>
+  </si>
+  <si>
+    <t>嗨，有啥事？</t>
+  </si>
+  <si>
+    <t>要想获得丰厚的渔获，必须要打理好网具。</t>
+  </si>
+  <si>
+    <t>这个小镇靠近大海，可以时常吃到一些海鲜菜肴。</t>
+  </si>
+  <si>
+    <t>据说大海的深处有美人鱼，不知道是不是真的。</t>
+  </si>
+  <si>
+    <t>如果你有时间的话，学习一下钓鱼吧，你会很有收获。</t>
+  </si>
+  <si>
+    <t>你找我是有什么事？</t>
+  </si>
+  <si>
+    <t>这个镇子虽小，却拥有完善的海港，常有舰船航行往来于各大陆之间。</t>
+  </si>
+  <si>
+    <t>经历了长时间的海上漂泊，我需要在岸上好好休息一下。</t>
+  </si>
+  <si>
+    <t>大海里有很多财富，也有很多风险。</t>
+  </si>
+  <si>
+    <t>你如果想去海那边，可以乘坐我的船。</t>
+  </si>
+  <si>
+    <t>找我吗？我也可以为你做事吗？</t>
+  </si>
+  <si>
+    <t>乘船出海游遍世界一直是我的愿望。</t>
+  </si>
+  <si>
+    <t>虽然海上的生活令人神往，但在这个小镇也还不错。</t>
+  </si>
+  <si>
+    <t>大家都很努力啊，我也不能懈怠。</t>
+  </si>
+  <si>
+    <t>如果我也有自己的船就好了。</t>
+  </si>
+  <si>
+    <t>静待你的委托</t>
+  </si>
+  <si>
+    <t>别人的秘密，何必要探究到底呢，只要不危害大家就好了。</t>
+  </si>
+  <si>
+    <t>你好，你想知道什么吗？</t>
+  </si>
+  <si>
+    <t>如果四季可以同时存在，会发生什么呢…</t>
+  </si>
+  <si>
+    <t>需要我的帮忙吗？</t>
+  </si>
+  <si>
+    <t>虽然我对神依然很崇敬，但我还是想干些其他的事情。</t>
+  </si>
+  <si>
+    <t>在战斗中祈求上帝是没有用了，我们只能依靠自己。</t>
+  </si>
+  <si>
+    <t>不知道上帝能不能听到我的心声，让我早日得偿所愿。</t>
+  </si>
+  <si>
+    <t>无论信不信上帝，都要坚守爱与和平。</t>
+  </si>
+  <si>
+    <t>我可以为你做些什么？</t>
+  </si>
+  <si>
+    <t>其实一个人巡逻也挺无聊的,如果有人来和我聊聊的话,我会很高兴。</t>
+  </si>
+  <si>
+    <t>很高兴能为你服务。</t>
+  </si>
+  <si>
+    <t>守护小姐是我的职责。</t>
+  </si>
+  <si>
+    <t>在这个镇子里，我经常会想起关于老主人的事。</t>
+  </si>
+  <si>
+    <t>回想过去，好像刚刚发生在昨天，那时小姐还是个孩子…</t>
+  </si>
+  <si>
+    <t>如果有更多的人陪伴小姐，小姐应该会更开心吧</t>
+  </si>
+  <si>
+    <t>如果有什么事情，我会尽力而为。</t>
+  </si>
+  <si>
+    <t>一个料理如果缺少调味料，就会寡淡无味，不要忘记购买呀。</t>
+  </si>
+  <si>
+    <t>好的装备可以大大促进劳动效率，我需要做什么？</t>
+  </si>
+  <si>
+    <t>我一定要把布拉德利培养成一个优秀的人,这就是我生活的意义。</t>
+  </si>
+  <si>
+    <t>布拉德利再长大一些的话，我会让他自己选择自己的道路。</t>
+  </si>
+  <si>
+    <t>你好，需要什么服务吗？</t>
+  </si>
+  <si>
+    <t>姐姐应该有更广阔的前景的，现在却被困住这个小镇…</t>
+  </si>
+  <si>
+    <t>如果我能更强大一些的话，姐姐就可以去追求自己的梦想了。</t>
+  </si>
+  <si>
+    <t>你可以帮助我，鼓励我一直坚强吗？</t>
+  </si>
+  <si>
+    <t>如果你愿意的话，可以随时来找我和我的姐姐。</t>
+  </si>
+  <si>
+    <t>有什么搞不定的事情？</t>
+  </si>
+  <si>
+    <t>注意,不要走得太远,外面可是有很多怪物。</t>
+  </si>
+  <si>
+    <t>听说你在征讨小镇周边的怪物，做的不错。</t>
+  </si>
+  <si>
+    <t>招待不周了，有什么事情吗？</t>
+  </si>
+  <si>
+    <t>有妹妹和妈妈陪着我，我觉得很幸福。</t>
+  </si>
+  <si>
+    <t>如果爸爸还在的话…</t>
+  </si>
+  <si>
+    <t>我要努力支撑我的家，可以为我加油吗？</t>
+  </si>
+  <si>
+    <t>可有什么事情需要我为你而做的？</t>
+  </si>
+  <si>
+    <t>纺织可是化腐朽为神奇的技术。</t>
+  </si>
+  <si>
+    <t>如果你想学习纺织技术的话，我可以教你。</t>
+  </si>
+  <si>
+    <t>我有时也会为缺少传承而烦恼呢。</t>
+  </si>
+  <si>
+    <t>相比能赚到钱，我更希望有人可以将我的技术传承下去。</t>
+  </si>
+  <si>
+    <t>我拥有的比你知道的还多，你有什么需要的吗？</t>
+  </si>
+  <si>
+    <t>固守成见是不行的，只有变革才能带来新的机遇。</t>
+  </si>
+  <si>
+    <t>放心吧，你的外公只是去了他想去的地方。</t>
+  </si>
+  <si>
+    <t>好好在这里生活吧，你的外公也会很欣慰的。</t>
+  </si>
+  <si>
+    <t>没有买到想要的东西，我有点不开心。</t>
+  </si>
+  <si>
+    <t>你的队伍已经满员了，还是下次再说吧。</t>
+  </si>
+  <si>
+    <t>我的身体还没有恢复，改天吧。</t>
+  </si>
+  <si>
+    <t>我先回家修养身体了，你自己保重。</t>
+  </si>
+  <si>
+    <t>造物主还没来得及创造这种感情，请耐心等待吧。</t>
+  </si>
+  <si>
+    <t>抱歉，我们的关系还没亲密到现在一起组队的程度。</t>
+  </si>
+  <si>
+    <t>现在还不行哦，想和我一起组队，你还得加倍努力呀。</t>
+  </si>
+  <si>
+    <t>我还有事情要做，不能和你组队。</t>
+  </si>
+  <si>
+    <t>如果我们更亲密一些的话，我会同意的。</t>
+  </si>
+  <si>
+    <t>对不起，我现在不能和你一起外出。</t>
+  </si>
+  <si>
+    <t>我还需要磨练意志，如果你能感化我的话也许可行。</t>
+  </si>
+  <si>
+    <t>我现在还不能完全信任你。</t>
+  </si>
+  <si>
+    <t>你可以让我安心将后背给你吗？做不到吧。</t>
+  </si>
+  <si>
+    <t>作为一个好船长，必须懂得挑选自己的团队，你现在还不行。</t>
+  </si>
+  <si>
+    <t>对不起，我不是很习惯和不熟悉的人一起行动。</t>
+  </si>
+  <si>
+    <t>抱歉了，我的时间很宝贵，你得先取得我的信任才行。</t>
+  </si>
+  <si>
+    <t>我需要照顾大小姐，除非我们更加亲密。</t>
+  </si>
+  <si>
+    <t>很高兴你来邀请我，但是请允许我拒绝。</t>
+  </si>
+  <si>
+    <t>我的职责很可是很重要的，除非你能证明你更重要。</t>
+  </si>
+  <si>
+    <t>我们的关系还不够啊，我还是不能同意。</t>
+  </si>
+  <si>
+    <t>啊，这个..还是谢谢你啦</t>
+  </si>
+  <si>
+    <t>如果是..</t>
+  </si>
+  <si>
+    <t>我不太需要这个..</t>
+  </si>
+  <si>
+    <t>唔,下次可以换其他的吗</t>
+  </si>
+  <si>
+    <t>哇,好棒的礼物,谢谢你！</t>
+  </si>
+  <si>
+    <t>是送我的吗？好高兴！</t>
+  </si>
+  <si>
+    <t>正是我需要的呢，谢谢！</t>
+  </si>
+  <si>
+    <t>谢谢你的礼物</t>
+  </si>
+  <si>
+    <t>叽叽..叽叽..</t>
+  </si>
+  <si>
+    <t>咯咯..咯咯..</t>
+  </si>
+  <si>
+    <t>呷呷..呷呷..</t>
+  </si>
+  <si>
+    <t>嘎嘎..嘎嘎..</t>
+  </si>
+  <si>
+    <t>噗呼..噗呼..</t>
+  </si>
+  <si>
+    <t>咩咩..咩咩..</t>
+  </si>
+  <si>
+    <t>哼哼..哼哼..</t>
+  </si>
+  <si>
+    <t>哞～哞～</t>
+  </si>
+  <si>
+    <t>嘶嘶..嘶嘶..</t>
+  </si>
+  <si>
+    <t>吱吱..吱吱..</t>
+  </si>
+  <si>
+    <t>咕噜..咕噜..</t>
+  </si>
+  <si>
+    <t>呦呦..呦呦..</t>
+  </si>
+  <si>
+    <t>呜～呜～</t>
+  </si>
+  <si>
+    <t>咳咳..咳咳..</t>
+  </si>
+  <si>
+    <t>这里就是农场，以后就归你管理了,现在准备种植吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择目标</t>
+  </si>
+  <si>
+    <t>背包空间不足，鱼已放生</t>
+  </si>
+  <si>
+    <t>本次垂钓一无所获</t>
+  </si>
+  <si>
+    <t>牧场</t>
+  </si>
+  <si>
+    <t>提升牧场等级</t>
+  </si>
+  <si>
+    <t>建造一座牧场</t>
+  </si>
+  <si>
+    <t>装备</t>
+  </si>
+  <si>
+    <t>前进</t>
+  </si>
+  <si>
+    <t>停止</t>
+  </si>
+  <si>
+    <t>取消</t>
+  </si>
+  <si>
+    <t>布置</t>
+  </si>
+  <si>
+    <t>所有地方</t>
+  </si>
+  <si>
+    <t>出售</t>
+  </si>
+  <si>
+    <t>使用</t>
+  </si>
+  <si>
+    <t>是否确定中止生产,消耗的物体将消失？</t>
+  </si>
+  <si>
+    <t>制作</t>
+  </si>
+  <si>
+    <t>中止</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>取出</t>
+  </si>
+  <si>
+    <t>制作完成！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等待制作</t>
+  </si>
+  <si>
+    <t>移除</t>
+  </si>
+  <si>
+    <t>放入</t>
+  </si>
+  <si>
+    <t>选择</t>
+  </si>
+  <si>
+    <t>毁坏的牧场</t>
+  </si>
+  <si>
+    <t>是否确认撤出战斗？</t>
+  </si>
+  <si>
+    <t>之月</t>
+  </si>
+  <si>
+    <t>我的奖杯</t>
+  </si>
+  <si>
+    <t>+ 破碎的无名苹果 +</t>
+  </si>
+  <si>
+    <t>购买</t>
+  </si>
+  <si>
+    <t>美味的红色果实，也许你想尝尝，不过小心它 的</t>
+  </si>
+  <si>
+    <t>探险成功</t>
+  </si>
+  <si>
+    <t>探险失败</t>
+  </si>
+  <si>
+    <t>探险获得道具：</t>
+  </si>
+  <si>
+    <t>+ 可爱的嗡 +</t>
+  </si>
+  <si>
+    <t>筛选</t>
+  </si>
+  <si>
+    <t>获得</t>
+  </si>
+  <si>
+    <t>鱼之书</t>
+  </si>
+  <si>
+    <t>植物之书</t>
+  </si>
+  <si>
+    <t>装备之书</t>
+  </si>
+  <si>
+    <t>动物之书</t>
+  </si>
+  <si>
+    <t>怪物之书</t>
+  </si>
+  <si>
+    <t>配方之书</t>
+  </si>
+  <si>
+    <t>许可清单</t>
+  </si>
+  <si>
+    <t>伙伴</t>
+  </si>
+  <si>
+    <t>1991年 春之月</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>敏捷</t>
+  </si>
+  <si>
+    <t>幸运</t>
+  </si>
+  <si>
+    <t>火焰弯刀</t>
+  </si>
+  <si>
+    <t>帽子</t>
+  </si>
+  <si>
+    <t>衣服</t>
+  </si>
+  <si>
+    <t>鞋子</t>
+  </si>
+  <si>
+    <t>拜访</t>
+  </si>
+  <si>
+    <t>修养中</t>
+  </si>
+  <si>
+    <t>好感度</t>
+  </si>
+  <si>
+    <t>商店街有一家植物店,那里拥有各种植物种子,去看看吧,买完了,记得直接到农场,我在那里等你。</t>
+  </si>
+  <si>
+    <t>名字:</t>
+  </si>
+  <si>
+    <t>阿历克斯</t>
+  </si>
+  <si>
+    <t>夏之月1日</t>
+  </si>
+  <si>
+    <t>生日:</t>
+  </si>
+  <si>
+    <t>养鸡场</t>
+  </si>
+  <si>
+    <t>是否消耗</t>
+  </si>
+  <si>
+    <t>当前拥有</t>
+  </si>
+  <si>
+    <t>建造一座牧场？</t>
+  </si>
+  <si>
+    <t>艾克但是</t>
+  </si>
+  <si>
+    <t>剑刃风暴</t>
+  </si>
+  <si>
+    <t>撤退</t>
+  </si>
+  <si>
+    <t>道具</t>
+  </si>
+  <si>
+    <t>自动</t>
+  </si>
+  <si>
+    <t>探索度:</t>
+  </si>
+  <si>
+    <t>鱼</t>
+  </si>
+  <si>
+    <t>记录:</t>
+  </si>
+  <si>
+    <t>最大记录:</t>
+  </si>
+  <si>
+    <t>栖息地：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出现季节： </t>
+  </si>
+  <si>
+    <t>炼金</t>
+  </si>
+  <si>
+    <t>可获得:</t>
+  </si>
+  <si>
+    <t>提炼</t>
+  </si>
+  <si>
+    <t>需要:</t>
+  </si>
+  <si>
+    <t>[材料]</t>
+  </si>
+  <si>
+    <t>获得安康鱼一条</t>
+  </si>
+  <si>
+    <t>查看</t>
+  </si>
+  <si>
+    <t>队伍</t>
+  </si>
+  <si>
+    <t>锻造台</t>
+  </si>
+  <si>
+    <t>配方</t>
+  </si>
+  <si>
+    <t>+ 原料 +</t>
+  </si>
+  <si>
+    <t>+ 产出 +</t>
+  </si>
+  <si>
+    <t>消耗RP:</t>
+  </si>
+  <si>
+    <t>自动选择</t>
+  </si>
+  <si>
+    <t>移动</t>
+  </si>
+  <si>
+    <t>书桌</t>
+  </si>
+  <si>
+    <t>提升容量</t>
+  </si>
+  <si>
+    <t>状态:</t>
+  </si>
+  <si>
+    <t>好感:</t>
+  </si>
+  <si>
+    <t>详情</t>
+  </si>
+  <si>
+    <t>检查检查</t>
+  </si>
+  <si>
+    <t>队伍等待</t>
+  </si>
+  <si>
+    <t>我的牧场</t>
+  </si>
+  <si>
+    <t>初级畜牧棚</t>
+  </si>
+  <si>
+    <t>动物:</t>
+  </si>
+  <si>
+    <t>产出:</t>
+  </si>
+  <si>
+    <t>食物:</t>
+  </si>
+  <si>
+    <t>水:</t>
+  </si>
+  <si>
+    <t>经商许可</t>
+  </si>
+  <si>
+    <t>条件</t>
+  </si>
+  <si>
+    <t>奖励</t>
+  </si>
+  <si>
+    <t>已布置</t>
+  </si>
+  <si>
+    <t>未布置</t>
+  </si>
+  <si>
+    <t>双人新床</t>
+  </si>
+  <si>
+    <t>释放</t>
+  </si>
+  <si>
+    <t>我的家具</t>
+  </si>
+  <si>
+    <t>春</t>
+  </si>
+  <si>
+    <t>星期一</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我宝宝户籍科不得 </t>
+  </si>
+  <si>
+    <t>保存</t>
+  </si>
+  <si>
+    <t>复制</t>
+  </si>
+  <si>
+    <t>生日</t>
+  </si>
+  <si>
+    <t>日</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>选择存档</t>
+  </si>
+  <si>
+    <t>手动存档</t>
+  </si>
+  <si>
+    <t>自动存档</t>
+  </si>
+  <si>
+    <t>注:进入游戏后随时会自动存档，在选择手动存档前，建议首先复制自动存档备份。</t>
+  </si>
+  <si>
+    <t>开始</t>
+  </si>
+  <si>
+    <t>删除</t>
+  </si>
+  <si>
+    <t>新起点！</t>
+  </si>
+  <si>
+    <t>读取存档</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>+ 主音量 +</t>
+  </si>
+  <si>
+    <t>+ 音乐 +</t>
+  </si>
+  <si>
+    <t>+ 音效 +</t>
+  </si>
+  <si>
+    <t>+ 效果 +</t>
+  </si>
+  <si>
+    <t>流畅</t>
+  </si>
+  <si>
+    <t>平衡</t>
+  </si>
+  <si>
+    <t>完美</t>
+  </si>
+  <si>
+    <t>卸载</t>
+  </si>
+  <si>
+    <t>亲爱的{0}:</t>
+  </si>
+  <si>
+    <t>最近，我身体感到越来越疲倦，我的时间不多了，我不想成为一个死在病榻上的糟老头，为此，在死神来找我之前，我决定踏上周游世界的旅程。</t>
+  </si>
+  <si>
+    <t>在这个世界上，我唯一关心的{0}。在我的小镇上有我的家，我不想让它荒废，希望你能继承。小镇上的居民都是十分善良的人，如果有什么困难他们都会帮助你的。</t>
+  </si>
+  <si>
+    <t>好了，差不多我也该出发了，祝福我吧。</t>
+  </si>
+  <si>
+    <t>你的外公</t>
+  </si>
+  <si>
+    <t>破碎的苹果苏北</t>
+  </si>
+  <si>
+    <t>上架数量:</t>
+  </si>
+  <si>
+    <t>更换</t>
+  </si>
+  <si>
+    <t>下架</t>
+  </si>
+  <si>
+    <t>聊聊</t>
+  </si>
+  <si>
+    <t>离队</t>
+  </si>
+  <si>
+    <t>今日天气</t>
+  </si>
+  <si>
+    <t>明日天气</t>
+  </si>
+  <si>
+    <t>迷之废墟</t>
+  </si>
+  <si>
+    <t>探索</t>
+  </si>
+  <si>
+    <t>特产</t>
+  </si>
+  <si>
+    <t>新旅途</t>
+  </si>
+  <si>
+    <t>继续旅途</t>
+  </si>
+  <si>
+    <t>战斗时</t>
+  </si>
+  <si>
+    <t>回合</t>
+  </si>
+  <si>
+    <t>最大体力</t>
+  </si>
+  <si>
+    <t>最大生命</t>
+  </si>
+  <si>
+    <t>最大法力</t>
+  </si>
+  <si>
+    <t>自定义值</t>
+  </si>
+  <si>
+    <t>体力</t>
+  </si>
+  <si>
+    <t>生命</t>
+  </si>
+  <si>
+    <t>法力</t>
+  </si>
+  <si>
+    <t>饱食</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>火</t>
+  </si>
+  <si>
+    <t>冰</t>
+  </si>
+  <si>
+    <t>风</t>
+  </si>
+  <si>
+    <t>土</t>
+  </si>
+  <si>
+    <t>属性改变</t>
+  </si>
+  <si>
+    <t>伤害</t>
+  </si>
+  <si>
+    <t>回复</t>
+  </si>
+  <si>
+    <t>生活设施</t>
+  </si>
+  <si>
+    <t>生产设施</t>
+  </si>
+  <si>
+    <t>生产设施</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>复活</t>
+  </si>
+  <si>
+    <t>待机</t>
+  </si>
+  <si>
+    <t>使用道具</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>待平整</t>
+  </si>
+  <si>
+    <t>战斗</t>
+  </si>
+  <si>
+    <t>平常</t>
+  </si>
+  <si>
+    <t>闲置</t>
+  </si>
+  <si>
+    <t>比赛</t>
+  </si>
+  <si>
+    <t>售卖</t>
+  </si>
+  <si>
+    <t>纪念</t>
+  </si>
+  <si>
+    <t>狂欢</t>
+  </si>
+  <si>
+    <t>铸造</t>
+  </si>
+  <si>
+    <t>装饰</t>
+  </si>
+  <si>
+    <t>收集物</t>
+  </si>
+  <si>
+    <t>工具</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>红晶</t>
+  </si>
+  <si>
+    <t>对话</t>
+  </si>
+  <si>
+    <t>饥饿</t>
+  </si>
+  <si>
+    <t>高兴</t>
+  </si>
+  <si>
+    <t>悲伤</t>
+  </si>
+  <si>
+    <t>死亡</t>
+  </si>
+  <si>
+    <t>衰老</t>
+  </si>
+  <si>
+    <t>幼年</t>
+  </si>
+  <si>
+    <t>成年</t>
+  </si>
+  <si>
+    <t>老年</t>
+  </si>
+  <si>
+    <t>鲜活</t>
+  </si>
+  <si>
+    <t>非鲜活</t>
+  </si>
+  <si>
+    <t>敌方</t>
+  </si>
+  <si>
+    <t>我方</t>
+  </si>
+  <si>
+    <t>自身</t>
+  </si>
+  <si>
+    <t>准备</t>
+  </si>
+  <si>
+    <t>行动</t>
+  </si>
+  <si>
+    <t>濒死</t>
+  </si>
+  <si>
+    <t>已平整</t>
+  </si>
+  <si>
+    <t>城镇</t>
+  </si>
+  <si>
+    <t>损毁</t>
+  </si>
+  <si>
+    <t>工作</t>
+  </si>
+  <si>
+    <t>睡眠</t>
+  </si>
+  <si>
+    <t>缝纫</t>
+  </si>
+  <si>
+    <t>书写</t>
+  </si>
+  <si>
+    <t>劈砍</t>
+  </si>
+  <si>
+    <t>纺线</t>
+  </si>
+  <si>
+    <t>织布</t>
+  </si>
+  <si>
+    <t>制革</t>
+  </si>
+  <si>
+    <t>粉磨</t>
+  </si>
+  <si>
+    <t>徒手</t>
+  </si>
+  <si>
+    <t>蒸煮</t>
+  </si>
+  <si>
+    <t>烘烤</t>
+  </si>
+  <si>
+    <t>酿造</t>
+  </si>
+  <si>
+    <t>搅拌</t>
+  </si>
+  <si>
+    <t>床</t>
+  </si>
+  <si>
+    <t>箱子</t>
+  </si>
+  <si>
+    <t>柜台</t>
+  </si>
+  <si>
+    <t>生产</t>
+  </si>
+  <si>
+    <t>干旱</t>
+  </si>
+  <si>
+    <t>枯死</t>
+  </si>
+  <si>
+    <t>成熟</t>
+  </si>
+  <si>
+    <t>礼物</t>
+  </si>
+  <si>
+    <t>邀请</t>
+  </si>
+  <si>
+    <t>夏</t>
+  </si>
+  <si>
+    <t>秋</t>
+  </si>
+  <si>
+    <t>冬</t>
+  </si>
+  <si>
+    <t>钻石</t>
+  </si>
+  <si>
+    <t>货币</t>
   </si>
 </sst>
 </file>
@@ -3934,7 +6056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1554"/>
+  <dimension ref="A1:D1845"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="56.125" style="1" customWidth="1"/>
@@ -9319,1481 +11441,3763 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="1073" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1073" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1073" s="1" t="s">
         <v>1077</v>
       </c>
     </row>
-    <row r="1074" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1074" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1074" s="1" t="s">
         <v>1078</v>
       </c>
     </row>
-    <row r="1075" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1075" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1075" s="1" t="s">
         <v>1079</v>
       </c>
     </row>
-    <row r="1076" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1076" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1076" s="1" t="s">
         <v>1080</v>
       </c>
     </row>
-    <row r="1077" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1077" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1077" s="7" t="s">
         <v>1081</v>
       </c>
     </row>
-    <row r="1078" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1078" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1078" s="7" t="s">
         <v>1082</v>
       </c>
     </row>
-    <row r="1079" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1079" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1079" s="7" t="s">
         <v>1083</v>
       </c>
     </row>
-    <row r="1080" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1080" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1080" s="7" t="s">
         <v>1084</v>
       </c>
     </row>
-    <row r="1081" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1081" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1081" s="7" t="s">
         <v>1085</v>
       </c>
     </row>
-    <row r="1082" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1082" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1082" s="7" t="s">
         <v>1086</v>
       </c>
     </row>
-    <row r="1083" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1083" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1083" s="7" t="s">
         <v>1087</v>
       </c>
     </row>
-    <row r="1084" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1084" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1084" t="s">
         <v>1088</v>
       </c>
     </row>
-    <row r="1085" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1085" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1085" t="s">
         <v>1089</v>
       </c>
     </row>
-    <row r="1086" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1086" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1086" t="s">
         <v>1090</v>
       </c>
     </row>
-    <row r="1087" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1087" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1087" t="s">
         <v>1091</v>
       </c>
     </row>
-    <row r="1088" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1088"/>
-    </row>
-    <row r="1089" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1089"/>
-    </row>
-    <row r="1090" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1090"/>
-    </row>
-    <row r="1091" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1091"/>
-    </row>
-    <row r="1092" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1092"/>
-    </row>
-    <row r="1093" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1093"/>
-    </row>
-    <row r="1094" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1094"/>
-    </row>
-    <row r="1095" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1095"/>
-    </row>
-    <row r="1096" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1096"/>
-    </row>
-    <row r="1097" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1097"/>
-    </row>
-    <row r="1098" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1098"/>
-    </row>
-    <row r="1099" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1099"/>
-    </row>
-    <row r="1100" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1100"/>
-    </row>
-    <row r="1101" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1101"/>
-    </row>
-    <row r="1102" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1102"/>
-    </row>
-    <row r="1103" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1103"/>
-    </row>
-    <row r="1104" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1104"/>
+    <row r="1088" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1088" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B1088"/>
+    </row>
+    <row r="1089" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1089" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B1089"/>
+    </row>
+    <row r="1090" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1090" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B1090"/>
+    </row>
+    <row r="1091" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1091" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1092" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1093" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1094" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1095" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1096" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1097" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1098" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1099" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1100" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1101" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1102" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1103" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1104" t="s">
+        <v>1108</v>
+      </c>
     </row>
     <row r="1105" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1105"/>
+      <c r="A1105" t="s">
+        <v>1109</v>
+      </c>
     </row>
     <row r="1106" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1106"/>
+      <c r="A1106" t="s">
+        <v>1110</v>
+      </c>
     </row>
     <row r="1107" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1107"/>
+      <c r="A1107" t="s">
+        <v>1111</v>
+      </c>
     </row>
     <row r="1108" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1108"/>
+      <c r="A1108" t="s">
+        <v>1112</v>
+      </c>
     </row>
     <row r="1109" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1109"/>
+      <c r="A1109" t="s">
+        <v>1113</v>
+      </c>
     </row>
     <row r="1110" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1110"/>
+      <c r="A1110" t="s">
+        <v>1114</v>
+      </c>
     </row>
     <row r="1111" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1111"/>
+      <c r="A1111" t="s">
+        <v>1115</v>
+      </c>
     </row>
     <row r="1112" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1112"/>
+      <c r="A1112" t="s">
+        <v>1116</v>
+      </c>
     </row>
     <row r="1113" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1113"/>
+      <c r="A1113" t="s">
+        <v>1117</v>
+      </c>
     </row>
     <row r="1114" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1114"/>
+      <c r="A1114" t="s">
+        <v>1118</v>
+      </c>
     </row>
     <row r="1115" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1115"/>
+      <c r="A1115" t="s">
+        <v>1119</v>
+      </c>
     </row>
     <row r="1116" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1116"/>
+      <c r="A1116" t="s">
+        <v>1120</v>
+      </c>
     </row>
     <row r="1117" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1117"/>
+      <c r="A1117" t="s">
+        <v>1121</v>
+      </c>
     </row>
     <row r="1118" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1118"/>
+      <c r="A1118" t="s">
+        <v>1122</v>
+      </c>
     </row>
     <row r="1119" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1119"/>
+      <c r="A1119" t="s">
+        <v>1123</v>
+      </c>
     </row>
     <row r="1120" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1120"/>
+      <c r="A1120" t="s">
+        <v>1124</v>
+      </c>
     </row>
     <row r="1121" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1121"/>
+      <c r="A1121" t="s">
+        <v>1125</v>
+      </c>
     </row>
     <row r="1122" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1122"/>
+      <c r="A1122" t="s">
+        <v>1126</v>
+      </c>
     </row>
     <row r="1123" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1123"/>
+      <c r="A1123" t="s">
+        <v>1127</v>
+      </c>
     </row>
     <row r="1124" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1124"/>
+      <c r="A1124" t="s">
+        <v>1128</v>
+      </c>
     </row>
     <row r="1125" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1125"/>
+      <c r="A1125" t="s">
+        <v>1129</v>
+      </c>
     </row>
     <row r="1126" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1126"/>
+      <c r="A1126" t="s">
+        <v>1130</v>
+      </c>
     </row>
     <row r="1127" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1127"/>
+      <c r="A1127" t="s">
+        <v>1131</v>
+      </c>
     </row>
     <row r="1128" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1128"/>
+      <c r="A1128" t="s">
+        <v>1132</v>
+      </c>
     </row>
     <row r="1129" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1129"/>
+      <c r="A1129" t="s">
+        <v>1133</v>
+      </c>
     </row>
     <row r="1130" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1130"/>
+      <c r="A1130" t="s">
+        <v>1134</v>
+      </c>
     </row>
     <row r="1131" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1131"/>
+      <c r="A1131" t="s">
+        <v>1135</v>
+      </c>
     </row>
     <row r="1132" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1132"/>
+      <c r="A1132" t="s">
+        <v>1136</v>
+      </c>
     </row>
     <row r="1133" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1133"/>
+      <c r="A1133" t="s">
+        <v>1137</v>
+      </c>
     </row>
     <row r="1134" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1134"/>
+      <c r="A1134" t="s">
+        <v>1138</v>
+      </c>
     </row>
     <row r="1135" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1135"/>
+      <c r="A1135" t="s">
+        <v>1139</v>
+      </c>
     </row>
     <row r="1136" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1136"/>
+      <c r="A1136" t="s">
+        <v>1140</v>
+      </c>
     </row>
     <row r="1137" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1137"/>
+      <c r="A1137" t="s">
+        <v>1141</v>
+      </c>
     </row>
     <row r="1138" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1138"/>
+      <c r="A1138" t="s">
+        <v>1142</v>
+      </c>
     </row>
     <row r="1139" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1139"/>
+      <c r="A1139" t="s">
+        <v>1143</v>
+      </c>
     </row>
     <row r="1140" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1140"/>
+      <c r="A1140" t="s">
+        <v>1144</v>
+      </c>
     </row>
     <row r="1141" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1141"/>
+      <c r="A1141" t="s">
+        <v>1145</v>
+      </c>
     </row>
     <row r="1142" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1142"/>
+      <c r="A1142" t="s">
+        <v>1146</v>
+      </c>
     </row>
     <row r="1143" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1143"/>
+      <c r="A1143" t="s">
+        <v>1147</v>
+      </c>
     </row>
     <row r="1144" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1144"/>
+      <c r="A1144" t="s">
+        <v>1148</v>
+      </c>
     </row>
     <row r="1145" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1145"/>
+      <c r="A1145" t="s">
+        <v>1149</v>
+      </c>
     </row>
     <row r="1146" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1146"/>
+      <c r="A1146" t="s">
+        <v>1150</v>
+      </c>
     </row>
     <row r="1147" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1147"/>
+      <c r="A1147" t="s">
+        <v>1151</v>
+      </c>
     </row>
     <row r="1148" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1148"/>
+      <c r="A1148" t="s">
+        <v>1152</v>
+      </c>
     </row>
     <row r="1149" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1149"/>
+      <c r="A1149" t="s">
+        <v>1153</v>
+      </c>
     </row>
     <row r="1150" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1150"/>
+      <c r="A1150" t="s">
+        <v>1154</v>
+      </c>
     </row>
     <row r="1151" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1151"/>
+      <c r="A1151" t="s">
+        <v>1155</v>
+      </c>
     </row>
     <row r="1152" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1152"/>
+      <c r="A1152" t="s">
+        <v>1156</v>
+      </c>
     </row>
     <row r="1153" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1153"/>
+      <c r="A1153" t="s">
+        <v>1157</v>
+      </c>
     </row>
     <row r="1154" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1154"/>
+      <c r="A1154" t="s">
+        <v>1158</v>
+      </c>
     </row>
     <row r="1155" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1155"/>
+      <c r="A1155" t="s">
+        <v>1159</v>
+      </c>
     </row>
     <row r="1156" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1156"/>
+      <c r="A1156" t="s">
+        <v>1160</v>
+      </c>
     </row>
     <row r="1157" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1157"/>
+      <c r="A1157" t="s">
+        <v>1161</v>
+      </c>
     </row>
     <row r="1158" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1158"/>
+      <c r="A1158" t="s">
+        <v>1162</v>
+      </c>
     </row>
     <row r="1159" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1159"/>
+      <c r="A1159" t="s">
+        <v>1163</v>
+      </c>
     </row>
     <row r="1160" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1160"/>
+      <c r="A1160" t="s">
+        <v>1164</v>
+      </c>
     </row>
     <row r="1161" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1161"/>
+      <c r="A1161" t="s">
+        <v>1165</v>
+      </c>
     </row>
     <row r="1162" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1162"/>
+      <c r="A1162" t="s">
+        <v>1166</v>
+      </c>
     </row>
     <row r="1163" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1163"/>
+      <c r="A1163" t="s">
+        <v>1167</v>
+      </c>
     </row>
     <row r="1164" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1164"/>
+      <c r="A1164" t="s">
+        <v>1168</v>
+      </c>
     </row>
     <row r="1165" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1165"/>
+      <c r="A1165" t="s">
+        <v>1169</v>
+      </c>
     </row>
     <row r="1166" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1166"/>
+      <c r="A1166" t="s">
+        <v>1170</v>
+      </c>
     </row>
     <row r="1167" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1167"/>
+      <c r="A1167" t="s">
+        <v>1171</v>
+      </c>
     </row>
     <row r="1168" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1168"/>
+      <c r="A1168" t="s">
+        <v>1172</v>
+      </c>
     </row>
     <row r="1169" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1169"/>
+      <c r="A1169" t="s">
+        <v>1173</v>
+      </c>
     </row>
     <row r="1170" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1170"/>
+      <c r="A1170" t="s">
+        <v>1174</v>
+      </c>
     </row>
     <row r="1171" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1171"/>
+      <c r="A1171" t="s">
+        <v>1175</v>
+      </c>
     </row>
     <row r="1172" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1172"/>
+      <c r="A1172" t="s">
+        <v>1176</v>
+      </c>
     </row>
     <row r="1173" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1173"/>
+      <c r="A1173" t="s">
+        <v>1177</v>
+      </c>
     </row>
     <row r="1174" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1174"/>
+      <c r="A1174" t="s">
+        <v>1178</v>
+      </c>
     </row>
     <row r="1175" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1175"/>
+      <c r="A1175" t="s">
+        <v>1179</v>
+      </c>
     </row>
     <row r="1176" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1176"/>
+      <c r="A1176" t="s">
+        <v>1180</v>
+      </c>
     </row>
     <row r="1177" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1177"/>
+      <c r="A1177" t="s">
+        <v>1181</v>
+      </c>
     </row>
     <row r="1178" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1178"/>
+      <c r="A1178" t="s">
+        <v>1182</v>
+      </c>
     </row>
     <row r="1179" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1179"/>
+      <c r="A1179" t="s">
+        <v>1183</v>
+      </c>
     </row>
     <row r="1180" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1180"/>
+      <c r="A1180" t="s">
+        <v>1184</v>
+      </c>
     </row>
     <row r="1181" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1181"/>
+      <c r="A1181" t="s">
+        <v>1185</v>
+      </c>
     </row>
     <row r="1182" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1182"/>
+      <c r="A1182" t="s">
+        <v>1186</v>
+      </c>
     </row>
     <row r="1183" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1183"/>
+      <c r="A1183" t="s">
+        <v>1187</v>
+      </c>
     </row>
     <row r="1184" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1184"/>
+      <c r="A1184" t="s">
+        <v>1188</v>
+      </c>
     </row>
     <row r="1185" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1185"/>
+      <c r="A1185" t="s">
+        <v>1189</v>
+      </c>
     </row>
     <row r="1186" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1186"/>
+      <c r="A1186" t="s">
+        <v>1190</v>
+      </c>
     </row>
     <row r="1187" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1187"/>
+      <c r="A1187" t="s">
+        <v>1191</v>
+      </c>
     </row>
     <row r="1188" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1188"/>
+      <c r="A1188" t="s">
+        <v>1192</v>
+      </c>
     </row>
     <row r="1189" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1189"/>
+      <c r="A1189" t="s">
+        <v>1193</v>
+      </c>
     </row>
     <row r="1190" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1190"/>
+      <c r="A1190" t="s">
+        <v>1194</v>
+      </c>
     </row>
     <row r="1191" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1191"/>
+      <c r="A1191" t="s">
+        <v>1195</v>
+      </c>
     </row>
     <row r="1192" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1192"/>
+      <c r="A1192" t="s">
+        <v>1196</v>
+      </c>
     </row>
     <row r="1193" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1193"/>
+      <c r="A1193" t="s">
+        <v>1197</v>
+      </c>
     </row>
     <row r="1194" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1194"/>
+      <c r="A1194" t="s">
+        <v>1198</v>
+      </c>
     </row>
     <row r="1195" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1195"/>
+      <c r="A1195" t="s">
+        <v>1199</v>
+      </c>
     </row>
     <row r="1196" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1196"/>
+      <c r="A1196" t="s">
+        <v>1200</v>
+      </c>
     </row>
     <row r="1197" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1197"/>
+      <c r="A1197" t="s">
+        <v>1201</v>
+      </c>
     </row>
     <row r="1198" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1198"/>
+      <c r="A1198" t="s">
+        <v>1202</v>
+      </c>
     </row>
     <row r="1199" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1199"/>
+      <c r="A1199" t="s">
+        <v>1203</v>
+      </c>
     </row>
     <row r="1200" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1200"/>
+      <c r="A1200" t="s">
+        <v>1204</v>
+      </c>
     </row>
     <row r="1201" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1201"/>
+      <c r="A1201" t="s">
+        <v>1205</v>
+      </c>
     </row>
     <row r="1202" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1202"/>
+      <c r="A1202" t="s">
+        <v>1206</v>
+      </c>
     </row>
     <row r="1203" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1203"/>
+      <c r="A1203" t="s">
+        <v>1207</v>
+      </c>
     </row>
     <row r="1204" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1204"/>
+      <c r="A1204" t="s">
+        <v>1208</v>
+      </c>
     </row>
     <row r="1205" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1205"/>
+      <c r="A1205" t="s">
+        <v>1209</v>
+      </c>
     </row>
     <row r="1206" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1206"/>
+      <c r="A1206" t="s">
+        <v>1210</v>
+      </c>
     </row>
     <row r="1207" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1207"/>
+      <c r="A1207" t="s">
+        <v>1211</v>
+      </c>
     </row>
     <row r="1208" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1208"/>
+      <c r="A1208" t="s">
+        <v>1212</v>
+      </c>
     </row>
     <row r="1209" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1209"/>
+      <c r="A1209" t="s">
+        <v>1213</v>
+      </c>
     </row>
     <row r="1210" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1210"/>
+      <c r="A1210" t="s">
+        <v>1214</v>
+      </c>
     </row>
     <row r="1211" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1211"/>
+      <c r="A1211" t="s">
+        <v>1215</v>
+      </c>
     </row>
     <row r="1212" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1212"/>
+      <c r="A1212" t="s">
+        <v>1216</v>
+      </c>
     </row>
     <row r="1213" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1213"/>
+      <c r="A1213" t="s">
+        <v>1217</v>
+      </c>
     </row>
     <row r="1214" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1214"/>
+      <c r="A1214" t="s">
+        <v>1218</v>
+      </c>
     </row>
     <row r="1215" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1215"/>
+      <c r="A1215" t="s">
+        <v>1219</v>
+      </c>
     </row>
     <row r="1216" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1216"/>
+      <c r="A1216" t="s">
+        <v>1220</v>
+      </c>
     </row>
     <row r="1217" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1217"/>
+      <c r="A1217" t="s">
+        <v>1221</v>
+      </c>
     </row>
     <row r="1218" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1218"/>
+      <c r="A1218" t="s">
+        <v>1222</v>
+      </c>
     </row>
     <row r="1219" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1219"/>
+      <c r="A1219" t="s">
+        <v>1223</v>
+      </c>
     </row>
     <row r="1220" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1220"/>
+      <c r="A1220" t="s">
+        <v>1224</v>
+      </c>
     </row>
     <row r="1221" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1221"/>
+      <c r="A1221" t="s">
+        <v>1225</v>
+      </c>
     </row>
     <row r="1222" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1222"/>
+      <c r="A1222" t="s">
+        <v>1226</v>
+      </c>
     </row>
     <row r="1223" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1223"/>
+      <c r="A1223" t="s">
+        <v>1227</v>
+      </c>
     </row>
     <row r="1224" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1224"/>
+      <c r="A1224" t="s">
+        <v>1228</v>
+      </c>
     </row>
     <row r="1225" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1225"/>
+      <c r="A1225" t="s">
+        <v>1229</v>
+      </c>
     </row>
     <row r="1226" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1226"/>
+      <c r="A1226" t="s">
+        <v>1230</v>
+      </c>
     </row>
     <row r="1227" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1227"/>
+      <c r="A1227" t="s">
+        <v>1231</v>
+      </c>
     </row>
     <row r="1228" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1228"/>
+      <c r="A1228" t="s">
+        <v>1232</v>
+      </c>
     </row>
     <row r="1229" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1229"/>
+      <c r="A1229" t="s">
+        <v>1233</v>
+      </c>
     </row>
     <row r="1230" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1230"/>
+      <c r="A1230" t="s">
+        <v>1234</v>
+      </c>
     </row>
     <row r="1231" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1231"/>
+      <c r="A1231" t="s">
+        <v>1235</v>
+      </c>
     </row>
     <row r="1232" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1232"/>
+      <c r="A1232" t="s">
+        <v>1236</v>
+      </c>
     </row>
     <row r="1233" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1233"/>
+      <c r="A1233" t="s">
+        <v>1237</v>
+      </c>
     </row>
     <row r="1234" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1234"/>
+      <c r="A1234" t="s">
+        <v>1238</v>
+      </c>
     </row>
     <row r="1235" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1235"/>
+      <c r="A1235" t="s">
+        <v>1239</v>
+      </c>
     </row>
     <row r="1236" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1236"/>
+      <c r="A1236" t="s">
+        <v>1240</v>
+      </c>
     </row>
     <row r="1237" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1237"/>
+      <c r="A1237" t="s">
+        <v>1241</v>
+      </c>
     </row>
     <row r="1238" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1238"/>
+      <c r="A1238" t="s">
+        <v>1242</v>
+      </c>
     </row>
     <row r="1239" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1239"/>
+      <c r="A1239" t="s">
+        <v>1243</v>
+      </c>
     </row>
     <row r="1240" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1240"/>
+      <c r="A1240" t="s">
+        <v>1244</v>
+      </c>
     </row>
     <row r="1241" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1241"/>
+      <c r="A1241" t="s">
+        <v>1245</v>
+      </c>
     </row>
     <row r="1242" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1242"/>
+      <c r="A1242" t="s">
+        <v>1246</v>
+      </c>
     </row>
     <row r="1243" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1243"/>
+      <c r="A1243" t="s">
+        <v>1247</v>
+      </c>
     </row>
     <row r="1244" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1244"/>
+      <c r="A1244" t="s">
+        <v>1248</v>
+      </c>
     </row>
     <row r="1245" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1245"/>
+      <c r="A1245" t="s">
+        <v>1249</v>
+      </c>
     </row>
     <row r="1246" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1246"/>
+      <c r="A1246" t="s">
+        <v>1250</v>
+      </c>
     </row>
     <row r="1247" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1247"/>
+      <c r="A1247" t="s">
+        <v>1251</v>
+      </c>
     </row>
     <row r="1248" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1248"/>
+      <c r="A1248" t="s">
+        <v>1252</v>
+      </c>
     </row>
     <row r="1249" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1249"/>
+      <c r="A1249" t="s">
+        <v>1253</v>
+      </c>
     </row>
     <row r="1250" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1250"/>
+      <c r="A1250" t="s">
+        <v>1254</v>
+      </c>
     </row>
     <row r="1251" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1251"/>
+      <c r="A1251" t="s">
+        <v>1255</v>
+      </c>
     </row>
     <row r="1252" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1252"/>
+      <c r="A1252" t="s">
+        <v>1256</v>
+      </c>
     </row>
     <row r="1253" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1253"/>
+      <c r="A1253" t="s">
+        <v>1553</v>
+      </c>
     </row>
     <row r="1254" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1254"/>
+      <c r="A1254" t="s">
+        <v>1257</v>
+      </c>
     </row>
     <row r="1255" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1255"/>
+      <c r="A1255" t="s">
+        <v>1258</v>
+      </c>
     </row>
     <row r="1256" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1256"/>
+      <c r="A1256" t="s">
+        <v>1259</v>
+      </c>
     </row>
     <row r="1257" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1257"/>
+      <c r="A1257" t="s">
+        <v>1260</v>
+      </c>
     </row>
     <row r="1258" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1258"/>
+      <c r="A1258" t="s">
+        <v>1261</v>
+      </c>
     </row>
     <row r="1259" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1259"/>
+      <c r="A1259" t="s">
+        <v>1262</v>
+      </c>
     </row>
     <row r="1260" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1260"/>
+      <c r="A1260" t="s">
+        <v>1263</v>
+      </c>
     </row>
     <row r="1261" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1261"/>
+      <c r="A1261" t="s">
+        <v>1264</v>
+      </c>
     </row>
     <row r="1262" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1262"/>
+      <c r="A1262" t="s">
+        <v>1265</v>
+      </c>
     </row>
     <row r="1263" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1263"/>
+      <c r="A1263" t="s">
+        <v>1266</v>
+      </c>
     </row>
     <row r="1264" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1264"/>
+      <c r="A1264" t="s">
+        <v>1267</v>
+      </c>
     </row>
     <row r="1265" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1265"/>
+      <c r="A1265" t="s">
+        <v>1268</v>
+      </c>
     </row>
     <row r="1266" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1266"/>
+      <c r="A1266" t="s">
+        <v>1269</v>
+      </c>
     </row>
     <row r="1267" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1267"/>
+      <c r="A1267" t="s">
+        <v>1270</v>
+      </c>
     </row>
     <row r="1268" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1268"/>
+      <c r="A1268" t="s">
+        <v>1271</v>
+      </c>
     </row>
     <row r="1269" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1269"/>
+      <c r="A1269" t="s">
+        <v>1272</v>
+      </c>
     </row>
     <row r="1270" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1270"/>
+      <c r="A1270" t="s">
+        <v>1273</v>
+      </c>
     </row>
     <row r="1271" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1271"/>
+      <c r="A1271" t="s">
+        <v>1274</v>
+      </c>
     </row>
     <row r="1272" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1272"/>
+      <c r="A1272" t="s">
+        <v>1275</v>
+      </c>
     </row>
     <row r="1273" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1273"/>
+      <c r="A1273" t="s">
+        <v>1276</v>
+      </c>
     </row>
     <row r="1274" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1274"/>
+      <c r="A1274" t="s">
+        <v>1277</v>
+      </c>
     </row>
     <row r="1275" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1275"/>
+      <c r="A1275" t="s">
+        <v>1278</v>
+      </c>
     </row>
     <row r="1276" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1276"/>
+      <c r="A1276" t="s">
+        <v>1279</v>
+      </c>
     </row>
     <row r="1277" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1277"/>
+      <c r="A1277" t="s">
+        <v>1280</v>
+      </c>
     </row>
     <row r="1278" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1278"/>
+      <c r="A1278" t="s">
+        <v>1281</v>
+      </c>
     </row>
     <row r="1279" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1279"/>
+      <c r="A1279" t="s">
+        <v>1282</v>
+      </c>
     </row>
     <row r="1280" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1280"/>
+      <c r="A1280" t="s">
+        <v>1283</v>
+      </c>
     </row>
     <row r="1281" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1281"/>
+      <c r="A1281" t="s">
+        <v>1284</v>
+      </c>
     </row>
     <row r="1282" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1282"/>
+      <c r="A1282" t="s">
+        <v>1285</v>
+      </c>
     </row>
     <row r="1283" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1283"/>
+      <c r="A1283" t="s">
+        <v>1286</v>
+      </c>
     </row>
     <row r="1284" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1284"/>
+      <c r="A1284" t="s">
+        <v>1287</v>
+      </c>
     </row>
     <row r="1285" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1285"/>
+      <c r="A1285" t="s">
+        <v>1288</v>
+      </c>
     </row>
     <row r="1286" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1286"/>
+      <c r="A1286" t="s">
+        <v>1289</v>
+      </c>
     </row>
     <row r="1287" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1287"/>
+      <c r="A1287" t="s">
+        <v>1290</v>
+      </c>
     </row>
     <row r="1288" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1288"/>
+      <c r="A1288" t="s">
+        <v>1291</v>
+      </c>
     </row>
     <row r="1289" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1289"/>
+      <c r="A1289" t="s">
+        <v>1292</v>
+      </c>
     </row>
     <row r="1290" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1290"/>
+      <c r="A1290" t="s">
+        <v>1293</v>
+      </c>
     </row>
     <row r="1291" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1291"/>
+      <c r="A1291" t="s">
+        <v>1294</v>
+      </c>
     </row>
     <row r="1292" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1292"/>
+      <c r="A1292" t="s">
+        <v>1295</v>
+      </c>
     </row>
     <row r="1293" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1293"/>
+      <c r="A1293" t="s">
+        <v>1296</v>
+      </c>
     </row>
     <row r="1294" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1294"/>
+      <c r="A1294" t="s">
+        <v>1297</v>
+      </c>
     </row>
     <row r="1295" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1295"/>
+      <c r="A1295" t="s">
+        <v>1298</v>
+      </c>
     </row>
     <row r="1296" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1296"/>
+      <c r="A1296" t="s">
+        <v>1299</v>
+      </c>
     </row>
     <row r="1297" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1297"/>
+      <c r="A1297" t="s">
+        <v>1300</v>
+      </c>
     </row>
     <row r="1298" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1298"/>
+      <c r="A1298" t="s">
+        <v>1301</v>
+      </c>
     </row>
     <row r="1299" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1299"/>
+      <c r="A1299" t="s">
+        <v>1302</v>
+      </c>
     </row>
     <row r="1300" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1300"/>
+      <c r="A1300" t="s">
+        <v>1303</v>
+      </c>
     </row>
     <row r="1301" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1301"/>
+      <c r="A1301" t="s">
+        <v>1304</v>
+      </c>
     </row>
     <row r="1302" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1302"/>
+      <c r="A1302" t="s">
+        <v>1305</v>
+      </c>
     </row>
     <row r="1303" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1303"/>
+      <c r="A1303" t="s">
+        <v>1306</v>
+      </c>
     </row>
     <row r="1304" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1304"/>
+      <c r="A1304" t="s">
+        <v>1307</v>
+      </c>
     </row>
     <row r="1305" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1305"/>
+      <c r="A1305" t="s">
+        <v>1308</v>
+      </c>
     </row>
     <row r="1306" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1306"/>
+      <c r="A1306" t="s">
+        <v>1309</v>
+      </c>
     </row>
     <row r="1307" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1307"/>
+      <c r="A1307" t="s">
+        <v>1310</v>
+      </c>
     </row>
     <row r="1308" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1308"/>
+      <c r="A1308" t="s">
+        <v>1311</v>
+      </c>
     </row>
     <row r="1309" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1309"/>
+      <c r="A1309" t="s">
+        <v>1312</v>
+      </c>
     </row>
     <row r="1310" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1310"/>
+      <c r="A1310" t="s">
+        <v>1313</v>
+      </c>
     </row>
     <row r="1311" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1311"/>
+      <c r="A1311" t="s">
+        <v>1314</v>
+      </c>
     </row>
     <row r="1312" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1312"/>
+      <c r="A1312" t="s">
+        <v>1315</v>
+      </c>
     </row>
     <row r="1313" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1313"/>
+      <c r="A1313" t="s">
+        <v>1316</v>
+      </c>
     </row>
     <row r="1314" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1314"/>
+      <c r="A1314" t="s">
+        <v>1317</v>
+      </c>
     </row>
     <row r="1315" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1315"/>
+      <c r="A1315" t="s">
+        <v>1318</v>
+      </c>
     </row>
     <row r="1316" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1316"/>
+      <c r="A1316" t="s">
+        <v>1319</v>
+      </c>
     </row>
     <row r="1317" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1317"/>
+      <c r="A1317" t="s">
+        <v>1320</v>
+      </c>
     </row>
     <row r="1318" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1318"/>
+      <c r="A1318" t="s">
+        <v>1321</v>
+      </c>
     </row>
     <row r="1319" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1319"/>
+      <c r="A1319" t="s">
+        <v>1322</v>
+      </c>
     </row>
     <row r="1320" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1320"/>
+      <c r="A1320" t="s">
+        <v>1323</v>
+      </c>
     </row>
     <row r="1321" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1321"/>
+      <c r="A1321" t="s">
+        <v>1324</v>
+      </c>
     </row>
     <row r="1322" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1322"/>
+      <c r="A1322" t="s">
+        <v>1325</v>
+      </c>
     </row>
     <row r="1323" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1323"/>
+      <c r="A1323" t="s">
+        <v>1326</v>
+      </c>
     </row>
     <row r="1324" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1324"/>
+      <c r="A1324" t="s">
+        <v>1327</v>
+      </c>
     </row>
     <row r="1325" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1325"/>
+      <c r="A1325" t="s">
+        <v>1328</v>
+      </c>
     </row>
     <row r="1326" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1326"/>
+      <c r="A1326" t="s">
+        <v>1329</v>
+      </c>
     </row>
     <row r="1327" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1327"/>
+      <c r="A1327" t="s">
+        <v>1330</v>
+      </c>
     </row>
     <row r="1328" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1328"/>
+      <c r="A1328" t="s">
+        <v>1331</v>
+      </c>
     </row>
     <row r="1329" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1329"/>
+      <c r="A1329" t="s">
+        <v>1332</v>
+      </c>
     </row>
     <row r="1330" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1330"/>
+      <c r="A1330" t="s">
+        <v>1333</v>
+      </c>
     </row>
     <row r="1331" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1331"/>
+      <c r="A1331" t="s">
+        <v>1334</v>
+      </c>
     </row>
     <row r="1332" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1332"/>
+      <c r="A1332" t="s">
+        <v>1335</v>
+      </c>
     </row>
     <row r="1333" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1333"/>
+      <c r="A1333" t="s">
+        <v>1336</v>
+      </c>
     </row>
     <row r="1334" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1334"/>
+      <c r="A1334" t="s">
+        <v>1337</v>
+      </c>
     </row>
     <row r="1335" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1335"/>
+      <c r="A1335" t="s">
+        <v>1338</v>
+      </c>
     </row>
     <row r="1336" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1336"/>
+      <c r="A1336" t="s">
+        <v>1339</v>
+      </c>
     </row>
     <row r="1337" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1337"/>
+      <c r="A1337" t="s">
+        <v>1340</v>
+      </c>
     </row>
     <row r="1338" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1338"/>
+      <c r="A1338" t="s">
+        <v>1341</v>
+      </c>
     </row>
     <row r="1339" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1339"/>
+      <c r="A1339" t="s">
+        <v>1342</v>
+      </c>
     </row>
     <row r="1340" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1340"/>
+      <c r="A1340" t="s">
+        <v>1343</v>
+      </c>
     </row>
     <row r="1341" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1341"/>
+      <c r="A1341" t="s">
+        <v>1344</v>
+      </c>
     </row>
     <row r="1342" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1342"/>
+      <c r="A1342" t="s">
+        <v>1345</v>
+      </c>
     </row>
     <row r="1343" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1343"/>
+      <c r="A1343" t="s">
+        <v>1346</v>
+      </c>
     </row>
     <row r="1344" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1344"/>
+      <c r="A1344" t="s">
+        <v>1347</v>
+      </c>
     </row>
     <row r="1345" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1345"/>
+      <c r="A1345" t="s">
+        <v>1348</v>
+      </c>
     </row>
     <row r="1346" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1346"/>
+      <c r="A1346" t="s">
+        <v>1349</v>
+      </c>
     </row>
     <row r="1347" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1347"/>
+      <c r="A1347" t="s">
+        <v>1350</v>
+      </c>
     </row>
     <row r="1348" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1348"/>
+      <c r="A1348" t="s">
+        <v>1351</v>
+      </c>
     </row>
     <row r="1349" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1349"/>
+      <c r="A1349" t="s">
+        <v>1352</v>
+      </c>
     </row>
     <row r="1350" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1350"/>
+      <c r="A1350" t="s">
+        <v>1353</v>
+      </c>
     </row>
     <row r="1351" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1351"/>
+      <c r="A1351" t="s">
+        <v>1354</v>
+      </c>
     </row>
     <row r="1352" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1352"/>
+      <c r="A1352" t="s">
+        <v>1355</v>
+      </c>
     </row>
     <row r="1353" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1353"/>
+      <c r="A1353" t="s">
+        <v>1356</v>
+      </c>
     </row>
     <row r="1354" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1354"/>
+      <c r="A1354" t="s">
+        <v>1357</v>
+      </c>
     </row>
     <row r="1355" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1355"/>
+      <c r="A1355" t="s">
+        <v>1358</v>
+      </c>
     </row>
     <row r="1356" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1356"/>
+      <c r="A1356" t="s">
+        <v>1359</v>
+      </c>
     </row>
     <row r="1357" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1357"/>
+      <c r="A1357" t="s">
+        <v>1360</v>
+      </c>
     </row>
     <row r="1358" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1358"/>
+      <c r="A1358" t="s">
+        <v>1361</v>
+      </c>
     </row>
     <row r="1359" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1359"/>
+      <c r="A1359" t="s">
+        <v>1362</v>
+      </c>
     </row>
     <row r="1360" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1360"/>
+      <c r="A1360" t="s">
+        <v>1363</v>
+      </c>
     </row>
     <row r="1361" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1361"/>
+      <c r="A1361" t="s">
+        <v>1364</v>
+      </c>
     </row>
     <row r="1362" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1362"/>
+      <c r="A1362" t="s">
+        <v>1365</v>
+      </c>
     </row>
     <row r="1363" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1363"/>
+      <c r="A1363" t="s">
+        <v>1366</v>
+      </c>
     </row>
     <row r="1364" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1364"/>
+      <c r="A1364" t="s">
+        <v>1367</v>
+      </c>
     </row>
     <row r="1365" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1365"/>
+      <c r="A1365" t="s">
+        <v>1368</v>
+      </c>
     </row>
     <row r="1366" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1366"/>
+      <c r="A1366" t="s">
+        <v>1369</v>
+      </c>
     </row>
     <row r="1367" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1367"/>
+      <c r="A1367" t="s">
+        <v>1370</v>
+      </c>
     </row>
     <row r="1368" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1368"/>
+      <c r="A1368" t="s">
+        <v>1371</v>
+      </c>
     </row>
     <row r="1369" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1369"/>
+      <c r="A1369" t="s">
+        <v>1372</v>
+      </c>
     </row>
     <row r="1370" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1370"/>
+      <c r="A1370" t="s">
+        <v>1373</v>
+      </c>
     </row>
     <row r="1371" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1371"/>
+      <c r="A1371" t="s">
+        <v>1374</v>
+      </c>
     </row>
     <row r="1372" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1372"/>
+      <c r="A1372" t="s">
+        <v>1375</v>
+      </c>
     </row>
     <row r="1373" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1373"/>
+      <c r="A1373" t="s">
+        <v>1376</v>
+      </c>
     </row>
     <row r="1374" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1374"/>
+      <c r="A1374" t="s">
+        <v>1377</v>
+      </c>
     </row>
     <row r="1375" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1375"/>
+      <c r="A1375" t="s">
+        <v>1378</v>
+      </c>
     </row>
     <row r="1376" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1376"/>
+      <c r="A1376" t="s">
+        <v>1379</v>
+      </c>
     </row>
     <row r="1377" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1377"/>
+      <c r="A1377" t="s">
+        <v>1380</v>
+      </c>
     </row>
     <row r="1378" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1378"/>
+      <c r="A1378" t="s">
+        <v>1381</v>
+      </c>
     </row>
     <row r="1379" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1379"/>
+      <c r="A1379" t="s">
+        <v>1382</v>
+      </c>
     </row>
     <row r="1380" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1380"/>
+      <c r="A1380" t="s">
+        <v>1383</v>
+      </c>
     </row>
     <row r="1381" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1381"/>
+      <c r="A1381" t="s">
+        <v>1384</v>
+      </c>
     </row>
     <row r="1382" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1382"/>
+      <c r="A1382" t="s">
+        <v>1385</v>
+      </c>
     </row>
     <row r="1383" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1383"/>
+      <c r="A1383" t="s">
+        <v>1386</v>
+      </c>
     </row>
     <row r="1384" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1384"/>
+      <c r="A1384" t="s">
+        <v>1387</v>
+      </c>
     </row>
     <row r="1385" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1385"/>
+      <c r="A1385" t="s">
+        <v>1388</v>
+      </c>
     </row>
     <row r="1386" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1386"/>
+      <c r="A1386" t="s">
+        <v>1389</v>
+      </c>
     </row>
     <row r="1387" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1387"/>
+      <c r="A1387" t="s">
+        <v>1390</v>
+      </c>
     </row>
     <row r="1388" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1388"/>
+      <c r="A1388" t="s">
+        <v>1391</v>
+      </c>
     </row>
     <row r="1389" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1389"/>
+      <c r="A1389" t="s">
+        <v>1392</v>
+      </c>
     </row>
     <row r="1390" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1390"/>
+      <c r="A1390" t="s">
+        <v>1393</v>
+      </c>
     </row>
     <row r="1391" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1391"/>
+      <c r="A1391" t="s">
+        <v>1394</v>
+      </c>
     </row>
     <row r="1392" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1392"/>
+      <c r="A1392" t="s">
+        <v>1395</v>
+      </c>
     </row>
     <row r="1393" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1393"/>
+      <c r="A1393" t="s">
+        <v>1396</v>
+      </c>
     </row>
     <row r="1394" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1394"/>
+      <c r="A1394" t="s">
+        <v>1397</v>
+      </c>
     </row>
     <row r="1395" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1395"/>
+      <c r="A1395" t="s">
+        <v>1398</v>
+      </c>
     </row>
     <row r="1396" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1396"/>
+      <c r="A1396" t="s">
+        <v>1399</v>
+      </c>
     </row>
     <row r="1397" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1397"/>
+      <c r="A1397" t="s">
+        <v>1400</v>
+      </c>
     </row>
     <row r="1398" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1398"/>
+      <c r="A1398" t="s">
+        <v>1401</v>
+      </c>
     </row>
     <row r="1399" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1399"/>
+      <c r="A1399" t="s">
+        <v>1402</v>
+      </c>
     </row>
     <row r="1400" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1400"/>
+      <c r="A1400" t="s">
+        <v>1403</v>
+      </c>
     </row>
     <row r="1401" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1401"/>
+      <c r="A1401" t="s">
+        <v>1404</v>
+      </c>
     </row>
     <row r="1402" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1402"/>
+      <c r="A1402" t="s">
+        <v>1405</v>
+      </c>
     </row>
     <row r="1403" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1403"/>
+      <c r="A1403" t="s">
+        <v>1406</v>
+      </c>
     </row>
     <row r="1404" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1404"/>
+      <c r="A1404" t="s">
+        <v>1407</v>
+      </c>
     </row>
     <row r="1405" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1405"/>
+      <c r="A1405" t="s">
+        <v>1408</v>
+      </c>
     </row>
     <row r="1406" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1406"/>
+      <c r="A1406" t="s">
+        <v>1409</v>
+      </c>
     </row>
     <row r="1407" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1407"/>
+      <c r="A1407" t="s">
+        <v>1410</v>
+      </c>
     </row>
     <row r="1408" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1408"/>
+      <c r="A1408" t="s">
+        <v>1411</v>
+      </c>
     </row>
     <row r="1409" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1409"/>
+      <c r="A1409" t="s">
+        <v>1412</v>
+      </c>
     </row>
     <row r="1410" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1410"/>
+      <c r="A1410" t="s">
+        <v>1413</v>
+      </c>
     </row>
     <row r="1411" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1411"/>
+      <c r="A1411" t="s">
+        <v>1414</v>
+      </c>
     </row>
     <row r="1412" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1412"/>
+      <c r="A1412" t="s">
+        <v>1415</v>
+      </c>
     </row>
     <row r="1413" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1413"/>
+      <c r="A1413" t="s">
+        <v>1416</v>
+      </c>
     </row>
     <row r="1414" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1414"/>
+      <c r="A1414" t="s">
+        <v>1417</v>
+      </c>
     </row>
     <row r="1415" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1415"/>
+      <c r="A1415" t="s">
+        <v>1418</v>
+      </c>
     </row>
     <row r="1416" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1416"/>
+      <c r="A1416" t="s">
+        <v>1419</v>
+      </c>
     </row>
     <row r="1417" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1417"/>
+      <c r="A1417" t="s">
+        <v>1420</v>
+      </c>
     </row>
     <row r="1418" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1418"/>
+      <c r="A1418" t="s">
+        <v>1421</v>
+      </c>
     </row>
     <row r="1419" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1419"/>
+      <c r="A1419" t="s">
+        <v>1422</v>
+      </c>
     </row>
     <row r="1420" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1420"/>
+      <c r="A1420" t="s">
+        <v>1423</v>
+      </c>
     </row>
     <row r="1421" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1421"/>
+      <c r="A1421" t="s">
+        <v>1424</v>
+      </c>
     </row>
     <row r="1422" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1422"/>
+      <c r="A1422" t="s">
+        <v>1425</v>
+      </c>
     </row>
     <row r="1423" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1423"/>
+      <c r="A1423" t="s">
+        <v>1426</v>
+      </c>
     </row>
     <row r="1424" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1424"/>
+      <c r="A1424" t="s">
+        <v>1427</v>
+      </c>
     </row>
     <row r="1425" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1425"/>
+      <c r="A1425" t="s">
+        <v>1428</v>
+      </c>
     </row>
     <row r="1426" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1426"/>
+      <c r="A1426" t="s">
+        <v>1429</v>
+      </c>
     </row>
     <row r="1427" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1427"/>
+      <c r="A1427" t="s">
+        <v>1430</v>
+      </c>
     </row>
     <row r="1428" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1428"/>
+      <c r="A1428" t="s">
+        <v>1431</v>
+      </c>
     </row>
     <row r="1429" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1429"/>
+      <c r="A1429" t="s">
+        <v>1432</v>
+      </c>
     </row>
     <row r="1430" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1430"/>
+      <c r="A1430" t="s">
+        <v>1433</v>
+      </c>
     </row>
     <row r="1431" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1431"/>
+      <c r="A1431" t="s">
+        <v>1434</v>
+      </c>
     </row>
     <row r="1432" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1432"/>
+      <c r="A1432" t="s">
+        <v>1435</v>
+      </c>
     </row>
     <row r="1433" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1433"/>
+      <c r="A1433" t="s">
+        <v>1436</v>
+      </c>
     </row>
     <row r="1434" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1434"/>
+      <c r="A1434" t="s">
+        <v>1437</v>
+      </c>
     </row>
     <row r="1435" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1435"/>
+      <c r="A1435" t="s">
+        <v>1438</v>
+      </c>
     </row>
     <row r="1436" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1436"/>
+      <c r="A1436" t="s">
+        <v>1439</v>
+      </c>
     </row>
     <row r="1437" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1437"/>
+      <c r="A1437" t="s">
+        <v>1440</v>
+      </c>
     </row>
     <row r="1438" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1438"/>
+      <c r="A1438" t="s">
+        <v>1441</v>
+      </c>
     </row>
     <row r="1439" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1439"/>
+      <c r="A1439" t="s">
+        <v>1442</v>
+      </c>
     </row>
     <row r="1440" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1440"/>
+      <c r="A1440" t="s">
+        <v>1443</v>
+      </c>
     </row>
     <row r="1441" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1441"/>
+      <c r="A1441" t="s">
+        <v>1444</v>
+      </c>
     </row>
     <row r="1442" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1442"/>
+      <c r="A1442" t="s">
+        <v>1445</v>
+      </c>
     </row>
     <row r="1443" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1443"/>
+      <c r="A1443" t="s">
+        <v>1446</v>
+      </c>
     </row>
     <row r="1444" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1444"/>
+      <c r="A1444" t="s">
+        <v>1447</v>
+      </c>
     </row>
     <row r="1445" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1445"/>
+      <c r="A1445" t="s">
+        <v>1448</v>
+      </c>
     </row>
     <row r="1446" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1446"/>
+      <c r="A1446" t="s">
+        <v>1449</v>
+      </c>
     </row>
     <row r="1447" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1447"/>
+      <c r="A1447" t="s">
+        <v>1450</v>
+      </c>
     </row>
     <row r="1448" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1448"/>
+      <c r="A1448" t="s">
+        <v>1451</v>
+      </c>
     </row>
     <row r="1449" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1449"/>
+      <c r="A1449" t="s">
+        <v>1452</v>
+      </c>
     </row>
     <row r="1450" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1450"/>
+      <c r="A1450" t="s">
+        <v>1453</v>
+      </c>
     </row>
     <row r="1451" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1451"/>
+      <c r="A1451" t="s">
+        <v>1454</v>
+      </c>
     </row>
     <row r="1452" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1452"/>
+      <c r="A1452" t="s">
+        <v>1455</v>
+      </c>
     </row>
     <row r="1453" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1453"/>
+      <c r="A1453" t="s">
+        <v>1456</v>
+      </c>
     </row>
     <row r="1454" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1454"/>
+      <c r="A1454" t="s">
+        <v>1457</v>
+      </c>
     </row>
     <row r="1455" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1455"/>
+      <c r="A1455" t="s">
+        <v>1458</v>
+      </c>
     </row>
     <row r="1456" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1456"/>
+      <c r="A1456" t="s">
+        <v>1459</v>
+      </c>
     </row>
     <row r="1457" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1457"/>
+      <c r="A1457" t="s">
+        <v>1460</v>
+      </c>
     </row>
     <row r="1458" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1458"/>
+      <c r="A1458" t="s">
+        <v>1461</v>
+      </c>
     </row>
     <row r="1459" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1459"/>
+      <c r="A1459" t="s">
+        <v>1462</v>
+      </c>
     </row>
     <row r="1460" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1460"/>
+      <c r="A1460" t="s">
+        <v>1463</v>
+      </c>
     </row>
     <row r="1461" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1461"/>
+      <c r="A1461" t="s">
+        <v>1464</v>
+      </c>
     </row>
     <row r="1462" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1462"/>
+      <c r="A1462" t="s">
+        <v>1465</v>
+      </c>
     </row>
     <row r="1463" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1463"/>
+      <c r="A1463" t="s">
+        <v>1466</v>
+      </c>
     </row>
     <row r="1464" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1464"/>
+      <c r="A1464" t="s">
+        <v>1467</v>
+      </c>
     </row>
     <row r="1465" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1465"/>
+      <c r="A1465" t="s">
+        <v>1468</v>
+      </c>
     </row>
     <row r="1466" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1466"/>
+      <c r="A1466" t="s">
+        <v>1469</v>
+      </c>
     </row>
     <row r="1467" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1467"/>
+      <c r="A1467" t="s">
+        <v>1470</v>
+      </c>
     </row>
     <row r="1468" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1468"/>
+      <c r="A1468" t="s">
+        <v>1471</v>
+      </c>
     </row>
     <row r="1469" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1469"/>
+      <c r="A1469" t="s">
+        <v>1472</v>
+      </c>
     </row>
     <row r="1470" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1470"/>
+      <c r="A1470" t="s">
+        <v>1473</v>
+      </c>
     </row>
     <row r="1471" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1471"/>
+      <c r="A1471" t="s">
+        <v>1474</v>
+      </c>
     </row>
     <row r="1472" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1472"/>
+      <c r="A1472" t="s">
+        <v>1475</v>
+      </c>
     </row>
     <row r="1473" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1473"/>
+      <c r="A1473" t="s">
+        <v>1476</v>
+      </c>
     </row>
     <row r="1474" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1474"/>
+      <c r="A1474" t="s">
+        <v>1477</v>
+      </c>
     </row>
     <row r="1475" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1475"/>
+      <c r="A1475" t="s">
+        <v>1478</v>
+      </c>
     </row>
     <row r="1476" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1476"/>
+      <c r="A1476" t="s">
+        <v>1479</v>
+      </c>
     </row>
     <row r="1477" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1477"/>
+      <c r="A1477" t="s">
+        <v>1480</v>
+      </c>
     </row>
     <row r="1478" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1478"/>
+      <c r="A1478" t="s">
+        <v>1481</v>
+      </c>
     </row>
     <row r="1479" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1479"/>
+      <c r="A1479" t="s">
+        <v>1482</v>
+      </c>
     </row>
     <row r="1480" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1480"/>
+      <c r="A1480" t="s">
+        <v>1483</v>
+      </c>
     </row>
     <row r="1481" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1481"/>
+      <c r="A1481" t="s">
+        <v>1484</v>
+      </c>
     </row>
     <row r="1482" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1482"/>
+      <c r="A1482" t="s">
+        <v>1485</v>
+      </c>
     </row>
     <row r="1483" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1483"/>
+      <c r="A1483" t="s">
+        <v>1486</v>
+      </c>
     </row>
     <row r="1484" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1484"/>
+      <c r="A1484" t="s">
+        <v>1487</v>
+      </c>
     </row>
     <row r="1485" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1485"/>
+      <c r="A1485" t="s">
+        <v>1488</v>
+      </c>
     </row>
     <row r="1486" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1486"/>
+      <c r="A1486" t="s">
+        <v>1489</v>
+      </c>
     </row>
     <row r="1487" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1487"/>
+      <c r="A1487" t="s">
+        <v>1490</v>
+      </c>
     </row>
     <row r="1488" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1488"/>
+      <c r="A1488" t="s">
+        <v>1491</v>
+      </c>
     </row>
     <row r="1489" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1489"/>
+      <c r="A1489" t="s">
+        <v>1492</v>
+      </c>
     </row>
     <row r="1490" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1490"/>
+      <c r="A1490" t="s">
+        <v>1493</v>
+      </c>
     </row>
     <row r="1491" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1491"/>
+      <c r="A1491" t="s">
+        <v>1494</v>
+      </c>
     </row>
     <row r="1492" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1492"/>
+      <c r="A1492" t="s">
+        <v>1495</v>
+      </c>
     </row>
     <row r="1493" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1493"/>
+      <c r="A1493" t="s">
+        <v>1496</v>
+      </c>
     </row>
     <row r="1494" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1494"/>
+      <c r="A1494" t="s">
+        <v>1497</v>
+      </c>
     </row>
     <row r="1495" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1495"/>
+      <c r="A1495" t="s">
+        <v>1498</v>
+      </c>
     </row>
     <row r="1496" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1496"/>
+      <c r="A1496" t="s">
+        <v>1499</v>
+      </c>
     </row>
     <row r="1497" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1497"/>
+      <c r="A1497" t="s">
+        <v>1500</v>
+      </c>
     </row>
     <row r="1498" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1498"/>
+      <c r="A1498" t="s">
+        <v>1501</v>
+      </c>
     </row>
     <row r="1499" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1499"/>
+      <c r="A1499" t="s">
+        <v>1502</v>
+      </c>
     </row>
     <row r="1500" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1500"/>
+      <c r="A1500" t="s">
+        <v>1503</v>
+      </c>
     </row>
     <row r="1501" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1501"/>
+      <c r="A1501" t="s">
+        <v>1504</v>
+      </c>
     </row>
     <row r="1502" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1502"/>
+      <c r="A1502" t="s">
+        <v>1505</v>
+      </c>
     </row>
     <row r="1503" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1503"/>
+      <c r="A1503" t="s">
+        <v>1506</v>
+      </c>
     </row>
     <row r="1504" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1504"/>
+      <c r="A1504" t="s">
+        <v>1507</v>
+      </c>
     </row>
     <row r="1505" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1505"/>
+      <c r="A1505" t="s">
+        <v>1508</v>
+      </c>
     </row>
     <row r="1506" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1506"/>
+      <c r="A1506" t="s">
+        <v>1509</v>
+      </c>
     </row>
     <row r="1507" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1507"/>
+      <c r="A1507" t="s">
+        <v>1510</v>
+      </c>
     </row>
     <row r="1508" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1508"/>
+      <c r="A1508" t="s">
+        <v>1511</v>
+      </c>
     </row>
     <row r="1509" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1509"/>
+      <c r="A1509" t="s">
+        <v>1512</v>
+      </c>
     </row>
     <row r="1510" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1510"/>
+      <c r="A1510" t="s">
+        <v>1513</v>
+      </c>
     </row>
     <row r="1511" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1511"/>
+      <c r="A1511" t="s">
+        <v>1514</v>
+      </c>
     </row>
     <row r="1512" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1512"/>
+      <c r="A1512" t="s">
+        <v>1515</v>
+      </c>
     </row>
     <row r="1513" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1513"/>
+      <c r="A1513" t="s">
+        <v>1516</v>
+      </c>
     </row>
     <row r="1514" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1514"/>
+      <c r="A1514" t="s">
+        <v>1517</v>
+      </c>
     </row>
     <row r="1515" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1515"/>
+      <c r="A1515" t="s">
+        <v>1518</v>
+      </c>
     </row>
     <row r="1516" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1516"/>
+      <c r="A1516" t="s">
+        <v>1519</v>
+      </c>
     </row>
     <row r="1517" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1517"/>
+      <c r="A1517" s="1" t="s">
+        <v>1520</v>
+      </c>
     </row>
     <row r="1518" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1518"/>
+      <c r="A1518" s="1" t="s">
+        <v>1521</v>
+      </c>
     </row>
     <row r="1519" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1519"/>
+      <c r="A1519" s="1" t="s">
+        <v>1522</v>
+      </c>
     </row>
     <row r="1520" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1520"/>
+      <c r="A1520" s="1" t="s">
+        <v>1523</v>
+      </c>
     </row>
     <row r="1521" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1521"/>
+      <c r="A1521" s="1" t="s">
+        <v>1524</v>
+      </c>
     </row>
     <row r="1522" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1522"/>
+      <c r="A1522" s="1" t="s">
+        <v>1525</v>
+      </c>
     </row>
     <row r="1523" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1523"/>
+      <c r="A1523" s="1" t="s">
+        <v>1526</v>
+      </c>
     </row>
     <row r="1524" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1524"/>
+      <c r="A1524" s="1" t="s">
+        <v>1527</v>
+      </c>
     </row>
     <row r="1525" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1525"/>
+      <c r="A1525" s="1" t="s">
+        <v>1528</v>
+      </c>
     </row>
     <row r="1526" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1526"/>
+      <c r="A1526" s="1" t="s">
+        <v>1529</v>
+      </c>
     </row>
     <row r="1527" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1527"/>
+      <c r="A1527" s="1" t="s">
+        <v>1530</v>
+      </c>
     </row>
     <row r="1528" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1528"/>
+      <c r="A1528" s="1" t="s">
+        <v>1531</v>
+      </c>
     </row>
     <row r="1529" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1529"/>
+      <c r="A1529" s="1" t="s">
+        <v>1532</v>
+      </c>
     </row>
     <row r="1530" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1530"/>
+      <c r="A1530" s="1" t="s">
+        <v>1533</v>
+      </c>
     </row>
     <row r="1531" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1531"/>
+      <c r="A1531" s="1" t="s">
+        <v>1534</v>
+      </c>
     </row>
     <row r="1532" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1532"/>
+      <c r="A1532" s="1" t="s">
+        <v>1535</v>
+      </c>
     </row>
     <row r="1533" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1533"/>
+      <c r="A1533" s="1" t="s">
+        <v>1536</v>
+      </c>
     </row>
     <row r="1534" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1534"/>
+      <c r="A1534" s="1" t="s">
+        <v>1537</v>
+      </c>
     </row>
     <row r="1535" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1535"/>
+      <c r="A1535" s="1" t="s">
+        <v>1538</v>
+      </c>
     </row>
     <row r="1536" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1536"/>
+      <c r="A1536" s="1" t="s">
+        <v>1539</v>
+      </c>
     </row>
     <row r="1537" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1537"/>
+      <c r="A1537" s="1" t="s">
+        <v>1540</v>
+      </c>
     </row>
     <row r="1538" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1538"/>
+      <c r="A1538" s="1" t="s">
+        <v>1541</v>
+      </c>
     </row>
     <row r="1539" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1539"/>
+      <c r="A1539" s="1" t="s">
+        <v>1542</v>
+      </c>
     </row>
     <row r="1540" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1540"/>
+      <c r="A1540" s="1" t="s">
+        <v>1543</v>
+      </c>
     </row>
     <row r="1541" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1541"/>
+      <c r="A1541" s="1" t="s">
+        <v>1544</v>
+      </c>
     </row>
     <row r="1542" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1542"/>
+      <c r="A1542" s="1" t="s">
+        <v>1545</v>
+      </c>
     </row>
     <row r="1543" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1543"/>
+      <c r="A1543" s="1" t="s">
+        <v>1546</v>
+      </c>
     </row>
     <row r="1544" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1544"/>
+      <c r="A1544" s="1" t="s">
+        <v>1547</v>
+      </c>
     </row>
     <row r="1545" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1545"/>
+      <c r="A1545" s="1" t="s">
+        <v>1548</v>
+      </c>
     </row>
     <row r="1546" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1546"/>
+      <c r="A1546" s="1" t="s">
+        <v>1549</v>
+      </c>
     </row>
     <row r="1547" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1547"/>
+      <c r="A1547" s="1" t="s">
+        <v>1550</v>
+      </c>
     </row>
     <row r="1548" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1548"/>
+      <c r="A1548" s="1" t="s">
+        <v>1551</v>
+      </c>
     </row>
     <row r="1549" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1549"/>
+      <c r="A1549" s="1" t="s">
+        <v>1552</v>
+      </c>
     </row>
     <row r="1550" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1550"/>
+      <c r="A1550" t="s">
+        <v>1554</v>
+      </c>
     </row>
     <row r="1551" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1551"/>
+      <c r="A1551" t="s">
+        <v>1555</v>
+      </c>
     </row>
     <row r="1552" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1552"/>
+      <c r="A1552" t="s">
+        <v>1556</v>
+      </c>
     </row>
     <row r="1553" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1553"/>
+      <c r="A1553" t="s">
+        <v>1557</v>
+      </c>
     </row>
     <row r="1554" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1554"/>
+      <c r="A1554" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1555" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1556" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1557" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1558" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1559" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1560" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1561" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1562" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1563" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1564" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1565" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1566" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1567" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1568" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1569" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1570" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1571" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1572" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1573" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1574" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1575" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1576" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1577" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1578" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1579" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1580" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1581" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1582" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1583" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1584" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1585" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1586" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1587" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1588" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1589" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1590" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1591" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1592" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1593" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1594" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1595" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1596" s="1" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1597" s="1" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1598" s="1" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1599" s="1" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1600" s="1" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1601" s="1" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1602" s="1" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1603" s="1" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1604" s="1" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1605" s="1" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1606" s="1" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:1" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A1607" s="1" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1608" s="1" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1609" s="1" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1610" s="1" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1611" s="1" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1612" s="1" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1613" s="1" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1614" s="1" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1615" s="1" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1616" s="1" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1617" s="1" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1618" s="1" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1619" s="1" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1620" s="1" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1621" s="1" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1622" s="1" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1623" s="1" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1624" s="1" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1625" s="1" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1626" s="1" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1627" s="1" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1628" s="1" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1629" s="1" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1630" s="1" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1631" s="1" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1632" s="1" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1633" s="1" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1634" s="1" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1635" s="1" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1636" s="1" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1637" s="1" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1638" s="1" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1639" s="1" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1640" s="1" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1641" s="1" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1642" s="1" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1643" s="1" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1644" s="1" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1645" s="1" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1646" s="1" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1647" s="1" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1648" s="1" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1649" s="1" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1650" s="1" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1651" s="1" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1652" s="1" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1653" s="1" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1654" s="1" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1655" s="1" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1656" s="1" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1657" s="1" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1658" s="1" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1659" s="1" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1660" s="1" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1661" s="1" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1662" s="1" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1663" s="1" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1664" s="1" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1665" s="1" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1666" s="1" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1667" s="1" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1668" s="1" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1669" s="1" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1670" s="1" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1671" s="1" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1672" s="1" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1673" s="1" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:1" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A1674" s="1" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1675" s="1" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1676" s="1" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1677" s="1" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1678" s="1" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1679" s="1" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1680" s="1" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1681" s="1" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1682" s="1" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1683" s="1" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1684" s="1" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1685" s="1" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1686" s="1" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1687" s="1" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1688" s="1" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:1" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A1689" s="1" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:1" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A1690" s="1" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1691" s="1" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1692" s="1" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1693" s="1" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1694" s="1" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1695" s="1" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1696" s="1" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1697" s="1" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1698" s="1" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1699" s="1" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1700" s="1" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1701" s="1" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1702" s="1" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1703" s="1" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1704" s="1" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1705" s="1" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1706" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1707" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1708" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1709" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1710" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1711" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1712" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1713" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1714" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1715" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1716" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1717" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1718" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1719" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1720" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1721" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1722" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1723" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1724" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1725" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1726" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1727" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1728" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1729" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1730" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1731" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1732" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1733" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1734" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1735" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1736" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1737" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1738" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1739" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1740" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1741" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1742" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1743" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1744" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1745" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1746" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1747" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1748" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1749" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1750" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1751" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1752" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1753" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1754" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1755" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1756" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1757" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1758" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1759" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1760" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1761" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1762" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1763" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1764" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1765" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1766" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1767" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1768" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1769" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1770" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1771" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1772" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1773" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1774" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1775" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1776" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1777" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1778" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1779" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1780" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1781" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1782" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1783" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1784" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1785" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1786" s="1" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1787" s="1" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1788" s="1" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1789" s="1" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1790" s="1" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1791"/>
+    </row>
+    <row r="1792" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1792"/>
+    </row>
+    <row r="1793" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1793"/>
+    </row>
+    <row r="1794" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1794"/>
+    </row>
+    <row r="1795" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1795"/>
+    </row>
+    <row r="1796" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1796"/>
+    </row>
+    <row r="1797" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1797"/>
+    </row>
+    <row r="1798" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1798"/>
+    </row>
+    <row r="1799" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1799"/>
+    </row>
+    <row r="1800" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1800"/>
+    </row>
+    <row r="1801" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1801"/>
+    </row>
+    <row r="1802" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1802"/>
+    </row>
+    <row r="1803" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1803"/>
+    </row>
+    <row r="1804" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1804"/>
+    </row>
+    <row r="1805" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1805"/>
+    </row>
+    <row r="1806" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1806"/>
+    </row>
+    <row r="1807" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1807"/>
+    </row>
+    <row r="1808" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1808"/>
+    </row>
+    <row r="1809" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1809"/>
+    </row>
+    <row r="1810" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1810"/>
+    </row>
+    <row r="1811" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1811"/>
+    </row>
+    <row r="1812" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1812"/>
+    </row>
+    <row r="1813" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1813"/>
+    </row>
+    <row r="1814" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1814"/>
+    </row>
+    <row r="1815" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1815"/>
+    </row>
+    <row r="1816" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1816"/>
+    </row>
+    <row r="1817" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1817"/>
+    </row>
+    <row r="1818" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1818"/>
+    </row>
+    <row r="1819" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1819"/>
+    </row>
+    <row r="1820" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1820"/>
+    </row>
+    <row r="1821" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1821"/>
+    </row>
+    <row r="1822" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1822"/>
+    </row>
+    <row r="1823" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1823"/>
+    </row>
+    <row r="1824" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1824"/>
+    </row>
+    <row r="1825" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1825"/>
+    </row>
+    <row r="1826" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1826"/>
+    </row>
+    <row r="1827" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1827"/>
+    </row>
+    <row r="1828" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1828"/>
+    </row>
+    <row r="1829" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1829"/>
+    </row>
+    <row r="1830" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1830"/>
+    </row>
+    <row r="1831" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1831"/>
+    </row>
+    <row r="1832" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1832"/>
+    </row>
+    <row r="1833" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1833"/>
+    </row>
+    <row r="1834" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1834"/>
+    </row>
+    <row r="1835" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1835"/>
+    </row>
+    <row r="1836" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1836"/>
+    </row>
+    <row r="1837" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1837"/>
+    </row>
+    <row r="1838" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1838"/>
+    </row>
+    <row r="1839" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1839"/>
+    </row>
+    <row r="1840" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1840"/>
+    </row>
+    <row r="1841" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1841"/>
+    </row>
+    <row r="1842" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1842"/>
+    </row>
+    <row r="1843" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1843"/>
+    </row>
+    <row r="1844" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1844"/>
+    </row>
+    <row r="1845" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1845"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -10812,4 +15216,610 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="F10:F128"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="10" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F10" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="11" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F11" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="12" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F12" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="13" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F13" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="14" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F14" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="15" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F15" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="16" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F17" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F18" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F19" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F20" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="21" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F21" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="22" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F22" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F23" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="24" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F24" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="25" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F25" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="26" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F26" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="27" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F27" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="28" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F28" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="29" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F29" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="30" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F30" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="31" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F31" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="32" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F32" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="33" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F33" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="34" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F34" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F35" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="36" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F36" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="37" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F37" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="38" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F38" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="39" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F39" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="40" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F40" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="41" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F41" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="42" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F42" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="43" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F43" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="44" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F44" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="45" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F45" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="46" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F46" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="47" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F47" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="48" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F48" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F49" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="50" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F50" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="51" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F51" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="52" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F52" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="53" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F53" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="54" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F54" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="55" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F55" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="56" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F56" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="57" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F57" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="58" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F58" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="59" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F59" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="60" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F60" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="61" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F61" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="62" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F62" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="63" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F63" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="64" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F64" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="65" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F65" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="66" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F66" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="67" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F67" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="68" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F68" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="69" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F69" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="70" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F70" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="71" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F71" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="72" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F72" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="73" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F73" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="74" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F74" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="75" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F75" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="76" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F76" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="77" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F77" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="78" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F78" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="79" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F79" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="80" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F80" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="81" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F81" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="82" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F82" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="83" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F83" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="84" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F84" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="85" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F85" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="86" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F86" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="87" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F87" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="88" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F88" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="89" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F89" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="90" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F90" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="91" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F91" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="92" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F92" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="93" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F93" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="94" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F94" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="95" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F95" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="96" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F96" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="97" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F97" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="98" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F98" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="99" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F99" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="100" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F100" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="101" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F101" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="102" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F102" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="103" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F103" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="104" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F104" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="105" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F105" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="106" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F106" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="107" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F107" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="108" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F108" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="109" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F109" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="110" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F110" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="111" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F111" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="112" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F112" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="113" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F113" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="114" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F114" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="115" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F115" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="116" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F116" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="117" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F117" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="118" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F118" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="119" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F119" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="120" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F120" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="121" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F121" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="122" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F122" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="123" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F123" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="124" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F124" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="125" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F125" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="126" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F126" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="127" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F127" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="128" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F128" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Datas/LanguageSwitchDataList.xlsx
+++ b/Datas/LanguageSwitchDataList.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4851" uniqueCount="4753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4879" uniqueCount="4785">
   <si>
     <t>string</t>
   </si>
@@ -14436,10 +14436,6 @@
     <t>个</t>
   </si>
   <si>
-    <t>获得</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>友好度降低1级</t>
   </si>
   <si>
@@ -14514,9 +14510,6 @@
     <t>item</t>
   </si>
   <si>
-    <t>Gained</t>
-  </si>
-  <si>
     <t>Friendship decreased by 1</t>
   </si>
   <si>
@@ -14581,13 +14574,116 @@
   </si>
   <si>
     <t>Discovered the recipe for crafting &lt;color=blue&gt;{0}&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 的生日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>'s birthday</t>
+  </si>
+  <si>
+    <t>空间不足</t>
+  </si>
+  <si>
+    <t>背包无法放下这么多东西</t>
+  </si>
+  <si>
+    <t>提示</t>
+  </si>
+  <si>
+    <t>植物已经死亡，请铲除!</t>
+  </si>
+  <si>
+    <t>请平整土地!</t>
+  </si>
+  <si>
+    <t>材料不足</t>
+  </si>
+  <si>
+    <t>消耗物品不足</t>
+  </si>
+  <si>
+    <t>需消耗:</t>
+  </si>
+  <si>
+    <t>当前拥有;</t>
+  </si>
+  <si>
+    <t>无法制作！</t>
+  </si>
+  <si>
+    <t>RP消耗过大</t>
+  </si>
+  <si>
+    <t>需消耗RP:</t>
+  </si>
+  <si>
+    <t>超过拥有RP;</t>
+  </si>
+  <si>
+    <t>购买{0}个</t>
+  </si>
+  <si>
+    <t>提炼{0}金币</t>
+  </si>
+  <si>
+    <t>拓展{0}空间?</t>
+  </si>
+  <si>
+    <t>Not enough space</t>
+  </si>
+  <si>
+    <t>Too many items for the bag</t>
+  </si>
+  <si>
+    <t>Tip</t>
+  </si>
+  <si>
+    <t>The plant is dead, please remove it!</t>
+  </si>
+  <si>
+    <t>Please flatten the land!</t>
+  </si>
+  <si>
+    <t>Not enough materials</t>
+  </si>
+  <si>
+    <t>Insufficient consumables</t>
+  </si>
+  <si>
+    <t>Required:</t>
+  </si>
+  <si>
+    <t>Current stock:</t>
+  </si>
+  <si>
+    <t>Cannot craft!</t>
+  </si>
+  <si>
+    <t>RP consumption too high</t>
+  </si>
+  <si>
+    <t>Required RP:</t>
+  </si>
+  <si>
+    <t>Exceeds available RP</t>
+  </si>
+  <si>
+    <t>Buy {0} items</t>
+  </si>
+  <si>
+    <t>Refine {0} coins</t>
+  </si>
+  <si>
+    <t>Expand {0} space?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -14615,6 +14711,15 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -14682,7 +14787,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -14745,6 +14850,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -15066,7 +15172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1851"/>
+  <dimension ref="A1:D1865"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.125" style="1" customWidth="1"/>
@@ -29803,7 +29909,7 @@
         <v>4699</v>
       </c>
       <c r="B1823" t="s">
-        <v>4724</v>
+        <v>4723</v>
       </c>
       <c r="C1823"/>
       <c r="D1823"/>
@@ -29813,7 +29919,7 @@
         <v>4700</v>
       </c>
       <c r="B1824" t="s">
-        <v>4725</v>
+        <v>4724</v>
       </c>
       <c r="C1824"/>
       <c r="D1824"/>
@@ -29823,7 +29929,7 @@
         <v>4701</v>
       </c>
       <c r="B1825" t="s">
-        <v>4726</v>
+        <v>4725</v>
       </c>
       <c r="C1825"/>
       <c r="D1825"/>
@@ -29833,17 +29939,17 @@
         <v>4702</v>
       </c>
       <c r="B1826" t="s">
-        <v>4727</v>
+        <v>4726</v>
       </c>
       <c r="C1826"/>
       <c r="D1826"/>
     </row>
     <row r="1827" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1827" t="s">
-        <v>4744</v>
+        <v>4742</v>
       </c>
       <c r="B1827" t="s">
-        <v>4745</v>
+        <v>4743</v>
       </c>
       <c r="C1827"/>
       <c r="D1827"/>
@@ -29853,7 +29959,7 @@
         <v>4703</v>
       </c>
       <c r="B1828" t="s">
-        <v>4728</v>
+        <v>4727</v>
       </c>
       <c r="C1828"/>
       <c r="D1828"/>
@@ -29863,7 +29969,7 @@
         <v>4704</v>
       </c>
       <c r="B1829" t="s">
-        <v>4729</v>
+        <v>4728</v>
       </c>
       <c r="C1829"/>
       <c r="D1829"/>
@@ -29873,7 +29979,7 @@
         <v>4705</v>
       </c>
       <c r="B1830" t="s">
-        <v>4730</v>
+        <v>4729</v>
       </c>
       <c r="C1830"/>
       <c r="D1830"/>
@@ -29883,7 +29989,7 @@
         <v>4706</v>
       </c>
       <c r="B1831" t="s">
-        <v>4731</v>
+        <v>4730</v>
       </c>
       <c r="C1831"/>
       <c r="D1831"/>
@@ -29893,7 +29999,7 @@
         <v>4707</v>
       </c>
       <c r="B1832" t="s">
-        <v>4732</v>
+        <v>4731</v>
       </c>
       <c r="C1832"/>
       <c r="D1832"/>
@@ -29903,7 +30009,7 @@
         <v>4708</v>
       </c>
       <c r="B1833" t="s">
-        <v>4733</v>
+        <v>4732</v>
       </c>
       <c r="C1833"/>
       <c r="D1833"/>
@@ -29913,7 +30019,7 @@
         <v>4709</v>
       </c>
       <c r="B1834" t="s">
-        <v>4734</v>
+        <v>4733</v>
       </c>
       <c r="C1834"/>
       <c r="D1834"/>
@@ -29923,7 +30029,7 @@
         <v>4710</v>
       </c>
       <c r="B1835" t="s">
-        <v>4735</v>
+        <v>4734</v>
       </c>
       <c r="C1835"/>
       <c r="D1835"/>
@@ -29933,7 +30039,7 @@
         <v>4711</v>
       </c>
       <c r="B1836" t="s">
-        <v>4736</v>
+        <v>4735</v>
       </c>
       <c r="C1836"/>
       <c r="D1836"/>
@@ -29943,7 +30049,7 @@
         <v>4712</v>
       </c>
       <c r="B1837" t="s">
-        <v>4737</v>
+        <v>4736</v>
       </c>
       <c r="C1837"/>
       <c r="D1837"/>
@@ -29953,7 +30059,7 @@
         <v>4713</v>
       </c>
       <c r="B1838" t="s">
-        <v>4738</v>
+        <v>4737</v>
       </c>
       <c r="C1838"/>
       <c r="D1838"/>
@@ -29963,27 +30069,25 @@
         <v>4714</v>
       </c>
       <c r="B1839" t="s">
-        <v>4739</v>
+        <v>4738</v>
       </c>
       <c r="C1839"/>
       <c r="D1839"/>
     </row>
     <row r="1840" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1840" t="s">
+      <c r="A1840" s="1" t="s">
         <v>4715</v>
       </c>
       <c r="B1840" t="s">
-        <v>4740</v>
-      </c>
-      <c r="C1840"/>
-      <c r="D1840"/>
+        <v>4739</v>
+      </c>
     </row>
     <row r="1841" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1841" s="1" t="s">
         <v>4716</v>
       </c>
       <c r="B1841" t="s">
-        <v>4741</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="1842" spans="1:2" x14ac:dyDescent="0.2">
@@ -29991,23 +30095,23 @@
         <v>4717</v>
       </c>
       <c r="B1842" t="s">
-        <v>4742</v>
+        <v>4741</v>
       </c>
     </row>
     <row r="1843" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1843" s="1" t="s">
-        <v>4718</v>
+        <v>4749</v>
       </c>
       <c r="B1843" t="s">
-        <v>4743</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="1844" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1844" s="1" t="s">
-        <v>4751</v>
+        <v>4718</v>
       </c>
       <c r="B1844" t="s">
-        <v>4752</v>
+        <v>4744</v>
       </c>
     </row>
     <row r="1845" spans="1:2" x14ac:dyDescent="0.2">
@@ -30015,7 +30119,7 @@
         <v>4719</v>
       </c>
       <c r="B1845" t="s">
-        <v>4746</v>
+        <v>4745</v>
       </c>
     </row>
     <row r="1846" spans="1:2" x14ac:dyDescent="0.2">
@@ -30023,20 +30127,20 @@
         <v>4720</v>
       </c>
       <c r="B1846" t="s">
-        <v>4747</v>
+        <v>4746</v>
       </c>
     </row>
     <row r="1847" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1847" s="1" t="s">
-        <v>4718</v>
+        <v>4721</v>
       </c>
       <c r="B1847" t="s">
-        <v>4743</v>
+        <v>4747</v>
       </c>
     </row>
     <row r="1848" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1848" s="1" t="s">
-        <v>4721</v>
+        <v>4722</v>
       </c>
       <c r="B1848" t="s">
         <v>4748</v>
@@ -30044,26 +30148,138 @@
     </row>
     <row r="1849" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1849" s="1" t="s">
-        <v>4722</v>
-      </c>
-      <c r="B1849" t="s">
-        <v>4749</v>
+        <v>4751</v>
+      </c>
+      <c r="B1849" s="24" t="s">
+        <v>4752</v>
       </c>
     </row>
     <row r="1850" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1850" s="1" t="s">
-        <v>4723</v>
+        <v>4753</v>
       </c>
       <c r="B1850" t="s">
-        <v>4750</v>
+        <v>4769</v>
       </c>
     </row>
     <row r="1851" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1851" s="1" t="s">
-        <v>4699</v>
+        <v>4754</v>
       </c>
       <c r="B1851" t="s">
-        <v>4724</v>
+        <v>4770</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1852" s="1" t="s">
+        <v>4755</v>
+      </c>
+      <c r="B1852" t="s">
+        <v>4771</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1853" s="1" t="s">
+        <v>4756</v>
+      </c>
+      <c r="B1853" t="s">
+        <v>4772</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1854" s="1" t="s">
+        <v>4757</v>
+      </c>
+      <c r="B1854" t="s">
+        <v>4773</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1855" s="1" t="s">
+        <v>4758</v>
+      </c>
+      <c r="B1855" t="s">
+        <v>4774</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1856" s="1" t="s">
+        <v>4759</v>
+      </c>
+      <c r="B1856" t="s">
+        <v>4775</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1857" s="1" t="s">
+        <v>4760</v>
+      </c>
+      <c r="B1857" t="s">
+        <v>4776</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1858" s="1" t="s">
+        <v>4761</v>
+      </c>
+      <c r="B1858" t="s">
+        <v>4777</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1859" s="1" t="s">
+        <v>4762</v>
+      </c>
+      <c r="B1859" t="s">
+        <v>4778</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1860" s="1" t="s">
+        <v>4763</v>
+      </c>
+      <c r="B1860" t="s">
+        <v>4779</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1861" s="1" t="s">
+        <v>4764</v>
+      </c>
+      <c r="B1861" t="s">
+        <v>4780</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1862" s="1" t="s">
+        <v>4765</v>
+      </c>
+      <c r="B1862" t="s">
+        <v>4781</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1863" s="1" t="s">
+        <v>4766</v>
+      </c>
+      <c r="B1863" t="s">
+        <v>4782</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1864" s="1" t="s">
+        <v>4767</v>
+      </c>
+      <c r="B1864" t="s">
+        <v>4783</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1865" s="1" t="s">
+        <v>4768</v>
+      </c>
+      <c r="B1865" t="s">
+        <v>4784</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/LanguageSwitchDataList.xlsx
+++ b/Datas/LanguageSwitchDataList.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4881" uniqueCount="4862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4937" uniqueCount="4917">
   <si>
     <t>string</t>
   </si>
@@ -15728,23 +15728,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Stock Quantity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Change</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Remove from Shelf</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Chat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Leave the Team</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -16740,6 +16728,192 @@
   <si>
     <t>浓郁果香，口感醇厚，将整串葡萄的精华浓缩。</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Count:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>椅子</t>
+  </si>
+  <si>
+    <t>储物箱</t>
+  </si>
+  <si>
+    <t>长椅</t>
+  </si>
+  <si>
+    <t>树墩</t>
+  </si>
+  <si>
+    <t>柴棚</t>
+  </si>
+  <si>
+    <t>牲畜棚</t>
+  </si>
+  <si>
+    <t>栅栏</t>
+  </si>
+  <si>
+    <t>春战场</t>
+  </si>
+  <si>
+    <t>夏战场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>秋战场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬战场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初级牲口棚</t>
+  </si>
+  <si>
+    <t>食物槽</t>
+  </si>
+  <si>
+    <t>水槽</t>
+  </si>
+  <si>
+    <t>收获篮</t>
+  </si>
+  <si>
+    <t>传送门</t>
+  </si>
+  <si>
+    <t>我的家</t>
+  </si>
+  <si>
+    <t>镇公所</t>
+  </si>
+  <si>
+    <t>教堂</t>
+  </si>
+  <si>
+    <t>酒馆</t>
+  </si>
+  <si>
+    <t>俱乐部</t>
+  </si>
+  <si>
+    <t>船坞</t>
+  </si>
+  <si>
+    <t>招牌</t>
+  </si>
+  <si>
+    <t>纺织机</t>
+  </si>
+  <si>
+    <t>客栈</t>
+  </si>
+  <si>
+    <t>别墅</t>
+  </si>
+  <si>
+    <t>自宅</t>
+  </si>
+  <si>
+    <t>Chair</t>
+  </si>
+  <si>
+    <t>Storage Chest</t>
+  </si>
+  <si>
+    <t>Bench</t>
+  </si>
+  <si>
+    <t>Stump</t>
+  </si>
+  <si>
+    <t>Wood Shed</t>
+  </si>
+  <si>
+    <t>Livestock Pen</t>
+  </si>
+  <si>
+    <t>Fence</t>
+  </si>
+  <si>
+    <t>Food Trough</t>
+  </si>
+  <si>
+    <t>Water Trough</t>
+  </si>
+  <si>
+    <t>Harvest Basket</t>
+  </si>
+  <si>
+    <t>Portal</t>
+  </si>
+  <si>
+    <t>My House</t>
+  </si>
+  <si>
+    <t>Town Hall</t>
+  </si>
+  <si>
+    <t>Church</t>
+  </si>
+  <si>
+    <t>Tavern</t>
+  </si>
+  <si>
+    <t>Club</t>
+  </si>
+  <si>
+    <t>Dock</t>
+  </si>
+  <si>
+    <t>Sign</t>
+  </si>
+  <si>
+    <t>Loom</t>
+  </si>
+  <si>
+    <t>Inn</t>
+  </si>
+  <si>
+    <t>Villa</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Spring Battle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Summer Battle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Autumn Battle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Winter Battle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破损牲畜棚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damaged Barn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic Barn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -17214,7 +17388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1866"/>
+  <dimension ref="A1:D1919"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.125" style="1" customWidth="1"/>
@@ -22359,7 +22533,7 @@
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A641" s="20" t="s">
-        <v>4770</v>
+        <v>4767</v>
       </c>
       <c r="B641" s="18" t="s">
         <v>3604</v>
@@ -22375,7 +22549,7 @@
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A643" s="20" t="s">
-        <v>4774</v>
+        <v>4771</v>
       </c>
       <c r="B643" s="18" t="s">
         <v>3606</v>
@@ -22399,7 +22573,7 @@
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A646" s="20" t="s">
-        <v>4771</v>
+        <v>4768</v>
       </c>
       <c r="B646" s="18" t="s">
         <v>3609</v>
@@ -22415,7 +22589,7 @@
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A648" s="20" t="s">
-        <v>4775</v>
+        <v>4772</v>
       </c>
       <c r="B648" s="18" t="s">
         <v>3611</v>
@@ -22423,7 +22597,7 @@
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A649" s="20" t="s">
-        <v>4776</v>
+        <v>4773</v>
       </c>
       <c r="B649" s="18" t="s">
         <v>3612</v>
@@ -22439,7 +22613,7 @@
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A651" s="20" t="s">
-        <v>4772</v>
+        <v>4769</v>
       </c>
       <c r="B651" s="18" t="s">
         <v>3614</v>
@@ -22455,7 +22629,7 @@
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A653" s="13" t="s">
-        <v>4777</v>
+        <v>4774</v>
       </c>
       <c r="B653" s="18" t="s">
         <v>3616</v>
@@ -22487,7 +22661,7 @@
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A657" s="20" t="s">
-        <v>4773</v>
+        <v>4770</v>
       </c>
       <c r="B657" s="18" t="s">
         <v>3620</v>
@@ -22671,226 +22845,226 @@
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A680" s="14" t="s">
-        <v>4834</v>
+        <v>4831</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>4806</v>
+        <v>4803</v>
       </c>
     </row>
     <row r="681" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A681" s="4" t="s">
-        <v>4835</v>
+        <v>4832</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>4807</v>
+        <v>4804</v>
       </c>
     </row>
     <row r="682" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A682" s="4" t="s">
-        <v>4836</v>
+        <v>4833</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>4808</v>
+        <v>4805</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A683" s="4" t="s">
-        <v>4837</v>
+        <v>4834</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>4809</v>
+        <v>4806</v>
       </c>
     </row>
     <row r="684" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A684" s="14" t="s">
-        <v>4838</v>
+        <v>4835</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>4810</v>
+        <v>4807</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A685" s="14" t="s">
-        <v>4839</v>
+        <v>4836</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>4811</v>
+        <v>4808</v>
       </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A686" s="4" t="s">
-        <v>4840</v>
+        <v>4837</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>4812</v>
+        <v>4809</v>
       </c>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A687" s="14" t="s">
-        <v>4841</v>
+        <v>4838</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>4813</v>
+        <v>4810</v>
       </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A688" s="4" t="s">
-        <v>4842</v>
+        <v>4839</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>4814</v>
+        <v>4811</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A689" s="4" t="s">
-        <v>4843</v>
+        <v>4840</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>4815</v>
+        <v>4812</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A690" s="4" t="s">
-        <v>4844</v>
+        <v>4841</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>4816</v>
+        <v>4813</v>
       </c>
     </row>
     <row r="691" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A691" s="4" t="s">
-        <v>4845</v>
+        <v>4842</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>4817</v>
+        <v>4814</v>
       </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A692" s="4" t="s">
-        <v>4846</v>
+        <v>4843</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>4818</v>
+        <v>4815</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A693" s="4" t="s">
-        <v>4847</v>
+        <v>4844</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>4819</v>
+        <v>4816</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A694" s="14" t="s">
-        <v>4848</v>
+        <v>4845</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>4820</v>
+        <v>4817</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A695" s="4" t="s">
-        <v>4849</v>
+        <v>4846</v>
       </c>
       <c r="B695" s="1" t="s">
-        <v>4821</v>
+        <v>4818</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A696" s="4" t="s">
-        <v>4850</v>
+        <v>4847</v>
       </c>
       <c r="B696" s="1" t="s">
-        <v>4822</v>
+        <v>4819</v>
       </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A697" s="4" t="s">
-        <v>4851</v>
+        <v>4848</v>
       </c>
       <c r="B697" s="1" t="s">
-        <v>4823</v>
+        <v>4820</v>
       </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A698" s="4" t="s">
-        <v>4852</v>
+        <v>4849</v>
       </c>
       <c r="B698" s="1" t="s">
-        <v>4824</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A699" s="14" t="s">
-        <v>4853</v>
+        <v>4850</v>
       </c>
       <c r="B699" s="1" t="s">
-        <v>4825</v>
+        <v>4822</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A700" s="14" t="s">
-        <v>4854</v>
+        <v>4851</v>
       </c>
       <c r="B700" s="1" t="s">
-        <v>4826</v>
+        <v>4823</v>
       </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A701" s="4" t="s">
-        <v>4855</v>
+        <v>4852</v>
       </c>
       <c r="B701" s="1" t="s">
-        <v>4827</v>
+        <v>4824</v>
       </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A702" s="14" t="s">
-        <v>4856</v>
+        <v>4853</v>
       </c>
       <c r="B702" s="1" t="s">
-        <v>4828</v>
+        <v>4825</v>
       </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A703" s="4" t="s">
-        <v>4857</v>
+        <v>4854</v>
       </c>
       <c r="B703" s="1" t="s">
-        <v>4829</v>
+        <v>4826</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A704" s="4" t="s">
-        <v>4858</v>
+        <v>4855</v>
       </c>
       <c r="B704" s="1" t="s">
-        <v>4830</v>
+        <v>4827</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A705" s="4" t="s">
-        <v>4859</v>
+        <v>4856</v>
       </c>
       <c r="B705" s="1" t="s">
-        <v>4831</v>
+        <v>4828</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A706" s="4" t="s">
-        <v>4860</v>
+        <v>4857</v>
       </c>
       <c r="B706" s="1" t="s">
-        <v>4832</v>
+        <v>4829</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A707" s="14" t="s">
-        <v>4861</v>
+        <v>4858</v>
       </c>
       <c r="B707" s="1" t="s">
-        <v>4833</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="708" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
@@ -23127,114 +23301,114 @@
     </row>
     <row r="737" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A737" s="14" t="s">
-        <v>4778</v>
+        <v>4775</v>
       </c>
       <c r="B737" s="18" t="s">
-        <v>4792</v>
+        <v>4789</v>
       </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A738" s="4" t="s">
-        <v>4779</v>
+        <v>4776</v>
       </c>
       <c r="B738" s="18" t="s">
-        <v>4793</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="739" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A739" s="14" t="s">
-        <v>4780</v>
+        <v>4777</v>
       </c>
       <c r="B739" s="18" t="s">
-        <v>4794</v>
+        <v>4791</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A740" s="4" t="s">
-        <v>4781</v>
+        <v>4778</v>
       </c>
       <c r="B740" s="18" t="s">
-        <v>4795</v>
+        <v>4792</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A741" s="4" t="s">
-        <v>4782</v>
+        <v>4779</v>
       </c>
       <c r="B741" s="18" t="s">
-        <v>4796</v>
+        <v>4793</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A742" s="4" t="s">
-        <v>4783</v>
+        <v>4780</v>
       </c>
       <c r="B742" s="18" t="s">
-        <v>4797</v>
+        <v>4794</v>
       </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A743" s="14" t="s">
-        <v>4784</v>
+        <v>4781</v>
       </c>
       <c r="B743" s="18" t="s">
-        <v>4798</v>
+        <v>4795</v>
       </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A744" s="4" t="s">
-        <v>4785</v>
+        <v>4782</v>
       </c>
       <c r="B744" s="18" t="s">
-        <v>4799</v>
+        <v>4796</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A745" s="14" t="s">
-        <v>4786</v>
+        <v>4783</v>
       </c>
       <c r="B745" s="18" t="s">
-        <v>4800</v>
+        <v>4797</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A746" s="4" t="s">
-        <v>4787</v>
+        <v>4784</v>
       </c>
       <c r="B746" s="18" t="s">
-        <v>4801</v>
+        <v>4798</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A747" s="4" t="s">
-        <v>4788</v>
+        <v>4785</v>
       </c>
       <c r="B747" s="18" t="s">
-        <v>4802</v>
+        <v>4799</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A748" s="14" t="s">
-        <v>4789</v>
+        <v>4786</v>
       </c>
       <c r="B748" s="18" t="s">
-        <v>4803</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="749" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A749" s="4" t="s">
-        <v>4790</v>
+        <v>4787</v>
       </c>
       <c r="B749" s="18" t="s">
-        <v>4804</v>
+        <v>4801</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A750" s="14" t="s">
-        <v>4791</v>
+        <v>4788</v>
       </c>
       <c r="B750" s="18" t="s">
-        <v>4805</v>
+        <v>4802</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.2">
@@ -30207,7 +30381,7 @@
     </row>
     <row r="1608" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1608" s="1" t="s">
-        <v>4769</v>
+        <v>4766</v>
       </c>
       <c r="B1608" s="18" t="s">
         <v>4518</v>
@@ -30863,7 +31037,7 @@
         <v>2296</v>
       </c>
       <c r="B1690" s="18" t="s">
-        <v>4598</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="1691" spans="1:2" x14ac:dyDescent="0.2">
@@ -30871,7 +31045,7 @@
         <v>1621</v>
       </c>
       <c r="B1691" s="18" t="s">
-        <v>4599</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="1692" spans="1:2" x14ac:dyDescent="0.2">
@@ -30879,7 +31053,7 @@
         <v>1622</v>
       </c>
       <c r="B1692" s="18" t="s">
-        <v>4600</v>
+        <v>4481</v>
       </c>
     </row>
     <row r="1693" spans="1:2" x14ac:dyDescent="0.2">
@@ -30887,7 +31061,7 @@
         <v>1623</v>
       </c>
       <c r="B1693" s="18" t="s">
-        <v>4601</v>
+        <v>4599</v>
       </c>
     </row>
     <row r="1694" spans="1:2" x14ac:dyDescent="0.2">
@@ -30895,7 +31069,7 @@
         <v>1624</v>
       </c>
       <c r="B1694" s="18" t="s">
-        <v>4602</v>
+        <v>4859</v>
       </c>
     </row>
     <row r="1695" spans="1:2" x14ac:dyDescent="0.2">
@@ -30903,7 +31077,7 @@
         <v>1625</v>
       </c>
       <c r="B1695" s="18" t="s">
-        <v>4603</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="1696" spans="1:2" x14ac:dyDescent="0.2">
@@ -30911,7 +31085,7 @@
         <v>1626</v>
       </c>
       <c r="B1696" s="18" t="s">
-        <v>4604</v>
+        <v>4601</v>
       </c>
     </row>
     <row r="1697" spans="1:2" x14ac:dyDescent="0.2">
@@ -30919,7 +31093,7 @@
         <v>1627</v>
       </c>
       <c r="B1697" s="18" t="s">
-        <v>4605</v>
+        <v>4602</v>
       </c>
     </row>
     <row r="1698" spans="1:2" x14ac:dyDescent="0.2">
@@ -30927,7 +31101,7 @@
         <v>1628</v>
       </c>
       <c r="B1698" s="18" t="s">
-        <v>4606</v>
+        <v>4603</v>
       </c>
     </row>
     <row r="1699" spans="1:2" x14ac:dyDescent="0.2">
@@ -30935,7 +31109,7 @@
         <v>1629</v>
       </c>
       <c r="B1699" s="18" t="s">
-        <v>4607</v>
+        <v>4604</v>
       </c>
     </row>
     <row r="1700" spans="1:2" x14ac:dyDescent="0.2">
@@ -30943,7 +31117,7 @@
         <v>1630</v>
       </c>
       <c r="B1700" s="18" t="s">
-        <v>4608</v>
+        <v>4605</v>
       </c>
     </row>
     <row r="1701" spans="1:2" x14ac:dyDescent="0.2">
@@ -30951,7 +31125,7 @@
         <v>1631</v>
       </c>
       <c r="B1701" s="18" t="s">
-        <v>4609</v>
+        <v>4606</v>
       </c>
     </row>
     <row r="1702" spans="1:2" x14ac:dyDescent="0.2">
@@ -30959,7 +31133,7 @@
         <v>1632</v>
       </c>
       <c r="B1702" s="18" t="s">
-        <v>4610</v>
+        <v>4607</v>
       </c>
     </row>
     <row r="1703" spans="1:2" x14ac:dyDescent="0.2">
@@ -30967,7 +31141,7 @@
         <v>1633</v>
       </c>
       <c r="B1703" s="18" t="s">
-        <v>4611</v>
+        <v>4608</v>
       </c>
     </row>
     <row r="1704" spans="1:2" x14ac:dyDescent="0.2">
@@ -30975,7 +31149,7 @@
         <v>1634</v>
       </c>
       <c r="B1704" s="18" t="s">
-        <v>4612</v>
+        <v>4609</v>
       </c>
     </row>
     <row r="1705" spans="1:2" x14ac:dyDescent="0.2">
@@ -30983,7 +31157,7 @@
         <v>1635</v>
       </c>
       <c r="B1705" s="18" t="s">
-        <v>4613</v>
+        <v>4610</v>
       </c>
     </row>
     <row r="1706" spans="1:2" x14ac:dyDescent="0.2">
@@ -30991,7 +31165,7 @@
         <v>1636</v>
       </c>
       <c r="B1706" s="18" t="s">
-        <v>4614</v>
+        <v>4611</v>
       </c>
     </row>
     <row r="1707" spans="1:2" x14ac:dyDescent="0.2">
@@ -30999,7 +31173,7 @@
         <v>1637</v>
       </c>
       <c r="B1707" s="18" t="s">
-        <v>4615</v>
+        <v>4612</v>
       </c>
     </row>
     <row r="1708" spans="1:2" x14ac:dyDescent="0.2">
@@ -31007,7 +31181,7 @@
         <v>1638</v>
       </c>
       <c r="B1708" s="18" t="s">
-        <v>4616</v>
+        <v>4613</v>
       </c>
     </row>
     <row r="1709" spans="1:2" x14ac:dyDescent="0.2">
@@ -31015,7 +31189,7 @@
         <v>1639</v>
       </c>
       <c r="B1709" s="18" t="s">
-        <v>4617</v>
+        <v>4614</v>
       </c>
     </row>
     <row r="1710" spans="1:2" x14ac:dyDescent="0.2">
@@ -31023,7 +31197,7 @@
         <v>1640</v>
       </c>
       <c r="B1710" s="18" t="s">
-        <v>4618</v>
+        <v>4615</v>
       </c>
     </row>
     <row r="1711" spans="1:2" x14ac:dyDescent="0.2">
@@ -31031,7 +31205,7 @@
         <v>1641</v>
       </c>
       <c r="B1711" s="18" t="s">
-        <v>4619</v>
+        <v>4616</v>
       </c>
     </row>
     <row r="1712" spans="1:2" x14ac:dyDescent="0.2">
@@ -31039,7 +31213,7 @@
         <v>1642</v>
       </c>
       <c r="B1712" s="18" t="s">
-        <v>4620</v>
+        <v>4617</v>
       </c>
     </row>
     <row r="1713" spans="1:2" x14ac:dyDescent="0.2">
@@ -31047,7 +31221,7 @@
         <v>1643</v>
       </c>
       <c r="B1713" s="18" t="s">
-        <v>4621</v>
+        <v>4618</v>
       </c>
     </row>
     <row r="1714" spans="1:2" x14ac:dyDescent="0.2">
@@ -31055,7 +31229,7 @@
         <v>1644</v>
       </c>
       <c r="B1714" s="18" t="s">
-        <v>4622</v>
+        <v>4619</v>
       </c>
     </row>
     <row r="1715" spans="1:2" x14ac:dyDescent="0.2">
@@ -31063,7 +31237,7 @@
         <v>1645</v>
       </c>
       <c r="B1715" s="18" t="s">
-        <v>4623</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="1716" spans="1:2" x14ac:dyDescent="0.2">
@@ -31071,7 +31245,7 @@
         <v>1646</v>
       </c>
       <c r="B1716" s="18" t="s">
-        <v>4624</v>
+        <v>4621</v>
       </c>
     </row>
     <row r="1717" spans="1:2" x14ac:dyDescent="0.2">
@@ -31079,7 +31253,7 @@
         <v>1655</v>
       </c>
       <c r="B1717" s="18" t="s">
-        <v>4625</v>
+        <v>4622</v>
       </c>
     </row>
     <row r="1718" spans="1:2" x14ac:dyDescent="0.2">
@@ -31087,7 +31261,7 @@
         <v>1659</v>
       </c>
       <c r="B1718" s="18" t="s">
-        <v>4626</v>
+        <v>4623</v>
       </c>
     </row>
     <row r="1719" spans="1:2" x14ac:dyDescent="0.2">
@@ -31095,7 +31269,7 @@
         <v>1690</v>
       </c>
       <c r="B1719" s="18" t="s">
-        <v>4627</v>
+        <v>4624</v>
       </c>
     </row>
     <row r="1720" spans="1:2" x14ac:dyDescent="0.2">
@@ -31103,7 +31277,7 @@
         <v>1691</v>
       </c>
       <c r="B1720" s="18" t="s">
-        <v>4628</v>
+        <v>4625</v>
       </c>
     </row>
     <row r="1721" spans="1:2" x14ac:dyDescent="0.2">
@@ -31111,7 +31285,7 @@
         <v>1647</v>
       </c>
       <c r="B1721" s="18" t="s">
-        <v>4629</v>
+        <v>4626</v>
       </c>
     </row>
     <row r="1722" spans="1:2" x14ac:dyDescent="0.2">
@@ -31119,7 +31293,7 @@
         <v>1648</v>
       </c>
       <c r="B1722" s="18" t="s">
-        <v>4630</v>
+        <v>4627</v>
       </c>
     </row>
     <row r="1723" spans="1:2" x14ac:dyDescent="0.2">
@@ -31127,7 +31301,7 @@
         <v>1649</v>
       </c>
       <c r="B1723" s="18" t="s">
-        <v>4631</v>
+        <v>4628</v>
       </c>
     </row>
     <row r="1724" spans="1:2" x14ac:dyDescent="0.2">
@@ -31135,7 +31309,7 @@
         <v>1660</v>
       </c>
       <c r="B1724" s="18" t="s">
-        <v>4632</v>
+        <v>4629</v>
       </c>
     </row>
     <row r="1725" spans="1:2" x14ac:dyDescent="0.2">
@@ -31151,7 +31325,7 @@
         <v>1662</v>
       </c>
       <c r="B1726" s="18" t="s">
-        <v>4633</v>
+        <v>4630</v>
       </c>
     </row>
     <row r="1727" spans="1:2" x14ac:dyDescent="0.2">
@@ -31159,7 +31333,7 @@
         <v>1663</v>
       </c>
       <c r="B1727" s="18" t="s">
-        <v>4634</v>
+        <v>4631</v>
       </c>
     </row>
     <row r="1728" spans="1:2" x14ac:dyDescent="0.2">
@@ -31167,7 +31341,7 @@
         <v>1664</v>
       </c>
       <c r="B1728" s="18" t="s">
-        <v>4635</v>
+        <v>4632</v>
       </c>
     </row>
     <row r="1729" spans="1:2" x14ac:dyDescent="0.2">
@@ -31175,7 +31349,7 @@
         <v>1692</v>
       </c>
       <c r="B1729" s="18" t="s">
-        <v>4636</v>
+        <v>4633</v>
       </c>
     </row>
     <row r="1730" spans="1:2" x14ac:dyDescent="0.2">
@@ -31183,7 +31357,7 @@
         <v>1693</v>
       </c>
       <c r="B1730" s="18" t="s">
-        <v>4637</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="1731" spans="1:2" x14ac:dyDescent="0.2">
@@ -31191,7 +31365,7 @@
         <v>1694</v>
       </c>
       <c r="B1731" s="18" t="s">
-        <v>4638</v>
+        <v>4635</v>
       </c>
     </row>
     <row r="1732" spans="1:2" x14ac:dyDescent="0.2">
@@ -31199,7 +31373,7 @@
         <v>1695</v>
       </c>
       <c r="B1732" s="18" t="s">
-        <v>4639</v>
+        <v>4636</v>
       </c>
     </row>
     <row r="1733" spans="1:2" x14ac:dyDescent="0.2">
@@ -31207,7 +31381,7 @@
         <v>1696</v>
       </c>
       <c r="B1733" s="18" t="s">
-        <v>4640</v>
+        <v>4637</v>
       </c>
     </row>
     <row r="1734" spans="1:2" x14ac:dyDescent="0.2">
@@ -31215,7 +31389,7 @@
         <v>1697</v>
       </c>
       <c r="B1734" s="18" t="s">
-        <v>4641</v>
+        <v>4638</v>
       </c>
     </row>
     <row r="1735" spans="1:2" x14ac:dyDescent="0.2">
@@ -31223,7 +31397,7 @@
         <v>1698</v>
       </c>
       <c r="B1735" s="18" t="s">
-        <v>4642</v>
+        <v>4639</v>
       </c>
     </row>
     <row r="1736" spans="1:2" x14ac:dyDescent="0.2">
@@ -31231,7 +31405,7 @@
         <v>1699</v>
       </c>
       <c r="B1736" s="18" t="s">
-        <v>4643</v>
+        <v>4640</v>
       </c>
     </row>
     <row r="1737" spans="1:2" x14ac:dyDescent="0.2">
@@ -31239,7 +31413,7 @@
         <v>1700</v>
       </c>
       <c r="B1737" s="18" t="s">
-        <v>4644</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="1738" spans="1:2" x14ac:dyDescent="0.2">
@@ -31247,7 +31421,7 @@
         <v>1701</v>
       </c>
       <c r="B1738" s="18" t="s">
-        <v>4645</v>
+        <v>4642</v>
       </c>
     </row>
     <row r="1739" spans="1:2" x14ac:dyDescent="0.2">
@@ -31255,7 +31429,7 @@
         <v>1702</v>
       </c>
       <c r="B1739" s="18" t="s">
-        <v>4646</v>
+        <v>4643</v>
       </c>
     </row>
     <row r="1740" spans="1:2" x14ac:dyDescent="0.2">
@@ -31263,7 +31437,7 @@
         <v>1703</v>
       </c>
       <c r="B1740" s="18" t="s">
-        <v>4647</v>
+        <v>4644</v>
       </c>
     </row>
     <row r="1741" spans="1:2" x14ac:dyDescent="0.2">
@@ -31271,7 +31445,7 @@
         <v>1650</v>
       </c>
       <c r="B1741" s="18" t="s">
-        <v>4648</v>
+        <v>4645</v>
       </c>
     </row>
     <row r="1742" spans="1:2" x14ac:dyDescent="0.2">
@@ -31279,7 +31453,7 @@
         <v>1651</v>
       </c>
       <c r="B1742" s="18" t="s">
-        <v>4649</v>
+        <v>4646</v>
       </c>
     </row>
     <row r="1743" spans="1:2" x14ac:dyDescent="0.2">
@@ -31287,7 +31461,7 @@
         <v>1665</v>
       </c>
       <c r="B1743" s="18" t="s">
-        <v>4650</v>
+        <v>4647</v>
       </c>
     </row>
     <row r="1744" spans="1:2" x14ac:dyDescent="0.2">
@@ -31295,7 +31469,7 @@
         <v>1704</v>
       </c>
       <c r="B1744" s="18" t="s">
-        <v>4651</v>
+        <v>4648</v>
       </c>
     </row>
     <row r="1745" spans="1:2" x14ac:dyDescent="0.2">
@@ -31303,7 +31477,7 @@
         <v>1705</v>
       </c>
       <c r="B1745" s="18" t="s">
-        <v>4652</v>
+        <v>4649</v>
       </c>
     </row>
     <row r="1746" spans="1:2" x14ac:dyDescent="0.2">
@@ -31311,7 +31485,7 @@
         <v>1706</v>
       </c>
       <c r="B1746" s="18" t="s">
-        <v>4653</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="1747" spans="1:2" x14ac:dyDescent="0.2">
@@ -31319,7 +31493,7 @@
         <v>1707</v>
       </c>
       <c r="B1747" s="18" t="s">
-        <v>4654</v>
+        <v>4651</v>
       </c>
     </row>
     <row r="1748" spans="1:2" x14ac:dyDescent="0.2">
@@ -31327,7 +31501,7 @@
         <v>1708</v>
       </c>
       <c r="B1748" s="18" t="s">
-        <v>4655</v>
+        <v>4652</v>
       </c>
     </row>
     <row r="1749" spans="1:2" x14ac:dyDescent="0.2">
@@ -31335,7 +31509,7 @@
         <v>1709</v>
       </c>
       <c r="B1749" s="18" t="s">
-        <v>4656</v>
+        <v>4653</v>
       </c>
     </row>
     <row r="1750" spans="1:2" x14ac:dyDescent="0.2">
@@ -31343,7 +31517,7 @@
         <v>1674</v>
       </c>
       <c r="B1750" s="18" t="s">
-        <v>4657</v>
+        <v>4654</v>
       </c>
     </row>
     <row r="1751" spans="1:2" x14ac:dyDescent="0.2">
@@ -31351,7 +31525,7 @@
         <v>1710</v>
       </c>
       <c r="B1751" s="18" t="s">
-        <v>4658</v>
+        <v>4655</v>
       </c>
     </row>
     <row r="1752" spans="1:2" x14ac:dyDescent="0.2">
@@ -31359,7 +31533,7 @@
         <v>1666</v>
       </c>
       <c r="B1752" s="18" t="s">
-        <v>4659</v>
+        <v>4656</v>
       </c>
     </row>
     <row r="1753" spans="1:2" x14ac:dyDescent="0.2">
@@ -31367,7 +31541,7 @@
         <v>1667</v>
       </c>
       <c r="B1753" s="18" t="s">
-        <v>4660</v>
+        <v>4657</v>
       </c>
     </row>
     <row r="1754" spans="1:2" x14ac:dyDescent="0.2">
@@ -31375,7 +31549,7 @@
         <v>1668</v>
       </c>
       <c r="B1754" s="18" t="s">
-        <v>4661</v>
+        <v>4658</v>
       </c>
     </row>
     <row r="1755" spans="1:2" x14ac:dyDescent="0.2">
@@ -31383,7 +31557,7 @@
         <v>1669</v>
       </c>
       <c r="B1755" s="18" t="s">
-        <v>4662</v>
+        <v>4659</v>
       </c>
     </row>
     <row r="1756" spans="1:2" x14ac:dyDescent="0.2">
@@ -31391,7 +31565,7 @@
         <v>1670</v>
       </c>
       <c r="B1756" s="18" t="s">
-        <v>4663</v>
+        <v>4660</v>
       </c>
     </row>
     <row r="1757" spans="1:2" x14ac:dyDescent="0.2">
@@ -31399,7 +31573,7 @@
         <v>1711</v>
       </c>
       <c r="B1757" s="18" t="s">
-        <v>4664</v>
+        <v>4661</v>
       </c>
     </row>
     <row r="1758" spans="1:2" x14ac:dyDescent="0.2">
@@ -31407,7 +31581,7 @@
         <v>1712</v>
       </c>
       <c r="B1758" s="18" t="s">
-        <v>4665</v>
+        <v>4662</v>
       </c>
     </row>
     <row r="1759" spans="1:2" x14ac:dyDescent="0.2">
@@ -31415,7 +31589,7 @@
         <v>1713</v>
       </c>
       <c r="B1759" s="18" t="s">
-        <v>4666</v>
+        <v>4663</v>
       </c>
     </row>
     <row r="1760" spans="1:2" x14ac:dyDescent="0.2">
@@ -31423,7 +31597,7 @@
         <v>1714</v>
       </c>
       <c r="B1760" s="18" t="s">
-        <v>4667</v>
+        <v>4664</v>
       </c>
     </row>
     <row r="1761" spans="1:2" x14ac:dyDescent="0.2">
@@ -31431,7 +31605,7 @@
         <v>1715</v>
       </c>
       <c r="B1761" s="18" t="s">
-        <v>4668</v>
+        <v>4665</v>
       </c>
     </row>
     <row r="1762" spans="1:2" x14ac:dyDescent="0.2">
@@ -31439,7 +31613,7 @@
         <v>1716</v>
       </c>
       <c r="B1762" s="18" t="s">
-        <v>4669</v>
+        <v>4666</v>
       </c>
     </row>
     <row r="1763" spans="1:2" x14ac:dyDescent="0.2">
@@ -31447,7 +31621,7 @@
         <v>1671</v>
       </c>
       <c r="B1763" s="18" t="s">
-        <v>4670</v>
+        <v>4667</v>
       </c>
     </row>
     <row r="1764" spans="1:2" x14ac:dyDescent="0.2">
@@ -31455,7 +31629,7 @@
         <v>1672</v>
       </c>
       <c r="B1764" s="18" t="s">
-        <v>4671</v>
+        <v>4668</v>
       </c>
     </row>
     <row r="1765" spans="1:2" x14ac:dyDescent="0.2">
@@ -31463,7 +31637,7 @@
         <v>1673</v>
       </c>
       <c r="B1765" s="18" t="s">
-        <v>4672</v>
+        <v>4669</v>
       </c>
     </row>
     <row r="1766" spans="1:2" x14ac:dyDescent="0.2">
@@ -31471,7 +31645,7 @@
         <v>1675</v>
       </c>
       <c r="B1766" s="18" t="s">
-        <v>4673</v>
+        <v>4670</v>
       </c>
     </row>
     <row r="1767" spans="1:2" x14ac:dyDescent="0.2">
@@ -31479,7 +31653,7 @@
         <v>1676</v>
       </c>
       <c r="B1767" s="18" t="s">
-        <v>4674</v>
+        <v>4671</v>
       </c>
     </row>
     <row r="1768" spans="1:2" x14ac:dyDescent="0.2">
@@ -31487,7 +31661,7 @@
         <v>1677</v>
       </c>
       <c r="B1768" s="18" t="s">
-        <v>4675</v>
+        <v>4672</v>
       </c>
     </row>
     <row r="1769" spans="1:2" x14ac:dyDescent="0.2">
@@ -31495,7 +31669,7 @@
         <v>1678</v>
       </c>
       <c r="B1769" s="18" t="s">
-        <v>4676</v>
+        <v>4673</v>
       </c>
     </row>
     <row r="1770" spans="1:2" x14ac:dyDescent="0.2">
@@ -31503,7 +31677,7 @@
         <v>1652</v>
       </c>
       <c r="B1770" s="18" t="s">
-        <v>4677</v>
+        <v>4674</v>
       </c>
     </row>
     <row r="1771" spans="1:2" x14ac:dyDescent="0.2">
@@ -31511,7 +31685,7 @@
         <v>1679</v>
       </c>
       <c r="B1771" s="18" t="s">
-        <v>4678</v>
+        <v>4675</v>
       </c>
     </row>
     <row r="1772" spans="1:2" x14ac:dyDescent="0.2">
@@ -31519,7 +31693,7 @@
         <v>1680</v>
       </c>
       <c r="B1772" s="18" t="s">
-        <v>4679</v>
+        <v>4676</v>
       </c>
     </row>
     <row r="1773" spans="1:2" x14ac:dyDescent="0.2">
@@ -31527,7 +31701,7 @@
         <v>1653</v>
       </c>
       <c r="B1773" s="18" t="s">
-        <v>4680</v>
+        <v>4677</v>
       </c>
     </row>
     <row r="1774" spans="1:2" x14ac:dyDescent="0.2">
@@ -31535,7 +31709,7 @@
         <v>1654</v>
       </c>
       <c r="B1774" s="18" t="s">
-        <v>4626</v>
+        <v>4623</v>
       </c>
     </row>
     <row r="1775" spans="1:2" x14ac:dyDescent="0.2">
@@ -31543,7 +31717,7 @@
         <v>1681</v>
       </c>
       <c r="B1775" s="18" t="s">
-        <v>4681</v>
+        <v>4678</v>
       </c>
     </row>
     <row r="1776" spans="1:2" x14ac:dyDescent="0.2">
@@ -31551,7 +31725,7 @@
         <v>1682</v>
       </c>
       <c r="B1776" s="18" t="s">
-        <v>4682</v>
+        <v>4679</v>
       </c>
     </row>
     <row r="1777" spans="1:2" x14ac:dyDescent="0.2">
@@ -31559,7 +31733,7 @@
         <v>1683</v>
       </c>
       <c r="B1777" s="18" t="s">
-        <v>4683</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="1778" spans="1:2" x14ac:dyDescent="0.2">
@@ -31567,7 +31741,7 @@
         <v>1684</v>
       </c>
       <c r="B1778" s="18" t="s">
-        <v>4684</v>
+        <v>4681</v>
       </c>
     </row>
     <row r="1779" spans="1:2" x14ac:dyDescent="0.2">
@@ -31575,7 +31749,7 @@
         <v>1685</v>
       </c>
       <c r="B1779" s="18" t="s">
-        <v>4685</v>
+        <v>4682</v>
       </c>
     </row>
     <row r="1780" spans="1:2" x14ac:dyDescent="0.2">
@@ -31583,7 +31757,7 @@
         <v>1686</v>
       </c>
       <c r="B1780" s="18" t="s">
-        <v>4686</v>
+        <v>4683</v>
       </c>
     </row>
     <row r="1781" spans="1:2" x14ac:dyDescent="0.2">
@@ -31591,7 +31765,7 @@
         <v>1656</v>
       </c>
       <c r="B1781" s="18" t="s">
-        <v>4687</v>
+        <v>4684</v>
       </c>
     </row>
     <row r="1782" spans="1:2" x14ac:dyDescent="0.2">
@@ -31599,7 +31773,7 @@
         <v>1687</v>
       </c>
       <c r="B1782" s="18" t="s">
-        <v>4688</v>
+        <v>4685</v>
       </c>
     </row>
     <row r="1783" spans="1:2" x14ac:dyDescent="0.2">
@@ -31607,7 +31781,7 @@
         <v>1657</v>
       </c>
       <c r="B1783" s="18" t="s">
-        <v>4689</v>
+        <v>4686</v>
       </c>
     </row>
     <row r="1784" spans="1:2" x14ac:dyDescent="0.2">
@@ -31615,7 +31789,7 @@
         <v>1688</v>
       </c>
       <c r="B1784" s="18" t="s">
-        <v>4690</v>
+        <v>4687</v>
       </c>
     </row>
     <row r="1785" spans="1:2" x14ac:dyDescent="0.2">
@@ -31623,7 +31797,7 @@
         <v>1658</v>
       </c>
       <c r="B1785" s="18" t="s">
-        <v>4691</v>
+        <v>4688</v>
       </c>
     </row>
     <row r="1786" spans="1:2" x14ac:dyDescent="0.2">
@@ -31631,7 +31805,7 @@
         <v>1689</v>
       </c>
       <c r="B1786" s="18" t="s">
-        <v>4692</v>
+        <v>4689</v>
       </c>
     </row>
     <row r="1787" spans="1:2" x14ac:dyDescent="0.2">
@@ -31639,7 +31813,7 @@
         <v>2875</v>
       </c>
       <c r="B1787" s="18" t="s">
-        <v>4693</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="1788" spans="1:2" x14ac:dyDescent="0.2">
@@ -31647,7 +31821,7 @@
         <v>2876</v>
       </c>
       <c r="B1788" s="18" t="s">
-        <v>4694</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="1789" spans="1:2" x14ac:dyDescent="0.2">
@@ -31655,7 +31829,7 @@
         <v>2877</v>
       </c>
       <c r="B1789" s="18" t="s">
-        <v>4695</v>
+        <v>4692</v>
       </c>
     </row>
     <row r="1790" spans="1:2" x14ac:dyDescent="0.2">
@@ -31663,7 +31837,7 @@
         <v>2879</v>
       </c>
       <c r="B1790" s="18" t="s">
-        <v>4696</v>
+        <v>4693</v>
       </c>
     </row>
     <row r="1791" spans="1:2" x14ac:dyDescent="0.2">
@@ -31679,7 +31853,7 @@
         <v>2882</v>
       </c>
       <c r="B1792" s="18" t="s">
-        <v>4697</v>
+        <v>4694</v>
       </c>
     </row>
     <row r="1793" spans="1:2" x14ac:dyDescent="0.2">
@@ -31687,7 +31861,7 @@
         <v>2883</v>
       </c>
       <c r="B1793" s="18" t="s">
-        <v>4698</v>
+        <v>4695</v>
       </c>
     </row>
     <row r="1794" spans="1:2" x14ac:dyDescent="0.2">
@@ -31695,7 +31869,7 @@
         <v>2874</v>
       </c>
       <c r="B1794" s="18" t="s">
-        <v>4697</v>
+        <v>4694</v>
       </c>
     </row>
     <row r="1795" spans="1:2" x14ac:dyDescent="0.2">
@@ -31703,7 +31877,7 @@
         <v>2884</v>
       </c>
       <c r="B1795" s="18" t="s">
-        <v>4699</v>
+        <v>4696</v>
       </c>
     </row>
     <row r="1796" spans="1:2" x14ac:dyDescent="0.2">
@@ -31711,7 +31885,7 @@
         <v>2885</v>
       </c>
       <c r="B1796" s="18" t="s">
-        <v>4700</v>
+        <v>4697</v>
       </c>
     </row>
     <row r="1797" spans="1:2" x14ac:dyDescent="0.2">
@@ -31719,7 +31893,7 @@
         <v>2886</v>
       </c>
       <c r="B1797" s="18" t="s">
-        <v>4701</v>
+        <v>4698</v>
       </c>
     </row>
     <row r="1798" spans="1:2" x14ac:dyDescent="0.2">
@@ -31727,7 +31901,7 @@
         <v>2887</v>
       </c>
       <c r="B1798" s="18" t="s">
-        <v>4702</v>
+        <v>4699</v>
       </c>
     </row>
     <row r="1799" spans="1:2" x14ac:dyDescent="0.2">
@@ -31735,7 +31909,7 @@
         <v>2888</v>
       </c>
       <c r="B1799" s="18" t="s">
-        <v>4703</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="1800" spans="1:2" x14ac:dyDescent="0.2">
@@ -31743,7 +31917,7 @@
         <v>2889</v>
       </c>
       <c r="B1800" s="18" t="s">
-        <v>4704</v>
+        <v>4701</v>
       </c>
     </row>
     <row r="1801" spans="1:2" x14ac:dyDescent="0.2">
@@ -31751,7 +31925,7 @@
         <v>2890</v>
       </c>
       <c r="B1801" s="18" t="s">
-        <v>4705</v>
+        <v>4702</v>
       </c>
     </row>
     <row r="1802" spans="1:2" x14ac:dyDescent="0.2">
@@ -31759,7 +31933,7 @@
         <v>2891</v>
       </c>
       <c r="B1802" s="18" t="s">
-        <v>4706</v>
+        <v>4703</v>
       </c>
     </row>
     <row r="1803" spans="1:2" x14ac:dyDescent="0.2">
@@ -31767,7 +31941,7 @@
         <v>2892</v>
       </c>
       <c r="B1803" s="18" t="s">
-        <v>4707</v>
+        <v>4704</v>
       </c>
     </row>
     <row r="1804" spans="1:2" x14ac:dyDescent="0.2">
@@ -31775,7 +31949,7 @@
         <v>2893</v>
       </c>
       <c r="B1804" s="18" t="s">
-        <v>4708</v>
+        <v>4705</v>
       </c>
     </row>
     <row r="1805" spans="1:2" x14ac:dyDescent="0.2">
@@ -31783,7 +31957,7 @@
         <v>2894</v>
       </c>
       <c r="B1805" s="18" t="s">
-        <v>4709</v>
+        <v>4706</v>
       </c>
     </row>
     <row r="1806" spans="1:2" x14ac:dyDescent="0.2">
@@ -31791,7 +31965,7 @@
         <v>2895</v>
       </c>
       <c r="B1806" s="18" t="s">
-        <v>4601</v>
+        <v>4599</v>
       </c>
     </row>
     <row r="1807" spans="1:2" x14ac:dyDescent="0.2">
@@ -31799,7 +31973,7 @@
         <v>2896</v>
       </c>
       <c r="B1807" s="18" t="s">
-        <v>4710</v>
+        <v>4707</v>
       </c>
     </row>
     <row r="1808" spans="1:2" x14ac:dyDescent="0.2">
@@ -31807,7 +31981,7 @@
         <v>2897</v>
       </c>
       <c r="B1808" s="18" t="s">
-        <v>4711</v>
+        <v>4708</v>
       </c>
     </row>
     <row r="1809" spans="1:4" x14ac:dyDescent="0.2">
@@ -31815,7 +31989,7 @@
         <v>2898</v>
       </c>
       <c r="B1809" s="18" t="s">
-        <v>4712</v>
+        <v>4709</v>
       </c>
     </row>
     <row r="1810" spans="1:4" x14ac:dyDescent="0.2">
@@ -31823,7 +31997,7 @@
         <v>2899</v>
       </c>
       <c r="B1810" s="18" t="s">
-        <v>4713</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="1811" spans="1:4" x14ac:dyDescent="0.2">
@@ -31839,7 +32013,7 @@
         <v>2901</v>
       </c>
       <c r="B1812" s="18" t="s">
-        <v>4714</v>
+        <v>4711</v>
       </c>
       <c r="C1812"/>
       <c r="D1812"/>
@@ -31849,7 +32023,7 @@
         <v>2902</v>
       </c>
       <c r="B1813" s="18" t="s">
-        <v>4715</v>
+        <v>4712</v>
       </c>
       <c r="C1813"/>
       <c r="D1813"/>
@@ -31859,7 +32033,7 @@
         <v>2903</v>
       </c>
       <c r="B1814" s="18" t="s">
-        <v>4716</v>
+        <v>4713</v>
       </c>
       <c r="C1814"/>
       <c r="D1814"/>
@@ -31869,7 +32043,7 @@
         <v>2904</v>
       </c>
       <c r="B1815" s="18" t="s">
-        <v>4717</v>
+        <v>4714</v>
       </c>
       <c r="C1815"/>
       <c r="D1815"/>
@@ -31879,7 +32053,7 @@
         <v>2905</v>
       </c>
       <c r="B1816" s="18" t="s">
-        <v>4718</v>
+        <v>4715</v>
       </c>
       <c r="C1816"/>
       <c r="D1816"/>
@@ -31889,7 +32063,7 @@
         <v>2906</v>
       </c>
       <c r="B1817" s="18" t="s">
-        <v>4719</v>
+        <v>4716</v>
       </c>
       <c r="C1817"/>
       <c r="D1817"/>
@@ -31899,7 +32073,7 @@
         <v>2907</v>
       </c>
       <c r="B1818" s="18" t="s">
-        <v>4720</v>
+        <v>4717</v>
       </c>
       <c r="C1818"/>
       <c r="D1818"/>
@@ -31909,7 +32083,7 @@
         <v>2908</v>
       </c>
       <c r="B1819" s="18" t="s">
-        <v>4721</v>
+        <v>4718</v>
       </c>
       <c r="C1819"/>
       <c r="D1819"/>
@@ -31919,7 +32093,7 @@
         <v>2909</v>
       </c>
       <c r="B1820" s="18" t="s">
-        <v>4722</v>
+        <v>4719</v>
       </c>
       <c r="C1820"/>
       <c r="D1820"/>
@@ -31929,7 +32103,7 @@
         <v>2910</v>
       </c>
       <c r="B1821" s="18" t="s">
-        <v>4723</v>
+        <v>4720</v>
       </c>
       <c r="C1821"/>
       <c r="D1821"/>
@@ -31939,7 +32113,7 @@
         <v>2919</v>
       </c>
       <c r="B1822" s="18" t="s">
-        <v>4724</v>
+        <v>4721</v>
       </c>
       <c r="C1822"/>
       <c r="D1822"/>
@@ -31949,7 +32123,7 @@
         <v>2918</v>
       </c>
       <c r="B1823" s="18" t="s">
-        <v>4725</v>
+        <v>4722</v>
       </c>
       <c r="C1823"/>
       <c r="D1823"/>
@@ -31959,7 +32133,7 @@
         <v>2920</v>
       </c>
       <c r="B1824" s="18" t="s">
-        <v>4726</v>
+        <v>4723</v>
       </c>
       <c r="C1824"/>
       <c r="D1824"/>
@@ -31969,7 +32143,7 @@
         <v>2921</v>
       </c>
       <c r="B1825" s="18" t="s">
-        <v>4727</v>
+        <v>4724</v>
       </c>
       <c r="C1825"/>
       <c r="D1825"/>
@@ -31979,7 +32153,7 @@
         <v>2922</v>
       </c>
       <c r="B1826" s="18" t="s">
-        <v>4728</v>
+        <v>4725</v>
       </c>
       <c r="C1826"/>
       <c r="D1826"/>
@@ -31989,7 +32163,7 @@
         <v>2923</v>
       </c>
       <c r="B1827" s="18" t="s">
-        <v>4729</v>
+        <v>4726</v>
       </c>
       <c r="C1827"/>
       <c r="D1827"/>
@@ -31999,7 +32173,7 @@
         <v>2944</v>
       </c>
       <c r="B1828" s="18" t="s">
-        <v>4730</v>
+        <v>4727</v>
       </c>
       <c r="C1828"/>
       <c r="D1828"/>
@@ -32009,7 +32183,7 @@
         <v>2924</v>
       </c>
       <c r="B1829" s="18" t="s">
-        <v>4731</v>
+        <v>4728</v>
       </c>
       <c r="C1829"/>
       <c r="D1829"/>
@@ -32019,7 +32193,7 @@
         <v>2925</v>
       </c>
       <c r="B1830" s="18" t="s">
-        <v>4732</v>
+        <v>4729</v>
       </c>
       <c r="C1830"/>
       <c r="D1830"/>
@@ -32029,7 +32203,7 @@
         <v>2926</v>
       </c>
       <c r="B1831" s="18" t="s">
-        <v>4733</v>
+        <v>4730</v>
       </c>
       <c r="C1831"/>
       <c r="D1831"/>
@@ -32039,7 +32213,7 @@
         <v>2927</v>
       </c>
       <c r="B1832" s="18" t="s">
-        <v>4734</v>
+        <v>4731</v>
       </c>
       <c r="C1832"/>
       <c r="D1832"/>
@@ -32049,7 +32223,7 @@
         <v>2928</v>
       </c>
       <c r="B1833" s="18" t="s">
-        <v>4735</v>
+        <v>4732</v>
       </c>
       <c r="C1833"/>
       <c r="D1833"/>
@@ -32059,7 +32233,7 @@
         <v>2929</v>
       </c>
       <c r="B1834" s="18" t="s">
-        <v>4736</v>
+        <v>4733</v>
       </c>
       <c r="C1834"/>
       <c r="D1834"/>
@@ -32069,7 +32243,7 @@
         <v>2930</v>
       </c>
       <c r="B1835" s="18" t="s">
-        <v>4737</v>
+        <v>4734</v>
       </c>
       <c r="C1835"/>
       <c r="D1835"/>
@@ -32079,7 +32253,7 @@
         <v>2931</v>
       </c>
       <c r="B1836" s="18" t="s">
-        <v>4738</v>
+        <v>4735</v>
       </c>
       <c r="C1836"/>
       <c r="D1836"/>
@@ -32089,7 +32263,7 @@
         <v>2932</v>
       </c>
       <c r="B1837" s="18" t="s">
-        <v>4739</v>
+        <v>4736</v>
       </c>
       <c r="C1837"/>
       <c r="D1837"/>
@@ -32099,7 +32273,7 @@
         <v>2933</v>
       </c>
       <c r="B1838" s="18" t="s">
-        <v>4740</v>
+        <v>4737</v>
       </c>
       <c r="C1838"/>
       <c r="D1838"/>
@@ -32109,7 +32283,7 @@
         <v>2934</v>
       </c>
       <c r="B1839" s="18" t="s">
-        <v>4741</v>
+        <v>4738</v>
       </c>
       <c r="C1839"/>
       <c r="D1839"/>
@@ -32119,7 +32293,7 @@
         <v>2935</v>
       </c>
       <c r="B1840" s="18" t="s">
-        <v>4742</v>
+        <v>4739</v>
       </c>
       <c r="C1840"/>
       <c r="D1840"/>
@@ -32129,7 +32303,7 @@
         <v>2936</v>
       </c>
       <c r="B1841" s="18" t="s">
-        <v>4743</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="1842" spans="1:2" x14ac:dyDescent="0.2">
@@ -32137,7 +32311,7 @@
         <v>2937</v>
       </c>
       <c r="B1842" s="18" t="s">
-        <v>4744</v>
+        <v>4741</v>
       </c>
     </row>
     <row r="1843" spans="1:2" x14ac:dyDescent="0.2">
@@ -32145,7 +32319,7 @@
         <v>2938</v>
       </c>
       <c r="B1843" s="18" t="s">
-        <v>4745</v>
+        <v>4742</v>
       </c>
     </row>
     <row r="1844" spans="1:2" x14ac:dyDescent="0.2">
@@ -32153,7 +32327,7 @@
         <v>2945</v>
       </c>
       <c r="B1844" s="18" t="s">
-        <v>4746</v>
+        <v>4743</v>
       </c>
     </row>
     <row r="1845" spans="1:2" x14ac:dyDescent="0.2">
@@ -32161,7 +32335,7 @@
         <v>2939</v>
       </c>
       <c r="B1845" s="18" t="s">
-        <v>4747</v>
+        <v>4744</v>
       </c>
     </row>
     <row r="1846" spans="1:2" x14ac:dyDescent="0.2">
@@ -32169,7 +32343,7 @@
         <v>2940</v>
       </c>
       <c r="B1846" s="18" t="s">
-        <v>4748</v>
+        <v>4745</v>
       </c>
     </row>
     <row r="1847" spans="1:2" x14ac:dyDescent="0.2">
@@ -32177,7 +32351,7 @@
         <v>2941</v>
       </c>
       <c r="B1847" s="18" t="s">
-        <v>4749</v>
+        <v>4746</v>
       </c>
     </row>
     <row r="1848" spans="1:2" x14ac:dyDescent="0.2">
@@ -32185,7 +32359,7 @@
         <v>2942</v>
       </c>
       <c r="B1848" s="18" t="s">
-        <v>4750</v>
+        <v>4747</v>
       </c>
     </row>
     <row r="1849" spans="1:2" x14ac:dyDescent="0.2">
@@ -32193,7 +32367,7 @@
         <v>2943</v>
       </c>
       <c r="B1849" s="18" t="s">
-        <v>4751</v>
+        <v>4748</v>
       </c>
     </row>
     <row r="1850" spans="1:2" x14ac:dyDescent="0.2">
@@ -32201,7 +32375,7 @@
         <v>2946</v>
       </c>
       <c r="B1850" s="18" t="s">
-        <v>4752</v>
+        <v>4749</v>
       </c>
     </row>
     <row r="1851" spans="1:2" x14ac:dyDescent="0.2">
@@ -32209,7 +32383,7 @@
         <v>2947</v>
       </c>
       <c r="B1851" s="18" t="s">
-        <v>4753</v>
+        <v>4750</v>
       </c>
     </row>
     <row r="1852" spans="1:2" x14ac:dyDescent="0.2">
@@ -32217,7 +32391,7 @@
         <v>2948</v>
       </c>
       <c r="B1852" s="18" t="s">
-        <v>4754</v>
+        <v>4751</v>
       </c>
     </row>
     <row r="1853" spans="1:2" x14ac:dyDescent="0.2">
@@ -32225,7 +32399,7 @@
         <v>2949</v>
       </c>
       <c r="B1853" s="18" t="s">
-        <v>4755</v>
+        <v>4752</v>
       </c>
     </row>
     <row r="1854" spans="1:2" x14ac:dyDescent="0.2">
@@ -32233,7 +32407,7 @@
         <v>2950</v>
       </c>
       <c r="B1854" s="18" t="s">
-        <v>4756</v>
+        <v>4753</v>
       </c>
     </row>
     <row r="1855" spans="1:2" x14ac:dyDescent="0.2">
@@ -32241,7 +32415,7 @@
         <v>2951</v>
       </c>
       <c r="B1855" s="18" t="s">
-        <v>4757</v>
+        <v>4754</v>
       </c>
     </row>
     <row r="1856" spans="1:2" x14ac:dyDescent="0.2">
@@ -32249,7 +32423,7 @@
         <v>2952</v>
       </c>
       <c r="B1856" s="18" t="s">
-        <v>4758</v>
+        <v>4755</v>
       </c>
     </row>
     <row r="1857" spans="1:2" x14ac:dyDescent="0.2">
@@ -32257,7 +32431,7 @@
         <v>2953</v>
       </c>
       <c r="B1857" s="18" t="s">
-        <v>4759</v>
+        <v>4756</v>
       </c>
     </row>
     <row r="1858" spans="1:2" x14ac:dyDescent="0.2">
@@ -32265,7 +32439,7 @@
         <v>2954</v>
       </c>
       <c r="B1858" s="18" t="s">
-        <v>4760</v>
+        <v>4757</v>
       </c>
     </row>
     <row r="1859" spans="1:2" x14ac:dyDescent="0.2">
@@ -32273,7 +32447,7 @@
         <v>2955</v>
       </c>
       <c r="B1859" s="18" t="s">
-        <v>4761</v>
+        <v>4758</v>
       </c>
     </row>
     <row r="1860" spans="1:2" x14ac:dyDescent="0.2">
@@ -32281,7 +32455,7 @@
         <v>2956</v>
       </c>
       <c r="B1860" s="18" t="s">
-        <v>4762</v>
+        <v>4759</v>
       </c>
     </row>
     <row r="1861" spans="1:2" x14ac:dyDescent="0.2">
@@ -32289,7 +32463,7 @@
         <v>2957</v>
       </c>
       <c r="B1861" s="18" t="s">
-        <v>4763</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="1862" spans="1:2" x14ac:dyDescent="0.2">
@@ -32297,7 +32471,7 @@
         <v>2958</v>
       </c>
       <c r="B1862" s="18" t="s">
-        <v>4764</v>
+        <v>4761</v>
       </c>
     </row>
     <row r="1863" spans="1:2" x14ac:dyDescent="0.2">
@@ -32305,7 +32479,7 @@
         <v>2959</v>
       </c>
       <c r="B1863" s="18" t="s">
-        <v>4765</v>
+        <v>4762</v>
       </c>
     </row>
     <row r="1864" spans="1:2" x14ac:dyDescent="0.2">
@@ -32313,7 +32487,7 @@
         <v>2960</v>
       </c>
       <c r="B1864" s="18" t="s">
-        <v>4766</v>
+        <v>4763</v>
       </c>
     </row>
     <row r="1865" spans="1:2" x14ac:dyDescent="0.2">
@@ -32321,7 +32495,7 @@
         <v>2961</v>
       </c>
       <c r="B1865" s="18" t="s">
-        <v>4767</v>
+        <v>4764</v>
       </c>
     </row>
     <row r="1866" spans="1:2" x14ac:dyDescent="0.2">
@@ -32329,8 +32503,382 @@
         <v>2962</v>
       </c>
       <c r="B1866" s="18" t="s">
-        <v>4768</v>
-      </c>
+        <v>4765</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1867" s="1" t="s">
+        <v>4861</v>
+      </c>
+      <c r="B1867" s="18" t="s">
+        <v>4888</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1868" s="1" t="s">
+        <v>4862</v>
+      </c>
+      <c r="B1868" s="18" t="s">
+        <v>4889</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1869" s="1" t="s">
+        <v>4863</v>
+      </c>
+      <c r="B1869" s="18" t="s">
+        <v>4890</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1870" s="1" t="s">
+        <v>4864</v>
+      </c>
+      <c r="B1870" s="18" t="s">
+        <v>4891</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1871" s="1" t="s">
+        <v>4865</v>
+      </c>
+      <c r="B1871" s="18" t="s">
+        <v>4892</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1872" s="1" t="s">
+        <v>4866</v>
+      </c>
+      <c r="B1872" s="18" t="s">
+        <v>4893</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1873" s="1" t="s">
+        <v>4867</v>
+      </c>
+      <c r="B1873" s="18" t="s">
+        <v>4894</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1874" s="1" t="s">
+        <v>4868</v>
+      </c>
+      <c r="B1874" s="18" t="s">
+        <v>4910</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1875" s="1" t="s">
+        <v>4869</v>
+      </c>
+      <c r="B1875" s="18" t="s">
+        <v>4911</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1876" s="1" t="s">
+        <v>4870</v>
+      </c>
+      <c r="B1876" s="18" t="s">
+        <v>4912</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1877" s="1" t="s">
+        <v>4871</v>
+      </c>
+      <c r="B1877" s="18" t="s">
+        <v>4913</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1878" s="1" t="s">
+        <v>4914</v>
+      </c>
+      <c r="B1878" s="18" t="s">
+        <v>4915</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1879" s="1" t="s">
+        <v>4872</v>
+      </c>
+      <c r="B1879" s="18" t="s">
+        <v>4916</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1880" s="1" t="s">
+        <v>4873</v>
+      </c>
+      <c r="B1880" s="18" t="s">
+        <v>4895</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1881" s="1" t="s">
+        <v>4874</v>
+      </c>
+      <c r="B1881" s="18" t="s">
+        <v>4896</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1882" s="1" t="s">
+        <v>4875</v>
+      </c>
+      <c r="B1882" s="18" t="s">
+        <v>4897</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1883" s="1" t="s">
+        <v>4876</v>
+      </c>
+      <c r="B1883" s="18" t="s">
+        <v>4898</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1884" s="1" t="s">
+        <v>4877</v>
+      </c>
+      <c r="B1884" s="18" t="s">
+        <v>4899</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1885" s="1" t="s">
+        <v>4878</v>
+      </c>
+      <c r="B1885" s="18" t="s">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1886" s="1" t="s">
+        <v>4879</v>
+      </c>
+      <c r="B1886" s="18" t="s">
+        <v>4901</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1887" s="1" t="s">
+        <v>4880</v>
+      </c>
+      <c r="B1887" s="18" t="s">
+        <v>4902</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1888" s="1" t="s">
+        <v>4881</v>
+      </c>
+      <c r="B1888" s="18" t="s">
+        <v>4903</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1889" s="1" t="s">
+        <v>4882</v>
+      </c>
+      <c r="B1889" s="18" t="s">
+        <v>4904</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1890" s="1" t="s">
+        <v>4883</v>
+      </c>
+      <c r="B1890" s="18" t="s">
+        <v>4905</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1891" s="1" t="s">
+        <v>4884</v>
+      </c>
+      <c r="B1891" s="18" t="s">
+        <v>4906</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1892" s="1" t="s">
+        <v>4885</v>
+      </c>
+      <c r="B1892" s="18" t="s">
+        <v>4907</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1893" s="1" t="s">
+        <v>4886</v>
+      </c>
+      <c r="B1893" s="18" t="s">
+        <v>4908</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1894" s="1" t="s">
+        <v>4887</v>
+      </c>
+      <c r="B1894" s="18" t="s">
+        <v>4909</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1895"/>
+      <c r="B1895"/>
+      <c r="C1895"/>
+      <c r="D1895"/>
+    </row>
+    <row r="1896" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1896"/>
+      <c r="B1896"/>
+      <c r="C1896"/>
+      <c r="D1896"/>
+    </row>
+    <row r="1897" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1897"/>
+      <c r="B1897"/>
+      <c r="C1897"/>
+      <c r="D1897"/>
+    </row>
+    <row r="1898" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1898"/>
+      <c r="B1898"/>
+      <c r="C1898"/>
+      <c r="D1898"/>
+    </row>
+    <row r="1899" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1899"/>
+      <c r="B1899"/>
+      <c r="C1899"/>
+      <c r="D1899"/>
+    </row>
+    <row r="1900" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1900"/>
+      <c r="B1900"/>
+      <c r="C1900"/>
+      <c r="D1900"/>
+    </row>
+    <row r="1901" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1901"/>
+      <c r="B1901"/>
+      <c r="C1901"/>
+      <c r="D1901"/>
+    </row>
+    <row r="1902" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1902"/>
+      <c r="B1902"/>
+      <c r="C1902"/>
+      <c r="D1902"/>
+    </row>
+    <row r="1903" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1903"/>
+      <c r="B1903"/>
+      <c r="C1903"/>
+      <c r="D1903"/>
+    </row>
+    <row r="1904" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1904"/>
+      <c r="B1904"/>
+      <c r="C1904"/>
+      <c r="D1904"/>
+    </row>
+    <row r="1905" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1905"/>
+      <c r="B1905"/>
+      <c r="C1905"/>
+      <c r="D1905"/>
+    </row>
+    <row r="1906" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1906"/>
+      <c r="B1906"/>
+      <c r="C1906"/>
+      <c r="D1906"/>
+    </row>
+    <row r="1907" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1907"/>
+      <c r="B1907"/>
+      <c r="C1907"/>
+      <c r="D1907"/>
+    </row>
+    <row r="1908" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1908"/>
+      <c r="B1908"/>
+      <c r="C1908"/>
+      <c r="D1908"/>
+    </row>
+    <row r="1909" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1909"/>
+      <c r="B1909"/>
+      <c r="C1909"/>
+      <c r="D1909"/>
+    </row>
+    <row r="1910" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1910"/>
+      <c r="B1910"/>
+      <c r="C1910"/>
+      <c r="D1910"/>
+    </row>
+    <row r="1911" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1911"/>
+      <c r="B1911"/>
+      <c r="C1911"/>
+      <c r="D1911"/>
+    </row>
+    <row r="1912" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1912"/>
+      <c r="B1912"/>
+      <c r="C1912"/>
+      <c r="D1912"/>
+    </row>
+    <row r="1913" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1913"/>
+      <c r="B1913"/>
+      <c r="C1913"/>
+      <c r="D1913"/>
+    </row>
+    <row r="1914" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1914"/>
+      <c r="B1914"/>
+      <c r="C1914"/>
+      <c r="D1914"/>
+    </row>
+    <row r="1915" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1915"/>
+      <c r="B1915"/>
+      <c r="C1915"/>
+      <c r="D1915"/>
+    </row>
+    <row r="1916" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1916"/>
+      <c r="B1916"/>
+      <c r="C1916"/>
+      <c r="D1916"/>
+    </row>
+    <row r="1917" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1917"/>
+      <c r="B1917"/>
+      <c r="C1917"/>
+      <c r="D1917"/>
+    </row>
+    <row r="1918" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1918"/>
+      <c r="B1918"/>
+      <c r="C1918"/>
+      <c r="D1918"/>
+    </row>
+    <row r="1919" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1919"/>
+      <c r="B1919"/>
+      <c r="C1919"/>
+      <c r="D1919"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Datas/LanguageSwitchDataList.xlsx
+++ b/Datas/LanguageSwitchDataList.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4937" uniqueCount="4917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4967" uniqueCount="4947">
   <si>
     <t>string</t>
   </si>
@@ -16914,6 +16914,96 @@
   <si>
     <t>Basic Barn</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Casual</t>
+  </si>
+  <si>
+    <t>Friendly</t>
+  </si>
+  <si>
+    <t>Familiar</t>
+  </si>
+  <si>
+    <t>Trust</t>
+  </si>
+  <si>
+    <t>Tuned</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+  <si>
+    <t>Deep</t>
+  </si>
+  <si>
+    <t>Intimate</t>
+  </si>
+  <si>
+    <t>Confidant</t>
+  </si>
+  <si>
+    <t>Intro</t>
+  </si>
+  <si>
+    <t>初识</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>友善</t>
+  </si>
+  <si>
+    <t>熟悉</t>
+  </si>
+  <si>
+    <t>信赖</t>
+  </si>
+  <si>
+    <t>默契</t>
+  </si>
+  <si>
+    <t>亲近</t>
+  </si>
+  <si>
+    <t>深厚</t>
+  </si>
+  <si>
+    <t>挚友</t>
+  </si>
+  <si>
+    <t>知交</t>
+  </si>
+  <si>
+    <t>好感度到达&lt;color=green&gt;Lv.2&lt;/color&gt;后可邀请组队，一起进行冒险</t>
+  </si>
+  <si>
+    <t>好感度到达&lt;color=green&gt;Lv.10&lt;/color&gt;后可以对单身异性进行表白，成为情侣</t>
+  </si>
+  <si>
+    <t>每天前&lt;color=red&gt;3&lt;/color&gt;次对话可以增加好感度</t>
+  </si>
+  <si>
+    <t>每天前&lt;color=red&gt;3&lt;/color&gt;次礼物可以增加好感度</t>
+  </si>
+  <si>
+    <t>每天前&lt;color=red&gt;2&lt;/color&gt;次组队探险可以增加好感度</t>
+  </si>
+  <si>
+    <t>Once the affection reaches &lt;color=green&gt;Lv.2&lt;/color&gt;, you can invite to team up and adventure together.</t>
+  </si>
+  <si>
+    <t>Once the affection reaches &lt;color=green&gt;Lv.10&lt;/color&gt;, you can confess to a single opposite gender and become a couple.</t>
+  </si>
+  <si>
+    <t>The first &lt;color=red&gt;3&lt;/color&gt; conversations each day can increase affection.</t>
+  </si>
+  <si>
+    <t>The first &lt;color=red&gt;3&lt;/color&gt; gifts each day can increase affection.</t>
+  </si>
+  <si>
+    <t>The first &lt;color=red&gt;2&lt;/color&gt; team adventures each day can increase affection.</t>
   </si>
 </sst>
 </file>
@@ -17015,7 +17105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -17067,6 +17157,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -32731,92 +32824,152 @@
       </c>
     </row>
     <row r="1895" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1895"/>
-      <c r="B1895"/>
+      <c r="A1895" t="s">
+        <v>4927</v>
+      </c>
+      <c r="B1895" t="s">
+        <v>4926</v>
+      </c>
       <c r="C1895"/>
       <c r="D1895"/>
     </row>
     <row r="1896" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1896"/>
-      <c r="B1896"/>
+      <c r="A1896" t="s">
+        <v>4928</v>
+      </c>
+      <c r="B1896" t="s">
+        <v>4917</v>
+      </c>
       <c r="C1896"/>
       <c r="D1896"/>
     </row>
     <row r="1897" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1897"/>
-      <c r="B1897"/>
+      <c r="A1897" t="s">
+        <v>4929</v>
+      </c>
+      <c r="B1897" t="s">
+        <v>4918</v>
+      </c>
       <c r="C1897"/>
       <c r="D1897"/>
     </row>
     <row r="1898" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1898"/>
-      <c r="B1898"/>
+      <c r="A1898" t="s">
+        <v>4930</v>
+      </c>
+      <c r="B1898" t="s">
+        <v>4919</v>
+      </c>
       <c r="C1898"/>
       <c r="D1898"/>
     </row>
     <row r="1899" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1899"/>
-      <c r="B1899"/>
+      <c r="A1899" t="s">
+        <v>4931</v>
+      </c>
+      <c r="B1899" t="s">
+        <v>4920</v>
+      </c>
       <c r="C1899"/>
       <c r="D1899"/>
     </row>
     <row r="1900" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1900"/>
-      <c r="B1900"/>
+      <c r="A1900" t="s">
+        <v>4932</v>
+      </c>
+      <c r="B1900" t="s">
+        <v>4921</v>
+      </c>
       <c r="C1900"/>
       <c r="D1900"/>
     </row>
     <row r="1901" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1901"/>
-      <c r="B1901"/>
+      <c r="A1901" t="s">
+        <v>4933</v>
+      </c>
+      <c r="B1901" t="s">
+        <v>4922</v>
+      </c>
       <c r="C1901"/>
       <c r="D1901"/>
     </row>
     <row r="1902" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1902"/>
-      <c r="B1902"/>
+      <c r="A1902" t="s">
+        <v>4934</v>
+      </c>
+      <c r="B1902" t="s">
+        <v>4923</v>
+      </c>
       <c r="C1902"/>
       <c r="D1902"/>
     </row>
     <row r="1903" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1903"/>
-      <c r="B1903"/>
+      <c r="A1903" t="s">
+        <v>4935</v>
+      </c>
+      <c r="B1903" t="s">
+        <v>4924</v>
+      </c>
       <c r="C1903"/>
       <c r="D1903"/>
     </row>
     <row r="1904" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1904"/>
-      <c r="B1904"/>
+      <c r="A1904" t="s">
+        <v>4936</v>
+      </c>
+      <c r="B1904" t="s">
+        <v>4925</v>
+      </c>
       <c r="C1904"/>
       <c r="D1904"/>
     </row>
     <row r="1905" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1905"/>
-      <c r="B1905"/>
+      <c r="A1905" t="s">
+        <v>4937</v>
+      </c>
+      <c r="B1905" s="21" t="s">
+        <v>4942</v>
+      </c>
       <c r="C1905"/>
       <c r="D1905"/>
     </row>
     <row r="1906" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1906"/>
-      <c r="B1906"/>
+      <c r="A1906" t="s">
+        <v>4938</v>
+      </c>
+      <c r="B1906" s="21" t="s">
+        <v>4943</v>
+      </c>
       <c r="C1906"/>
       <c r="D1906"/>
     </row>
     <row r="1907" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1907"/>
-      <c r="B1907"/>
+      <c r="A1907" t="s">
+        <v>4939</v>
+      </c>
+      <c r="B1907" s="21" t="s">
+        <v>4944</v>
+      </c>
       <c r="C1907"/>
       <c r="D1907"/>
     </row>
     <row r="1908" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1908"/>
-      <c r="B1908"/>
+      <c r="A1908" t="s">
+        <v>4940</v>
+      </c>
+      <c r="B1908" s="21" t="s">
+        <v>4945</v>
+      </c>
       <c r="C1908"/>
       <c r="D1908"/>
     </row>
     <row r="1909" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1909"/>
-      <c r="B1909"/>
+      <c r="A1909" t="s">
+        <v>4941</v>
+      </c>
+      <c r="B1909" s="21" t="s">
+        <v>4946</v>
+      </c>
       <c r="C1909"/>
       <c r="D1909"/>
     </row>

--- a/Datas/LanguageSwitchDataList.xlsx
+++ b/Datas/LanguageSwitchDataList.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4967" uniqueCount="4947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4985" uniqueCount="4965">
   <si>
     <t>string</t>
   </si>
@@ -17005,12 +17005,82 @@
   <si>
     <t>The first &lt;color=red&gt;2&lt;/color&gt; team adventures each day can increase affection.</t>
   </si>
+  <si>
+    <t>公示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亲爱的小伙伴们，大家好，我是一名独立游戏制作者，这个游戏是我在工作之余独自一人开发的。由于需要兼顾工作，一些功能做的比较仓促，请大家见谅啦，我会继续开发下去，修复bug，优化体验，把没有制作的功能开发下去。 
+大家如果对游戏有什么想法可以发电子邮件给我，邮件我会仔细阅读。我的邮件地址是:shanflyer@qq.com
+如果意见被采纳，我会将您加入到贡献名单中，让这个游戏变成我们大家的游戏吧！
+如果您愿意支援我，我更会努力完成我们的愿望，谢谢大家。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点赞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分享</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贡献名单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赞助</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支援</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>为游戏做出贡献的小伙伴们：</t>
+  </si>
+  <si>
+    <t>Dear friends,
+Hello everyone! I am an independent game developer, and this game was created entirely by me during my spare time while balancing my full-time job. Due to limited availability, some features may feel rushed—thank you for your understanding! I will continue developing the game, fixing bugs, improving the experience, and adding unfinished features.
+If you have any ideas or feedback, please email me at shanflyer@qq.com. I read every message carefully. If your suggestions are adopted, I will add your name to the Contributors list. Let’s make this game our game together!
+If you’d like to support my work, your encouragement will fuel my efforts to achieve our shared vision. Thank you!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Like</t>
+  </si>
+  <si>
+    <t>Share</t>
+  </si>
+  <si>
+    <t>Contributors</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>Sponsor</t>
+  </si>
+  <si>
+    <t>Contribute</t>
+  </si>
+  <si>
+    <t>To all contributors who helped shape this game!</t>
+  </si>
+  <si>
+    <t>Bulletin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -17056,6 +17126,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF404040"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -17105,7 +17181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -17160,6 +17236,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -32974,56 +33051,92 @@
       <c r="D1909"/>
     </row>
     <row r="1910" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1910"/>
-      <c r="B1910"/>
+      <c r="A1910" t="s">
+        <v>4947</v>
+      </c>
+      <c r="B1910" t="s">
+        <v>4964</v>
+      </c>
       <c r="C1910"/>
       <c r="D1910"/>
     </row>
-    <row r="1911" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1911"/>
-      <c r="B1911"/>
+    <row r="1911" spans="1:4" ht="213.75" x14ac:dyDescent="0.2">
+      <c r="A1911" s="1" t="s">
+        <v>4948</v>
+      </c>
+      <c r="B1911" s="1" t="s">
+        <v>4956</v>
+      </c>
       <c r="C1911"/>
       <c r="D1911"/>
     </row>
-    <row r="1912" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1912"/>
-      <c r="B1912"/>
+    <row r="1912" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1912" t="s">
+        <v>4949</v>
+      </c>
+      <c r="B1912" s="22" t="s">
+        <v>4957</v>
+      </c>
       <c r="C1912"/>
       <c r="D1912"/>
     </row>
-    <row r="1913" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1913"/>
-      <c r="B1913"/>
+    <row r="1913" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1913" t="s">
+        <v>4950</v>
+      </c>
+      <c r="B1913" s="22" t="s">
+        <v>4958</v>
+      </c>
       <c r="C1913"/>
       <c r="D1913"/>
     </row>
-    <row r="1914" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1914"/>
-      <c r="B1914"/>
+    <row r="1914" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1914" t="s">
+        <v>4951</v>
+      </c>
+      <c r="B1914" s="22" t="s">
+        <v>4959</v>
+      </c>
       <c r="C1914"/>
       <c r="D1914"/>
     </row>
-    <row r="1915" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1915"/>
-      <c r="B1915"/>
+    <row r="1915" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1915" t="s">
+        <v>4952</v>
+      </c>
+      <c r="B1915" s="22" t="s">
+        <v>4960</v>
+      </c>
       <c r="C1915"/>
       <c r="D1915"/>
     </row>
-    <row r="1916" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1916"/>
-      <c r="B1916"/>
+    <row r="1916" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1916" t="s">
+        <v>4953</v>
+      </c>
+      <c r="B1916" s="22" t="s">
+        <v>4961</v>
+      </c>
       <c r="C1916"/>
       <c r="D1916"/>
     </row>
-    <row r="1917" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1917"/>
-      <c r="B1917"/>
+    <row r="1917" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1917" t="s">
+        <v>4954</v>
+      </c>
+      <c r="B1917" s="22" t="s">
+        <v>4962</v>
+      </c>
       <c r="C1917"/>
       <c r="D1917"/>
     </row>
-    <row r="1918" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1918"/>
-      <c r="B1918"/>
+    <row r="1918" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1918" t="s">
+        <v>4955</v>
+      </c>
+      <c r="B1918" s="22" t="s">
+        <v>4963</v>
+      </c>
       <c r="C1918"/>
       <c r="D1918"/>
     </row>

--- a/Datas/LanguageSwitchDataList.xlsx
+++ b/Datas/LanguageSwitchDataList.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4985" uniqueCount="4965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4986" uniqueCount="4966">
   <si>
     <t>string</t>
   </si>
@@ -17074,6 +17074,9 @@
   <si>
     <t>Bulletin</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>队伍人数超过4，不能购买动物</t>
   </si>
 </sst>
 </file>
@@ -33141,7 +33144,9 @@
       <c r="D1918"/>
     </row>
     <row r="1919" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1919"/>
+      <c r="A1919" t="s">
+        <v>4965</v>
+      </c>
       <c r="B1919"/>
       <c r="C1919"/>
       <c r="D1919"/>

--- a/Datas/LanguageSwitchDataList.xlsx
+++ b/Datas/LanguageSwitchDataList.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4986" uniqueCount="4966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4987" uniqueCount="4967">
   <si>
     <t>string</t>
   </si>
@@ -17077,6 +17077,11 @@
   </si>
   <si>
     <t>队伍人数超过4，不能购买动物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The party size exceeds 4, cannot purchase animals</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -33143,11 +33148,13 @@
       <c r="C1918"/>
       <c r="D1918"/>
     </row>
-    <row r="1919" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1919" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1919" t="s">
         <v>4965</v>
       </c>
-      <c r="B1919"/>
+      <c r="B1919" s="22" t="s">
+        <v>4966</v>
+      </c>
       <c r="C1919"/>
       <c r="D1919"/>
     </row>

--- a/Datas/LanguageSwitchDataList.xlsx
+++ b/Datas/LanguageSwitchDataList.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4987" uniqueCount="4967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4995" uniqueCount="4975">
   <si>
     <t>string</t>
   </si>
@@ -17081,6 +17081,32 @@
   </si>
   <si>
     <t>The party size exceeds 4, cannot purchase animals</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>售卖价格:</t>
+  </si>
+  <si>
+    <t>（植物在适宜季节生长速度翻倍，在不适宜季节生长速度减半）</t>
+  </si>
+  <si>
+    <t>种子售卖条件：</t>
+  </si>
+  <si>
+    <t>Selling Price:</t>
+  </si>
+  <si>
+    <t>(Plant growth speed doubles in suitable seasons and halves in unsuitable seasons)</t>
+  </si>
+  <si>
+    <t>Seed selling conditions:</t>
+  </si>
+  <si>
+    <t>与+ 玛德琳 +或+ 布莱兹 +的友好度到达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reach friendship level with Madeleine or Blaze</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -17566,7 +17592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1919"/>
+  <dimension ref="A1:D1934"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.125" style="1" customWidth="1"/>
@@ -33157,6 +33183,71 @@
       </c>
       <c r="C1919"/>
       <c r="D1919"/>
+    </row>
+    <row r="1920" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1920" s="1" t="s">
+        <v>4967</v>
+      </c>
+      <c r="B1920" s="18" t="s">
+        <v>4970</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:2" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A1921" s="1" t="s">
+        <v>4968</v>
+      </c>
+      <c r="B1921" s="18" t="s">
+        <v>4971</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1922" s="1" t="s">
+        <v>4973</v>
+      </c>
+      <c r="B1922" s="18" t="s">
+        <v>4974</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1923" s="1" t="s">
+        <v>4969</v>
+      </c>
+      <c r="B1923" s="18" t="s">
+        <v>4972</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1924" s="1"/>
+    </row>
+    <row r="1925" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1925" s="1"/>
+    </row>
+    <row r="1926" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1926" s="1"/>
+    </row>
+    <row r="1927" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1927" s="1"/>
+    </row>
+    <row r="1928" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1928" s="1"/>
+    </row>
+    <row r="1929" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1929" s="1"/>
+    </row>
+    <row r="1930" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1930" s="1"/>
+    </row>
+    <row r="1931" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1931" s="1"/>
+    </row>
+    <row r="1932" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1932" s="1"/>
+    </row>
+    <row r="1933" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1933" s="1"/>
+    </row>
+    <row r="1934" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B1934" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Datas/LanguageSwitchDataList.xlsx
+++ b/Datas/LanguageSwitchDataList.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4995" uniqueCount="4975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5001" uniqueCount="4981">
   <si>
     <t>string</t>
   </si>
@@ -17108,6 +17108,24 @@
   <si>
     <t>Reach friendship level with Madeleine or Blaze</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小时</t>
+  </si>
+  <si>
+    <t>采摘次数:</t>
+  </si>
+  <si>
+    <t>成熟时间:</t>
+  </si>
+  <si>
+    <t>寿命:</t>
+  </si>
+  <si>
+    <t>生产间隔:</t>
+  </si>
+  <si>
+    <t>生长时间:</t>
   </si>
 </sst>
 </file>
@@ -33217,21 +33235,39 @@
       </c>
     </row>
     <row r="1924" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1924" s="1" t="s">
+        <v>4980</v>
+      </c>
       <c r="B1924" s="1"/>
     </row>
     <row r="1925" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1925" s="1" t="s">
+        <v>4975</v>
+      </c>
       <c r="B1925" s="1"/>
     </row>
     <row r="1926" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1926" s="1" t="s">
+        <v>4976</v>
+      </c>
       <c r="B1926" s="1"/>
     </row>
     <row r="1927" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1927" s="1" t="s">
+        <v>4977</v>
+      </c>
       <c r="B1927" s="1"/>
     </row>
     <row r="1928" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1928" s="1" t="s">
+        <v>4978</v>
+      </c>
       <c r="B1928" s="1"/>
     </row>
     <row r="1929" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1929" s="1" t="s">
+        <v>4979</v>
+      </c>
       <c r="B1929" s="1"/>
     </row>
     <row r="1930" spans="1:2" x14ac:dyDescent="0.2">

--- a/Datas/LanguageSwitchDataList.xlsx
+++ b/Datas/LanguageSwitchDataList.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5001" uniqueCount="4981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5013" uniqueCount="4993">
   <si>
     <t>string</t>
   </si>
@@ -17126,6 +17126,43 @@
   </si>
   <si>
     <t>生长时间:</t>
+  </si>
+  <si>
+    <t>发现了新农作物！</t>
+  </si>
+  <si>
+    <t>农作物</t>
+  </si>
+  <si>
+    <t>总收获:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth Time:</t>
+  </si>
+  <si>
+    <t>hour(s)</t>
+  </si>
+  <si>
+    <t>Harvest Count:</t>
+  </si>
+  <si>
+    <t>Maturation Time:</t>
+  </si>
+  <si>
+    <t>Lifespan:</t>
+  </si>
+  <si>
+    <t>Production Interval:</t>
+  </si>
+  <si>
+    <t>New crop discovered!</t>
+  </si>
+  <si>
+    <t>Crop</t>
+  </si>
+  <si>
+    <t>Total Harvest:</t>
   </si>
 </sst>
 </file>
@@ -33238,46 +33275,73 @@
       <c r="A1924" s="1" t="s">
         <v>4980</v>
       </c>
-      <c r="B1924" s="1"/>
+      <c r="B1924" s="1" t="s">
+        <v>4984</v>
+      </c>
     </row>
     <row r="1925" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1925" s="1" t="s">
         <v>4975</v>
       </c>
-      <c r="B1925" s="1"/>
+      <c r="B1925" s="1" t="s">
+        <v>4985</v>
+      </c>
     </row>
     <row r="1926" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1926" s="1" t="s">
         <v>4976</v>
       </c>
-      <c r="B1926" s="1"/>
+      <c r="B1926" s="1" t="s">
+        <v>4986</v>
+      </c>
     </row>
     <row r="1927" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1927" s="1" t="s">
         <v>4977</v>
       </c>
-      <c r="B1927" s="1"/>
+      <c r="B1927" s="1" t="s">
+        <v>4987</v>
+      </c>
     </row>
     <row r="1928" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1928" s="1" t="s">
         <v>4978</v>
       </c>
-      <c r="B1928" s="1"/>
+      <c r="B1928" s="1" t="s">
+        <v>4988</v>
+      </c>
     </row>
     <row r="1929" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1929" s="1" t="s">
         <v>4979</v>
       </c>
-      <c r="B1929" s="1"/>
+      <c r="B1929" s="1" t="s">
+        <v>4989</v>
+      </c>
     </row>
     <row r="1930" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B1930" s="1"/>
+      <c r="A1930" s="1" t="s">
+        <v>4981</v>
+      </c>
+      <c r="B1930" s="1" t="s">
+        <v>4990</v>
+      </c>
     </row>
     <row r="1931" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B1931" s="1"/>
+      <c r="A1931" s="1" t="s">
+        <v>4982</v>
+      </c>
+      <c r="B1931" s="1" t="s">
+        <v>4991</v>
+      </c>
     </row>
     <row r="1932" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B1932" s="1"/>
+      <c r="A1932" s="1" t="s">
+        <v>4983</v>
+      </c>
+      <c r="B1932" s="1" t="s">
+        <v>4992</v>
+      </c>
     </row>
     <row r="1933" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B1933" s="1"/>

--- a/Datas/LanguageSwitchDataList.xlsx
+++ b/Datas/LanguageSwitchDataList.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5029" uniqueCount="5009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5035" uniqueCount="5015">
   <si>
     <t>string</t>
   </si>
@@ -17212,6 +17212,28 @@
   </si>
   <si>
     <t>Area inhabited by Fire and Earth attribute monsters. Recommended equipment: Water and Wind attribute gear.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关于</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开发者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>About</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Developer</t>
+  </si>
+  <si>
+    <t>本游戏 部分资源购买自线上：</t>
+  </si>
+  <si>
+    <t>Some resources in this game were purchased online:</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -17697,7 +17719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1940"/>
+  <dimension ref="A1:D1943"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.125" style="1" customWidth="1"/>
@@ -33455,6 +33477,30 @@
       </c>
       <c r="B1940" s="18" t="s">
         <v>5007</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1941" s="1" t="s">
+        <v>5009</v>
+      </c>
+      <c r="B1941" s="18" t="s">
+        <v>5011</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1942" s="1" t="s">
+        <v>5010</v>
+      </c>
+      <c r="B1942" s="18" t="s">
+        <v>5012</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1943" s="1" t="s">
+        <v>5013</v>
+      </c>
+      <c r="B1943" s="18" t="s">
+        <v>5014</v>
       </c>
     </row>
   </sheetData>
